--- a/members/C1/experiment_log_C1.xlsx
+++ b/members/C1/experiment_log_C1.xlsx
@@ -751,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1000"/>
+  <dimension ref="A1:R852"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="19" min="1" max="1"/>
@@ -6562,1504 +6562,5404 @@
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="19">
-      <c r="A81" s="8" t="n"/>
-      <c r="B81" s="23" t="n"/>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="n"/>
-      <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
-      <c r="I81" s="8" t="n"/>
-      <c r="J81" s="24" t="n"/>
-      <c r="K81" s="8" t="n"/>
-      <c r="L81" s="8" t="n"/>
-      <c r="M81" s="8" t="n"/>
-      <c r="N81" s="8" t="n"/>
-      <c r="O81" s="25" t="n"/>
-      <c r="P81" s="25" t="n"/>
-      <c r="Q81" s="25" t="n"/>
-      <c r="R81" s="8" t="n"/>
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>C1-080</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G81" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K81" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L81" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M81" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N81" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O81" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P81" s="25" t="n">
+        <v>0.5916</v>
+      </c>
+      <c r="Q81" s="25" t="n">
+        <v>0.6802</v>
+      </c>
+      <c r="R81" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="19">
-      <c r="A82" s="8" t="n"/>
-      <c r="B82" s="23" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-      <c r="J82" s="24" t="n"/>
-      <c r="K82" s="8" t="n"/>
-      <c r="L82" s="8" t="n"/>
-      <c r="M82" s="8" t="n"/>
-      <c r="N82" s="8" t="n"/>
-      <c r="O82" s="25" t="n"/>
-      <c r="P82" s="25" t="n"/>
-      <c r="Q82" s="25" t="n"/>
-      <c r="R82" s="8" t="n"/>
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>C1-081</t>
+        </is>
+      </c>
+      <c r="B82" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J82" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K82" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L82" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M82" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N82" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O82" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P82" s="25" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="Q82" s="25" t="n">
+        <v>0.6819</v>
+      </c>
+      <c r="R82" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="19">
-      <c r="A83" s="8" t="n"/>
-      <c r="B83" s="23" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
-      <c r="J83" s="24" t="n"/>
-      <c r="K83" s="8" t="n"/>
-      <c r="L83" s="8" t="n"/>
-      <c r="M83" s="8" t="n"/>
-      <c r="N83" s="8" t="n"/>
-      <c r="O83" s="25" t="n"/>
-      <c r="P83" s="25" t="n"/>
-      <c r="Q83" s="25" t="n"/>
-      <c r="R83" s="8" t="n"/>
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>C1-082</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K83" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L83" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M83" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N83" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O83" s="25" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="P83" s="25" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="Q83" s="25" t="n">
+        <v>0.6843</v>
+      </c>
+      <c r="R83" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="19">
-      <c r="A84" s="8" t="n"/>
-      <c r="B84" s="23" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="24" t="n"/>
-      <c r="K84" s="8" t="n"/>
-      <c r="L84" s="8" t="n"/>
-      <c r="M84" s="8" t="n"/>
-      <c r="N84" s="8" t="n"/>
-      <c r="O84" s="25" t="n"/>
-      <c r="P84" s="25" t="n"/>
-      <c r="Q84" s="25" t="n"/>
-      <c r="R84" s="8" t="n"/>
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>C1-083</t>
+        </is>
+      </c>
+      <c r="B84" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J84" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K84" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L84" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M84" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N84" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O84" s="25" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="P84" s="25" t="n">
+        <v>0.5843</v>
+      </c>
+      <c r="Q84" s="25" t="n">
+        <v>0.6689000000000001</v>
+      </c>
+      <c r="R84" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="19">
-      <c r="A85" s="8" t="n"/>
-      <c r="B85" s="23" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
-      <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
-      <c r="I85" s="8" t="n"/>
-      <c r="J85" s="24" t="n"/>
-      <c r="K85" s="8" t="n"/>
-      <c r="L85" s="8" t="n"/>
-      <c r="M85" s="8" t="n"/>
-      <c r="N85" s="8" t="n"/>
-      <c r="O85" s="25" t="n"/>
-      <c r="P85" s="25" t="n"/>
-      <c r="Q85" s="25" t="n"/>
-      <c r="R85" s="8" t="n"/>
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>C1-084</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G85" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K85" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L85" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M85" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O85" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P85" s="25" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="Q85" s="25" t="n">
+        <v>0.6816</v>
+      </c>
+      <c r="R85" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="19">
-      <c r="A86" s="8" t="n"/>
-      <c r="B86" s="23" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
-      <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="n"/>
-      <c r="I86" s="8" t="n"/>
-      <c r="J86" s="24" t="n"/>
-      <c r="K86" s="8" t="n"/>
-      <c r="L86" s="8" t="n"/>
-      <c r="M86" s="8" t="n"/>
-      <c r="N86" s="8" t="n"/>
-      <c r="O86" s="25" t="n"/>
-      <c r="P86" s="25" t="n"/>
-      <c r="Q86" s="25" t="n"/>
-      <c r="R86" s="8" t="n"/>
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>C1-085</t>
+        </is>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J86" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K86" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L86" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M86" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N86" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O86" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P86" s="25" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="Q86" s="25" t="n">
+        <v>0.7010999999999999</v>
+      </c>
+      <c r="R86" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="19">
-      <c r="A87" s="8" t="n"/>
-      <c r="B87" s="23" t="n"/>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
-      <c r="E87" s="8" t="n"/>
-      <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
-      <c r="J87" s="24" t="n"/>
-      <c r="K87" s="8" t="n"/>
-      <c r="L87" s="8" t="n"/>
-      <c r="M87" s="8" t="n"/>
-      <c r="N87" s="8" t="n"/>
-      <c r="O87" s="25" t="n"/>
-      <c r="P87" s="25" t="n"/>
-      <c r="Q87" s="25" t="n"/>
-      <c r="R87" s="8" t="n"/>
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>C1-086</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G87" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K87" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L87" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O87" s="25" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="P87" s="25" t="n">
+        <v>0.5893</v>
+      </c>
+      <c r="Q87" s="25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R87" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="19">
-      <c r="A88" s="8" t="n"/>
-      <c r="B88" s="23" t="n"/>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
-      <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
-      <c r="J88" s="24" t="n"/>
-      <c r="K88" s="8" t="n"/>
-      <c r="L88" s="8" t="n"/>
-      <c r="M88" s="8" t="n"/>
-      <c r="N88" s="8" t="n"/>
-      <c r="O88" s="25" t="n"/>
-      <c r="P88" s="25" t="n"/>
-      <c r="Q88" s="25" t="n"/>
-      <c r="R88" s="8" t="n"/>
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>C1-087</t>
+        </is>
+      </c>
+      <c r="B88" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J88" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K88" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L88" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O88" s="25" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="P88" s="25" t="n">
+        <v>0.6035</v>
+      </c>
+      <c r="Q88" s="25" t="n">
+        <v>0.6871</v>
+      </c>
+      <c r="R88" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="19">
-      <c r="A89" s="8" t="n"/>
-      <c r="B89" s="23" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="8" t="n"/>
-      <c r="J89" s="24" t="n"/>
-      <c r="K89" s="8" t="n"/>
-      <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="n"/>
-      <c r="N89" s="8" t="n"/>
-      <c r="O89" s="25" t="n"/>
-      <c r="P89" s="25" t="n"/>
-      <c r="Q89" s="25" t="n"/>
-      <c r="R89" s="8" t="n"/>
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>C1-088</t>
+        </is>
+      </c>
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G89" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K89" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L89" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M89" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O89" s="25" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="P89" s="25" t="n">
+        <v>0.6097</v>
+      </c>
+      <c r="Q89" s="25" t="n">
+        <v>0.6878</v>
+      </c>
+      <c r="R89" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="19">
-      <c r="A90" s="8" t="n"/>
-      <c r="B90" s="23" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="8" t="n"/>
-      <c r="F90" s="8" t="n"/>
-      <c r="G90" s="8" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="8" t="n"/>
-      <c r="J90" s="24" t="n"/>
-      <c r="K90" s="8" t="n"/>
-      <c r="L90" s="8" t="n"/>
-      <c r="M90" s="8" t="n"/>
-      <c r="N90" s="8" t="n"/>
-      <c r="O90" s="25" t="n"/>
-      <c r="P90" s="25" t="n"/>
-      <c r="Q90" s="25" t="n"/>
-      <c r="R90" s="8" t="n"/>
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>C1-089</t>
+        </is>
+      </c>
+      <c r="B90" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G90" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J90" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K90" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L90" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M90" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N90" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O90" s="25" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="P90" s="25" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="Q90" s="25" t="n">
+        <v>0.7039</v>
+      </c>
+      <c r="R90" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="19">
-      <c r="A91" s="8" t="n"/>
-      <c r="B91" s="23" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="n"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="8" t="n"/>
-      <c r="J91" s="24" t="n"/>
-      <c r="K91" s="8" t="n"/>
-      <c r="L91" s="8" t="n"/>
-      <c r="M91" s="8" t="n"/>
-      <c r="N91" s="8" t="n"/>
-      <c r="O91" s="25" t="n"/>
-      <c r="P91" s="25" t="n"/>
-      <c r="Q91" s="25" t="n"/>
-      <c r="R91" s="8" t="n"/>
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>C1-090</t>
+        </is>
+      </c>
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K91" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L91" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M91" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O91" s="25" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="P91" s="25" t="n">
+        <v>0.5907</v>
+      </c>
+      <c r="Q91" s="25" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="R91" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="19">
-      <c r="A92" s="8" t="n"/>
-      <c r="B92" s="23" t="n"/>
-      <c r="C92" s="8" t="n"/>
-      <c r="D92" s="8" t="n"/>
-      <c r="E92" s="8" t="n"/>
-      <c r="F92" s="8" t="n"/>
-      <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="8" t="n"/>
-      <c r="J92" s="24" t="n"/>
-      <c r="K92" s="8" t="n"/>
-      <c r="L92" s="8" t="n"/>
-      <c r="M92" s="8" t="n"/>
-      <c r="N92" s="8" t="n"/>
-      <c r="O92" s="25" t="n"/>
-      <c r="P92" s="25" t="n"/>
-      <c r="Q92" s="25" t="n"/>
-      <c r="R92" s="8" t="n"/>
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>C1-091</t>
+        </is>
+      </c>
+      <c r="B92" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J92" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K92" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L92" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M92" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N92" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O92" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P92" s="25" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="Q92" s="25" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="R92" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="19">
-      <c r="A93" s="8" t="n"/>
-      <c r="B93" s="23" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
-      <c r="E93" s="8" t="n"/>
-      <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="8" t="n"/>
-      <c r="J93" s="24" t="n"/>
-      <c r="K93" s="8" t="n"/>
-      <c r="L93" s="8" t="n"/>
-      <c r="M93" s="8" t="n"/>
-      <c r="N93" s="8" t="n"/>
-      <c r="O93" s="25" t="n"/>
-      <c r="P93" s="25" t="n"/>
-      <c r="Q93" s="25" t="n"/>
-      <c r="R93" s="8" t="n"/>
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>C1-092</t>
+        </is>
+      </c>
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K93" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L93" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M93" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N93" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O93" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P93" s="25" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="Q93" s="25" t="n">
+        <v>0.6945</v>
+      </c>
+      <c r="R93" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="19">
-      <c r="A94" s="8" t="n"/>
-      <c r="B94" s="23" t="n"/>
-      <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="8" t="n"/>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="8" t="n"/>
-      <c r="J94" s="24" t="n"/>
-      <c r="K94" s="8" t="n"/>
-      <c r="L94" s="8" t="n"/>
-      <c r="M94" s="8" t="n"/>
-      <c r="N94" s="8" t="n"/>
-      <c r="O94" s="25" t="n"/>
-      <c r="P94" s="25" t="n"/>
-      <c r="Q94" s="25" t="n"/>
-      <c r="R94" s="8" t="n"/>
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>C1-093</t>
+        </is>
+      </c>
+      <c r="B94" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G94" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J94" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K94" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L94" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M94" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N94" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O94" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P94" s="25" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="Q94" s="25" t="n">
+        <v>0.6918</v>
+      </c>
+      <c r="R94" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="19">
-      <c r="A95" s="8" t="n"/>
-      <c r="B95" s="23" t="n"/>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
-      <c r="E95" s="8" t="n"/>
-      <c r="F95" s="8" t="n"/>
-      <c r="G95" s="8" t="n"/>
-      <c r="H95" s="8" t="n"/>
-      <c r="I95" s="8" t="n"/>
-      <c r="J95" s="24" t="n"/>
-      <c r="K95" s="8" t="n"/>
-      <c r="L95" s="8" t="n"/>
-      <c r="M95" s="8" t="n"/>
-      <c r="N95" s="8" t="n"/>
-      <c r="O95" s="25" t="n"/>
-      <c r="P95" s="25" t="n"/>
-      <c r="Q95" s="25" t="n"/>
-      <c r="R95" s="8" t="n"/>
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>C1-094</t>
+        </is>
+      </c>
+      <c r="B95" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G95" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K95" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L95" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M95" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N95" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O95" s="25" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="P95" s="25" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="Q95" s="25" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="R95" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 A, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="19">
-      <c r="A96" s="8" t="n"/>
-      <c r="B96" s="23" t="n"/>
-      <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="8" t="n"/>
-      <c r="J96" s="24" t="n"/>
-      <c r="K96" s="8" t="n"/>
-      <c r="L96" s="8" t="n"/>
-      <c r="M96" s="8" t="n"/>
-      <c r="N96" s="8" t="n"/>
-      <c r="O96" s="25" t="n"/>
-      <c r="P96" s="25" t="n"/>
-      <c r="Q96" s="25" t="n"/>
-      <c r="R96" s="8" t="n"/>
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>C1-095</t>
+        </is>
+      </c>
+      <c r="B96" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G96" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J96" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K96" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L96" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M96" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N96" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O96" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P96" s="25" t="n">
+        <v>0.5849</v>
+      </c>
+      <c r="Q96" s="25" t="n">
+        <v>0.6845</v>
+      </c>
+      <c r="R96" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="19">
-      <c r="A97" s="8" t="n"/>
-      <c r="B97" s="23" t="n"/>
-      <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
-      <c r="E97" s="8" t="n"/>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="n"/>
-      <c r="J97" s="24" t="n"/>
-      <c r="K97" s="8" t="n"/>
-      <c r="L97" s="8" t="n"/>
-      <c r="M97" s="8" t="n"/>
-      <c r="N97" s="8" t="n"/>
-      <c r="O97" s="25" t="n"/>
-      <c r="P97" s="25" t="n"/>
-      <c r="Q97" s="25" t="n"/>
-      <c r="R97" s="8" t="n"/>
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>C1-096</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J97" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K97" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L97" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M97" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N97" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O97" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P97" s="25" t="n">
+        <v>0.5891</v>
+      </c>
+      <c r="Q97" s="25" t="n">
+        <v>0.6711</v>
+      </c>
+      <c r="R97" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="19">
-      <c r="A98" s="8" t="n"/>
-      <c r="B98" s="23" t="n"/>
-      <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="8" t="n"/>
-      <c r="F98" s="8" t="n"/>
-      <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-      <c r="J98" s="24" t="n"/>
-      <c r="K98" s="8" t="n"/>
-      <c r="L98" s="8" t="n"/>
-      <c r="M98" s="8" t="n"/>
-      <c r="N98" s="8" t="n"/>
-      <c r="O98" s="25" t="n"/>
-      <c r="P98" s="25" t="n"/>
-      <c r="Q98" s="25" t="n"/>
-      <c r="R98" s="8" t="n"/>
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>C1-097</t>
+        </is>
+      </c>
+      <c r="B98" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G98" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J98" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K98" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L98" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M98" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N98" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O98" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P98" s="25" t="n">
+        <v>0.5894</v>
+      </c>
+      <c r="Q98" s="25" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="R98" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="19">
-      <c r="A99" s="8" t="n"/>
-      <c r="B99" s="23" t="n"/>
-      <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
-      <c r="E99" s="8" t="n"/>
-      <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
-      <c r="J99" s="24" t="n"/>
-      <c r="K99" s="8" t="n"/>
-      <c r="L99" s="8" t="n"/>
-      <c r="M99" s="8" t="n"/>
-      <c r="N99" s="8" t="n"/>
-      <c r="O99" s="25" t="n"/>
-      <c r="P99" s="25" t="n"/>
-      <c r="Q99" s="25" t="n"/>
-      <c r="R99" s="8" t="n"/>
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>C1-098</t>
+        </is>
+      </c>
+      <c r="B99" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G99" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J99" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K99" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L99" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M99" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N99" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O99" s="25" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="P99" s="25" t="n">
+        <v>0.6166</v>
+      </c>
+      <c r="Q99" s="25" t="n">
+        <v>0.6906</v>
+      </c>
+      <c r="R99" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="19">
-      <c r="A100" s="8" t="n"/>
-      <c r="B100" s="23" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="8" t="n"/>
-      <c r="J100" s="24" t="n"/>
-      <c r="K100" s="8" t="n"/>
-      <c r="L100" s="8" t="n"/>
-      <c r="M100" s="8" t="n"/>
-      <c r="N100" s="8" t="n"/>
-      <c r="O100" s="25" t="n"/>
-      <c r="P100" s="25" t="n"/>
-      <c r="Q100" s="25" t="n"/>
-      <c r="R100" s="8" t="n"/>
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>C1-099</t>
+        </is>
+      </c>
+      <c r="B100" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G100" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J100" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K100" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L100" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M100" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N100" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O100" s="25" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="P100" s="25" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="Q100" s="25" t="n">
+        <v>0.6572</v>
+      </c>
+      <c r="R100" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="19">
-      <c r="A101" s="8" t="n"/>
-      <c r="B101" s="23" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="n"/>
-      <c r="J101" s="24" t="n"/>
-      <c r="K101" s="8" t="n"/>
-      <c r="L101" s="8" t="n"/>
-      <c r="M101" s="8" t="n"/>
-      <c r="N101" s="8" t="n"/>
-      <c r="O101" s="25" t="n"/>
-      <c r="P101" s="25" t="n"/>
-      <c r="Q101" s="25" t="n"/>
-      <c r="R101" s="8" t="n"/>
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>C1-100</t>
+        </is>
+      </c>
+      <c r="B101" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G101" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J101" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K101" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L101" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M101" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N101" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O101" s="25" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="P101" s="25" t="n">
+        <v>0.5873</v>
+      </c>
+      <c r="Q101" s="25" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="R101" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="19">
-      <c r="A102" s="8" t="n"/>
-      <c r="B102" s="23" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="n"/>
-      <c r="G102" s="8" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
-      <c r="J102" s="24" t="n"/>
-      <c r="K102" s="8" t="n"/>
-      <c r="L102" s="8" t="n"/>
-      <c r="M102" s="8" t="n"/>
-      <c r="N102" s="8" t="n"/>
-      <c r="O102" s="25" t="n"/>
-      <c r="P102" s="25" t="n"/>
-      <c r="Q102" s="25" t="n"/>
-      <c r="R102" s="8" t="n"/>
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>C1-101</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G102" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J102" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K102" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L102" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M102" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N102" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O102" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P102" s="25" t="n">
+        <v>0.5894</v>
+      </c>
+      <c r="Q102" s="25" t="n">
+        <v>0.6892</v>
+      </c>
+      <c r="R102" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="19">
-      <c r="A103" s="8" t="n"/>
-      <c r="B103" s="23" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
-      <c r="J103" s="24" t="n"/>
-      <c r="K103" s="8" t="n"/>
-      <c r="L103" s="8" t="n"/>
-      <c r="M103" s="8" t="n"/>
-      <c r="N103" s="8" t="n"/>
-      <c r="O103" s="25" t="n"/>
-      <c r="P103" s="25" t="n"/>
-      <c r="Q103" s="25" t="n"/>
-      <c r="R103" s="8" t="n"/>
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>C1-102</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G103" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J103" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K103" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L103" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M103" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N103" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O103" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P103" s="25" t="n">
+        <v>0.5934</v>
+      </c>
+      <c r="Q103" s="25" t="n">
+        <v>0.6708</v>
+      </c>
+      <c r="R103" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="19">
-      <c r="A104" s="8" t="n"/>
-      <c r="B104" s="23" t="n"/>
-      <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="n"/>
-      <c r="E104" s="8" t="n"/>
-      <c r="F104" s="8" t="n"/>
-      <c r="G104" s="8" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="8" t="n"/>
-      <c r="J104" s="24" t="n"/>
-      <c r="K104" s="8" t="n"/>
-      <c r="L104" s="8" t="n"/>
-      <c r="M104" s="8" t="n"/>
-      <c r="N104" s="8" t="n"/>
-      <c r="O104" s="25" t="n"/>
-      <c r="P104" s="25" t="n"/>
-      <c r="Q104" s="25" t="n"/>
-      <c r="R104" s="8" t="n"/>
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>C1-103</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G104" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J104" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K104" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L104" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M104" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N104" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O104" s="25" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="P104" s="25" t="n">
+        <v>0.5988</v>
+      </c>
+      <c r="Q104" s="25" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="R104" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="19">
-      <c r="A105" s="8" t="n"/>
-      <c r="B105" s="23" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
-      <c r="E105" s="8" t="n"/>
-      <c r="F105" s="8" t="n"/>
-      <c r="G105" s="8" t="n"/>
-      <c r="H105" s="8" t="n"/>
-      <c r="I105" s="8" t="n"/>
-      <c r="J105" s="24" t="n"/>
-      <c r="K105" s="8" t="n"/>
-      <c r="L105" s="8" t="n"/>
-      <c r="M105" s="8" t="n"/>
-      <c r="N105" s="8" t="n"/>
-      <c r="O105" s="25" t="n"/>
-      <c r="P105" s="25" t="n"/>
-      <c r="Q105" s="25" t="n"/>
-      <c r="R105" s="8" t="n"/>
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>C1-104</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G105" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J105" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K105" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L105" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M105" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N105" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O105" s="25" t="n">
+        <v>0.7696</v>
+      </c>
+      <c r="P105" s="25" t="n">
+        <v>0.5988</v>
+      </c>
+      <c r="Q105" s="25" t="n">
+        <v>0.6587</v>
+      </c>
+      <c r="R105" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="19">
-      <c r="A106" s="8" t="n"/>
-      <c r="B106" s="23" t="n"/>
-      <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
-      <c r="E106" s="8" t="n"/>
-      <c r="F106" s="8" t="n"/>
-      <c r="G106" s="8" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="8" t="n"/>
-      <c r="J106" s="24" t="n"/>
-      <c r="K106" s="8" t="n"/>
-      <c r="L106" s="8" t="n"/>
-      <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n"/>
-      <c r="O106" s="25" t="n"/>
-      <c r="P106" s="25" t="n"/>
-      <c r="Q106" s="25" t="n"/>
-      <c r="R106" s="8" t="n"/>
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>C1-105</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G106" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J106" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K106" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L106" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M106" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N106" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O106" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P106" s="25" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="Q106" s="25" t="n">
+        <v>0.6798999999999999</v>
+      </c>
+      <c r="R106" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="19">
-      <c r="A107" s="8" t="n"/>
-      <c r="B107" s="23" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="24" t="n"/>
-      <c r="K107" s="8" t="n"/>
-      <c r="L107" s="8" t="n"/>
-      <c r="M107" s="8" t="n"/>
-      <c r="N107" s="8" t="n"/>
-      <c r="O107" s="25" t="n"/>
-      <c r="P107" s="25" t="n"/>
-      <c r="Q107" s="25" t="n"/>
-      <c r="R107" s="8" t="n"/>
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>C1-106</t>
+        </is>
+      </c>
+      <c r="B107" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G107" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J107" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K107" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L107" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M107" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N107" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O107" s="25" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="P107" s="25" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="Q107" s="25" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="R107" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="19">
-      <c r="A108" s="8" t="n"/>
-      <c r="B108" s="23" t="n"/>
-      <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="8" t="n"/>
-      <c r="F108" s="8" t="n"/>
-      <c r="G108" s="8" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="24" t="n"/>
-      <c r="K108" s="8" t="n"/>
-      <c r="L108" s="8" t="n"/>
-      <c r="M108" s="8" t="n"/>
-      <c r="N108" s="8" t="n"/>
-      <c r="O108" s="25" t="n"/>
-      <c r="P108" s="25" t="n"/>
-      <c r="Q108" s="25" t="n"/>
-      <c r="R108" s="8" t="n"/>
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>C1-107</t>
+        </is>
+      </c>
+      <c r="B108" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G108" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J108" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K108" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L108" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M108" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N108" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O108" s="25" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="P108" s="25" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="Q108" s="25" t="n">
+        <v>0.6794</v>
+      </c>
+      <c r="R108" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="19">
-      <c r="A109" s="8" t="n"/>
-      <c r="B109" s="23" t="n"/>
-      <c r="C109" s="8" t="n"/>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="8" t="n"/>
-      <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
-      <c r="J109" s="24" t="n"/>
-      <c r="K109" s="8" t="n"/>
-      <c r="L109" s="8" t="n"/>
-      <c r="M109" s="8" t="n"/>
-      <c r="N109" s="8" t="n"/>
-      <c r="O109" s="25" t="n"/>
-      <c r="P109" s="25" t="n"/>
-      <c r="Q109" s="25" t="n"/>
-      <c r="R109" s="8" t="n"/>
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>C1-108</t>
+        </is>
+      </c>
+      <c r="B109" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G109" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J109" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K109" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L109" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M109" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N109" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O109" s="25" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="P109" s="25" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="Q109" s="25" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="R109" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="19">
-      <c r="A110" s="8" t="n"/>
-      <c r="B110" s="23" t="n"/>
-      <c r="C110" s="8" t="n"/>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="8" t="n"/>
-      <c r="F110" s="8" t="n"/>
-      <c r="G110" s="8" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="8" t="n"/>
-      <c r="J110" s="24" t="n"/>
-      <c r="K110" s="8" t="n"/>
-      <c r="L110" s="8" t="n"/>
-      <c r="M110" s="8" t="n"/>
-      <c r="N110" s="8" t="n"/>
-      <c r="O110" s="25" t="n"/>
-      <c r="P110" s="25" t="n"/>
-      <c r="Q110" s="25" t="n"/>
-      <c r="R110" s="8" t="n"/>
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>C1-109</t>
+        </is>
+      </c>
+      <c r="B110" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G110" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J110" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K110" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L110" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M110" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N110" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O110" s="25" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="P110" s="25" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="Q110" s="25" t="n">
+        <v>0.6732</v>
+      </c>
+      <c r="R110" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 B, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="19">
-      <c r="A111" s="8" t="n"/>
-      <c r="B111" s="23" t="n"/>
-      <c r="C111" s="8" t="n"/>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="8" t="n"/>
-      <c r="F111" s="8" t="n"/>
-      <c r="G111" s="8" t="n"/>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="8" t="n"/>
-      <c r="J111" s="24" t="n"/>
-      <c r="K111" s="8" t="n"/>
-      <c r="L111" s="8" t="n"/>
-      <c r="M111" s="8" t="n"/>
-      <c r="N111" s="8" t="n"/>
-      <c r="O111" s="25" t="n"/>
-      <c r="P111" s="25" t="n"/>
-      <c r="Q111" s="25" t="n"/>
-      <c r="R111" s="8" t="n"/>
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>C1-110</t>
+        </is>
+      </c>
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G111" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J111" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K111" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L111" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M111" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N111" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O111" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P111" s="25" t="n">
+        <v>0.6068</v>
+      </c>
+      <c r="Q111" s="25" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="R111" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="19">
-      <c r="A112" s="8" t="n"/>
-      <c r="B112" s="23" t="n"/>
-      <c r="C112" s="8" t="n"/>
-      <c r="D112" s="8" t="n"/>
-      <c r="E112" s="8" t="n"/>
-      <c r="F112" s="8" t="n"/>
-      <c r="G112" s="8" t="n"/>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="8" t="n"/>
-      <c r="J112" s="24" t="n"/>
-      <c r="K112" s="8" t="n"/>
-      <c r="L112" s="8" t="n"/>
-      <c r="M112" s="8" t="n"/>
-      <c r="N112" s="8" t="n"/>
-      <c r="O112" s="25" t="n"/>
-      <c r="P112" s="25" t="n"/>
-      <c r="Q112" s="25" t="n"/>
-      <c r="R112" s="8" t="n"/>
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>C1-111</t>
+        </is>
+      </c>
+      <c r="B112" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G112" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J112" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K112" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L112" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M112" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N112" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O112" s="25" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="P112" s="25" t="n">
+        <v>0.5924</v>
+      </c>
+      <c r="Q112" s="25" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="R112" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="19">
-      <c r="A113" s="8" t="n"/>
-      <c r="B113" s="23" t="n"/>
-      <c r="C113" s="8" t="n"/>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="8" t="n"/>
-      <c r="G113" s="8" t="n"/>
-      <c r="H113" s="8" t="n"/>
-      <c r="I113" s="8" t="n"/>
-      <c r="J113" s="24" t="n"/>
-      <c r="K113" s="8" t="n"/>
-      <c r="L113" s="8" t="n"/>
-      <c r="M113" s="8" t="n"/>
-      <c r="N113" s="8" t="n"/>
-      <c r="O113" s="25" t="n"/>
-      <c r="P113" s="25" t="n"/>
-      <c r="Q113" s="25" t="n"/>
-      <c r="R113" s="8" t="n"/>
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>C1-112</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J113" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K113" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L113" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M113" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N113" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O113" s="25" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="P113" s="25" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="Q113" s="25" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="R113" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="19">
-      <c r="A114" s="8" t="n"/>
-      <c r="B114" s="23" t="n"/>
-      <c r="C114" s="8" t="n"/>
-      <c r="D114" s="8" t="n"/>
-      <c r="E114" s="8" t="n"/>
-      <c r="F114" s="8" t="n"/>
-      <c r="G114" s="8" t="n"/>
-      <c r="H114" s="8" t="n"/>
-      <c r="I114" s="8" t="n"/>
-      <c r="J114" s="24" t="n"/>
-      <c r="K114" s="8" t="n"/>
-      <c r="L114" s="8" t="n"/>
-      <c r="M114" s="8" t="n"/>
-      <c r="N114" s="8" t="n"/>
-      <c r="O114" s="25" t="n"/>
-      <c r="P114" s="25" t="n"/>
-      <c r="Q114" s="25" t="n"/>
-      <c r="R114" s="8" t="n"/>
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>C1-113</t>
+        </is>
+      </c>
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G114" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J114" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K114" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L114" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M114" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N114" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O114" s="25" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="P114" s="25" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="Q114" s="25" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="R114" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="19">
-      <c r="A115" s="8" t="n"/>
-      <c r="B115" s="23" t="n"/>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
-      <c r="E115" s="8" t="n"/>
-      <c r="F115" s="8" t="n"/>
-      <c r="G115" s="8" t="n"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="8" t="n"/>
-      <c r="J115" s="24" t="n"/>
-      <c r="K115" s="8" t="n"/>
-      <c r="L115" s="8" t="n"/>
-      <c r="M115" s="8" t="n"/>
-      <c r="N115" s="8" t="n"/>
-      <c r="O115" s="25" t="n"/>
-      <c r="P115" s="25" t="n"/>
-      <c r="Q115" s="25" t="n"/>
-      <c r="R115" s="8" t="n"/>
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>C1-114</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G115" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J115" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K115" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L115" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M115" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N115" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O115" s="25" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="P115" s="25" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="Q115" s="25" t="n">
+        <v>0.6926</v>
+      </c>
+      <c r="R115" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="19">
-      <c r="A116" s="8" t="n"/>
-      <c r="B116" s="23" t="n"/>
-      <c r="C116" s="8" t="n"/>
-      <c r="D116" s="8" t="n"/>
-      <c r="E116" s="8" t="n"/>
-      <c r="F116" s="8" t="n"/>
-      <c r="G116" s="8" t="n"/>
-      <c r="H116" s="8" t="n"/>
-      <c r="I116" s="8" t="n"/>
-      <c r="J116" s="24" t="n"/>
-      <c r="K116" s="8" t="n"/>
-      <c r="L116" s="8" t="n"/>
-      <c r="M116" s="8" t="n"/>
-      <c r="N116" s="8" t="n"/>
-      <c r="O116" s="25" t="n"/>
-      <c r="P116" s="25" t="n"/>
-      <c r="Q116" s="25" t="n"/>
-      <c r="R116" s="8" t="n"/>
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>C1-115</t>
+        </is>
+      </c>
+      <c r="B116" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J116" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K116" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L116" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M116" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N116" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O116" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P116" s="25" t="n">
+        <v>0.6135</v>
+      </c>
+      <c r="Q116" s="25" t="n">
+        <v>0.6771</v>
+      </c>
+      <c r="R116" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="19">
-      <c r="A117" s="8" t="n"/>
-      <c r="B117" s="23" t="n"/>
-      <c r="C117" s="8" t="n"/>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="8" t="n"/>
-      <c r="F117" s="8" t="n"/>
-      <c r="G117" s="8" t="n"/>
-      <c r="H117" s="8" t="n"/>
-      <c r="I117" s="8" t="n"/>
-      <c r="J117" s="24" t="n"/>
-      <c r="K117" s="8" t="n"/>
-      <c r="L117" s="8" t="n"/>
-      <c r="M117" s="8" t="n"/>
-      <c r="N117" s="8" t="n"/>
-      <c r="O117" s="25" t="n"/>
-      <c r="P117" s="25" t="n"/>
-      <c r="Q117" s="25" t="n"/>
-      <c r="R117" s="8" t="n"/>
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>C1-116</t>
+        </is>
+      </c>
+      <c r="B117" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G117" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J117" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K117" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L117" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M117" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N117" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O117" s="25" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="P117" s="25" t="n">
+        <v>0.6069</v>
+      </c>
+      <c r="Q117" s="25" t="n">
+        <v>0.6553</v>
+      </c>
+      <c r="R117" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="19">
-      <c r="A118" s="8" t="n"/>
-      <c r="B118" s="23" t="n"/>
-      <c r="C118" s="8" t="n"/>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="8" t="n"/>
-      <c r="F118" s="8" t="n"/>
-      <c r="G118" s="8" t="n"/>
-      <c r="H118" s="8" t="n"/>
-      <c r="I118" s="8" t="n"/>
-      <c r="J118" s="24" t="n"/>
-      <c r="K118" s="8" t="n"/>
-      <c r="L118" s="8" t="n"/>
-      <c r="M118" s="8" t="n"/>
-      <c r="N118" s="8" t="n"/>
-      <c r="O118" s="25" t="n"/>
-      <c r="P118" s="25" t="n"/>
-      <c r="Q118" s="25" t="n"/>
-      <c r="R118" s="8" t="n"/>
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>C1-117</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G118" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J118" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K118" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L118" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M118" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N118" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O118" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P118" s="25" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="Q118" s="25" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="R118" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="19">
-      <c r="A119" s="8" t="n"/>
-      <c r="B119" s="23" t="n"/>
-      <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="8" t="n"/>
-      <c r="F119" s="8" t="n"/>
-      <c r="G119" s="8" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="8" t="n"/>
-      <c r="J119" s="24" t="n"/>
-      <c r="K119" s="8" t="n"/>
-      <c r="L119" s="8" t="n"/>
-      <c r="M119" s="8" t="n"/>
-      <c r="N119" s="8" t="n"/>
-      <c r="O119" s="25" t="n"/>
-      <c r="P119" s="25" t="n"/>
-      <c r="Q119" s="25" t="n"/>
-      <c r="R119" s="8" t="n"/>
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>C1-118</t>
+        </is>
+      </c>
+      <c r="B119" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J119" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K119" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L119" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M119" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N119" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O119" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P119" s="25" t="n">
+        <v>0.5946</v>
+      </c>
+      <c r="Q119" s="25" t="n">
+        <v>0.6748</v>
+      </c>
+      <c r="R119" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="19">
-      <c r="A120" s="8" t="n"/>
-      <c r="B120" s="23" t="n"/>
-      <c r="C120" s="8" t="n"/>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="8" t="n"/>
-      <c r="F120" s="8" t="n"/>
-      <c r="G120" s="8" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="8" t="n"/>
-      <c r="J120" s="24" t="n"/>
-      <c r="K120" s="8" t="n"/>
-      <c r="L120" s="8" t="n"/>
-      <c r="M120" s="8" t="n"/>
-      <c r="N120" s="8" t="n"/>
-      <c r="O120" s="25" t="n"/>
-      <c r="P120" s="25" t="n"/>
-      <c r="Q120" s="25" t="n"/>
-      <c r="R120" s="8" t="n"/>
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>C1-119</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G120" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J120" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K120" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L120" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M120" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N120" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O120" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P120" s="25" t="n">
+        <v>0.6117</v>
+      </c>
+      <c r="Q120" s="25" t="n">
+        <v>0.6645</v>
+      </c>
+      <c r="R120" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="19">
-      <c r="A121" s="8" t="n"/>
-      <c r="B121" s="23" t="n"/>
-      <c r="C121" s="8" t="n"/>
-      <c r="D121" s="8" t="n"/>
-      <c r="E121" s="8" t="n"/>
-      <c r="F121" s="8" t="n"/>
-      <c r="G121" s="8" t="n"/>
-      <c r="H121" s="8" t="n"/>
-      <c r="I121" s="8" t="n"/>
-      <c r="J121" s="24" t="n"/>
-      <c r="K121" s="8" t="n"/>
-      <c r="L121" s="8" t="n"/>
-      <c r="M121" s="8" t="n"/>
-      <c r="N121" s="8" t="n"/>
-      <c r="O121" s="25" t="n"/>
-      <c r="P121" s="25" t="n"/>
-      <c r="Q121" s="25" t="n"/>
-      <c r="R121" s="8" t="n"/>
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>C1-120</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G121" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J121" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K121" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L121" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M121" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N121" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O121" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P121" s="25" t="n">
+        <v>0.5972</v>
+      </c>
+      <c r="Q121" s="25" t="n">
+        <v>0.6708</v>
+      </c>
+      <c r="R121" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="19">
-      <c r="A122" s="8" t="n"/>
-      <c r="B122" s="23" t="n"/>
-      <c r="C122" s="8" t="n"/>
-      <c r="D122" s="8" t="n"/>
-      <c r="E122" s="8" t="n"/>
-      <c r="F122" s="8" t="n"/>
-      <c r="G122" s="8" t="n"/>
-      <c r="H122" s="8" t="n"/>
-      <c r="I122" s="8" t="n"/>
-      <c r="J122" s="24" t="n"/>
-      <c r="K122" s="8" t="n"/>
-      <c r="L122" s="8" t="n"/>
-      <c r="M122" s="8" t="n"/>
-      <c r="N122" s="8" t="n"/>
-      <c r="O122" s="25" t="n"/>
-      <c r="P122" s="25" t="n"/>
-      <c r="Q122" s="25" t="n"/>
-      <c r="R122" s="8" t="n"/>
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>C1-121</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G122" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J122" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K122" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L122" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M122" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N122" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O122" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P122" s="25" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="Q122" s="25" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="R122" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="19">
-      <c r="A123" s="8" t="n"/>
-      <c r="B123" s="23" t="n"/>
-      <c r="C123" s="8" t="n"/>
-      <c r="D123" s="8" t="n"/>
-      <c r="E123" s="8" t="n"/>
-      <c r="F123" s="8" t="n"/>
-      <c r="G123" s="8" t="n"/>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="8" t="n"/>
-      <c r="J123" s="24" t="n"/>
-      <c r="K123" s="8" t="n"/>
-      <c r="L123" s="8" t="n"/>
-      <c r="M123" s="8" t="n"/>
-      <c r="N123" s="8" t="n"/>
-      <c r="O123" s="25" t="n"/>
-      <c r="P123" s="25" t="n"/>
-      <c r="Q123" s="25" t="n"/>
-      <c r="R123" s="8" t="n"/>
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>C1-122</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G123" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J123" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K123" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L123" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M123" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N123" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O123" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P123" s="25" t="n">
+        <v>0.6068</v>
+      </c>
+      <c r="Q123" s="25" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="R123" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="19">
-      <c r="A124" s="8" t="n"/>
-      <c r="B124" s="23" t="n"/>
-      <c r="C124" s="8" t="n"/>
-      <c r="D124" s="8" t="n"/>
-      <c r="E124" s="8" t="n"/>
-      <c r="F124" s="8" t="n"/>
-      <c r="G124" s="8" t="n"/>
-      <c r="H124" s="8" t="n"/>
-      <c r="I124" s="8" t="n"/>
-      <c r="J124" s="24" t="n"/>
-      <c r="K124" s="8" t="n"/>
-      <c r="L124" s="8" t="n"/>
-      <c r="M124" s="8" t="n"/>
-      <c r="N124" s="8" t="n"/>
-      <c r="O124" s="25" t="n"/>
-      <c r="P124" s="25" t="n"/>
-      <c r="Q124" s="25" t="n"/>
-      <c r="R124" s="8" t="n"/>
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>C1-123</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G124" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J124" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K124" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L124" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M124" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N124" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O124" s="25" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="P124" s="25" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+      <c r="Q124" s="25" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="R124" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="19">
-      <c r="A125" s="8" t="n"/>
-      <c r="B125" s="23" t="n"/>
-      <c r="C125" s="8" t="n"/>
-      <c r="D125" s="8" t="n"/>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="8" t="n"/>
-      <c r="G125" s="8" t="n"/>
-      <c r="H125" s="8" t="n"/>
-      <c r="I125" s="8" t="n"/>
-      <c r="J125" s="24" t="n"/>
-      <c r="K125" s="8" t="n"/>
-      <c r="L125" s="8" t="n"/>
-      <c r="M125" s="8" t="n"/>
-      <c r="N125" s="8" t="n"/>
-      <c r="O125" s="25" t="n"/>
-      <c r="P125" s="25" t="n"/>
-      <c r="Q125" s="25" t="n"/>
-      <c r="R125" s="8" t="n"/>
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>C1-124</t>
+        </is>
+      </c>
+      <c r="B125" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J125" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K125" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L125" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M125" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N125" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O125" s="25" t="n">
+        <v>0.7853</v>
+      </c>
+      <c r="P125" s="25" t="n">
+        <v>0.6024</v>
+      </c>
+      <c r="Q125" s="25" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="R125" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 C, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="19">
-      <c r="A126" s="8" t="n"/>
-      <c r="B126" s="23" t="n"/>
-      <c r="C126" s="8" t="n"/>
-      <c r="D126" s="8" t="n"/>
-      <c r="E126" s="8" t="n"/>
-      <c r="F126" s="8" t="n"/>
-      <c r="G126" s="8" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="8" t="n"/>
-      <c r="J126" s="24" t="n"/>
-      <c r="K126" s="8" t="n"/>
-      <c r="L126" s="8" t="n"/>
-      <c r="M126" s="8" t="n"/>
-      <c r="N126" s="8" t="n"/>
-      <c r="O126" s="25" t="n"/>
-      <c r="P126" s="25" t="n"/>
-      <c r="Q126" s="25" t="n"/>
-      <c r="R126" s="8" t="n"/>
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>C1-125</t>
+        </is>
+      </c>
+      <c r="B126" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G126" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J126" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K126" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L126" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M126" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N126" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O126" s="25" t="n">
+        <v>0.7592</v>
+      </c>
+      <c r="P126" s="25" t="n">
+        <v>0.6197</v>
+      </c>
+      <c r="Q126" s="25" t="n">
+        <v>0.6816</v>
+      </c>
+      <c r="R126" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="19">
-      <c r="A127" s="8" t="n"/>
-      <c r="B127" s="23" t="n"/>
-      <c r="C127" s="8" t="n"/>
-      <c r="D127" s="8" t="n"/>
-      <c r="E127" s="8" t="n"/>
-      <c r="F127" s="8" t="n"/>
-      <c r="G127" s="8" t="n"/>
-      <c r="H127" s="8" t="n"/>
-      <c r="I127" s="8" t="n"/>
-      <c r="J127" s="24" t="n"/>
-      <c r="K127" s="8" t="n"/>
-      <c r="L127" s="8" t="n"/>
-      <c r="M127" s="8" t="n"/>
-      <c r="N127" s="8" t="n"/>
-      <c r="O127" s="25" t="n"/>
-      <c r="P127" s="25" t="n"/>
-      <c r="Q127" s="25" t="n"/>
-      <c r="R127" s="8" t="n"/>
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>C1-126</t>
+        </is>
+      </c>
+      <c r="B127" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G127" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J127" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K127" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L127" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M127" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N127" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O127" s="25" t="n">
+        <v>0.7644</v>
+      </c>
+      <c r="P127" s="25" t="n">
+        <v>0.6122</v>
+      </c>
+      <c r="Q127" s="25" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R127" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="19">
-      <c r="A128" s="8" t="n"/>
-      <c r="B128" s="23" t="n"/>
-      <c r="C128" s="8" t="n"/>
-      <c r="D128" s="8" t="n"/>
-      <c r="E128" s="8" t="n"/>
-      <c r="F128" s="8" t="n"/>
-      <c r="G128" s="8" t="n"/>
-      <c r="H128" s="8" t="n"/>
-      <c r="I128" s="8" t="n"/>
-      <c r="J128" s="24" t="n"/>
-      <c r="K128" s="8" t="n"/>
-      <c r="L128" s="8" t="n"/>
-      <c r="M128" s="8" t="n"/>
-      <c r="N128" s="8" t="n"/>
-      <c r="O128" s="25" t="n"/>
-      <c r="P128" s="25" t="n"/>
-      <c r="Q128" s="25" t="n"/>
-      <c r="R128" s="8" t="n"/>
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>C1-127</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G128" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H128" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J128" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K128" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L128" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M128" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N128" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O128" s="25" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="P128" s="25" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="Q128" s="25" t="n">
+        <v>0.6776</v>
+      </c>
+      <c r="R128" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="19">
-      <c r="A129" s="8" t="n"/>
-      <c r="B129" s="23" t="n"/>
-      <c r="C129" s="8" t="n"/>
-      <c r="D129" s="8" t="n"/>
-      <c r="E129" s="8" t="n"/>
-      <c r="F129" s="8" t="n"/>
-      <c r="G129" s="8" t="n"/>
-      <c r="H129" s="8" t="n"/>
-      <c r="I129" s="8" t="n"/>
-      <c r="J129" s="24" t="n"/>
-      <c r="K129" s="8" t="n"/>
-      <c r="L129" s="8" t="n"/>
-      <c r="M129" s="8" t="n"/>
-      <c r="N129" s="8" t="n"/>
-      <c r="O129" s="25" t="n"/>
-      <c r="P129" s="25" t="n"/>
-      <c r="Q129" s="25" t="n"/>
-      <c r="R129" s="8" t="n"/>
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>C1-128</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G129" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J129" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K129" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L129" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M129" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N129" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O129" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P129" s="25" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="Q129" s="25" t="n">
+        <v>0.6707</v>
+      </c>
+      <c r="R129" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="19">
-      <c r="A130" s="8" t="n"/>
-      <c r="B130" s="23" t="n"/>
-      <c r="C130" s="8" t="n"/>
-      <c r="D130" s="8" t="n"/>
-      <c r="E130" s="8" t="n"/>
-      <c r="F130" s="8" t="n"/>
-      <c r="G130" s="8" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="8" t="n"/>
-      <c r="J130" s="24" t="n"/>
-      <c r="K130" s="8" t="n"/>
-      <c r="L130" s="8" t="n"/>
-      <c r="M130" s="8" t="n"/>
-      <c r="N130" s="8" t="n"/>
-      <c r="O130" s="25" t="n"/>
-      <c r="P130" s="25" t="n"/>
-      <c r="Q130" s="25" t="n"/>
-      <c r="R130" s="8" t="n"/>
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>C1-129</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G130" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J130" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K130" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L130" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M130" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N130" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O130" s="25" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="P130" s="25" t="n">
+        <v>0.6196</v>
+      </c>
+      <c r="Q130" s="25" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="R130" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="19">
-      <c r="A131" s="8" t="n"/>
-      <c r="B131" s="23" t="n"/>
-      <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
-      <c r="E131" s="8" t="n"/>
-      <c r="F131" s="8" t="n"/>
-      <c r="G131" s="8" t="n"/>
-      <c r="H131" s="8" t="n"/>
-      <c r="I131" s="8" t="n"/>
-      <c r="J131" s="24" t="n"/>
-      <c r="K131" s="8" t="n"/>
-      <c r="L131" s="8" t="n"/>
-      <c r="M131" s="8" t="n"/>
-      <c r="N131" s="8" t="n"/>
-      <c r="O131" s="25" t="n"/>
-      <c r="P131" s="25" t="n"/>
-      <c r="Q131" s="25" t="n"/>
-      <c r="R131" s="8" t="n"/>
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>C1-130</t>
+        </is>
+      </c>
+      <c r="B131" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G131" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I131" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J131" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K131" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L131" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M131" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N131" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O131" s="25" t="n">
+        <v>0.7696</v>
+      </c>
+      <c r="P131" s="25" t="n">
+        <v>0.6391</v>
+      </c>
+      <c r="Q131" s="25" t="n">
+        <v>0.6793</v>
+      </c>
+      <c r="R131" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="19">
-      <c r="A132" s="8" t="n"/>
-      <c r="B132" s="23" t="n"/>
-      <c r="C132" s="8" t="n"/>
-      <c r="D132" s="8" t="n"/>
-      <c r="E132" s="8" t="n"/>
-      <c r="F132" s="8" t="n"/>
-      <c r="G132" s="8" t="n"/>
-      <c r="H132" s="8" t="n"/>
-      <c r="I132" s="8" t="n"/>
-      <c r="J132" s="24" t="n"/>
-      <c r="K132" s="8" t="n"/>
-      <c r="L132" s="8" t="n"/>
-      <c r="M132" s="8" t="n"/>
-      <c r="N132" s="8" t="n"/>
-      <c r="O132" s="25" t="n"/>
-      <c r="P132" s="25" t="n"/>
-      <c r="Q132" s="25" t="n"/>
-      <c r="R132" s="8" t="n"/>
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>C1-131</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G132" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J132" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K132" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L132" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M132" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N132" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O132" s="25" t="n">
+        <v>0.7539</v>
+      </c>
+      <c r="P132" s="25" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="Q132" s="25" t="n">
+        <v>0.6838</v>
+      </c>
+      <c r="R132" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="19">
-      <c r="A133" s="8" t="n"/>
-      <c r="B133" s="23" t="n"/>
-      <c r="C133" s="8" t="n"/>
-      <c r="D133" s="8" t="n"/>
-      <c r="E133" s="8" t="n"/>
-      <c r="F133" s="8" t="n"/>
-      <c r="G133" s="8" t="n"/>
-      <c r="H133" s="8" t="n"/>
-      <c r="I133" s="8" t="n"/>
-      <c r="J133" s="24" t="n"/>
-      <c r="K133" s="8" t="n"/>
-      <c r="L133" s="8" t="n"/>
-      <c r="M133" s="8" t="n"/>
-      <c r="N133" s="8" t="n"/>
-      <c r="O133" s="25" t="n"/>
-      <c r="P133" s="25" t="n"/>
-      <c r="Q133" s="25" t="n"/>
-      <c r="R133" s="8" t="n"/>
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>C1-132</t>
+        </is>
+      </c>
+      <c r="B133" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G133" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J133" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K133" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L133" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M133" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N133" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O133" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P133" s="25" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="Q133" s="25" t="n">
+        <v>0.6706</v>
+      </c>
+      <c r="R133" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="19">
-      <c r="A134" s="8" t="n"/>
-      <c r="B134" s="23" t="n"/>
-      <c r="C134" s="8" t="n"/>
-      <c r="D134" s="8" t="n"/>
-      <c r="E134" s="8" t="n"/>
-      <c r="F134" s="8" t="n"/>
-      <c r="G134" s="8" t="n"/>
-      <c r="H134" s="8" t="n"/>
-      <c r="I134" s="8" t="n"/>
-      <c r="J134" s="24" t="n"/>
-      <c r="K134" s="8" t="n"/>
-      <c r="L134" s="8" t="n"/>
-      <c r="M134" s="8" t="n"/>
-      <c r="N134" s="8" t="n"/>
-      <c r="O134" s="25" t="n"/>
-      <c r="P134" s="25" t="n"/>
-      <c r="Q134" s="25" t="n"/>
-      <c r="R134" s="8" t="n"/>
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>C1-133</t>
+        </is>
+      </c>
+      <c r="B134" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G134" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J134" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K134" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L134" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M134" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N134" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O134" s="25" t="n">
+        <v>0.7749</v>
+      </c>
+      <c r="P134" s="25" t="n">
+        <v>0.6258</v>
+      </c>
+      <c r="Q134" s="25" t="n">
+        <v>0.6804</v>
+      </c>
+      <c r="R134" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="19">
-      <c r="A135" s="8" t="n"/>
-      <c r="B135" s="23" t="n"/>
-      <c r="C135" s="8" t="n"/>
-      <c r="D135" s="8" t="n"/>
-      <c r="E135" s="8" t="n"/>
-      <c r="F135" s="8" t="n"/>
-      <c r="G135" s="8" t="n"/>
-      <c r="H135" s="8" t="n"/>
-      <c r="I135" s="8" t="n"/>
-      <c r="J135" s="24" t="n"/>
-      <c r="K135" s="8" t="n"/>
-      <c r="L135" s="8" t="n"/>
-      <c r="M135" s="8" t="n"/>
-      <c r="N135" s="8" t="n"/>
-      <c r="O135" s="25" t="n"/>
-      <c r="P135" s="25" t="n"/>
-      <c r="Q135" s="25" t="n"/>
-      <c r="R135" s="8" t="n"/>
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>C1-134</t>
+        </is>
+      </c>
+      <c r="B135" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G135" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J135" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K135" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L135" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M135" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N135" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O135" s="25" t="n">
+        <v>0.7592</v>
+      </c>
+      <c r="P135" s="25" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="Q135" s="25" t="n">
+        <v>0.6822</v>
+      </c>
+      <c r="R135" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="19">
-      <c r="A136" s="8" t="n"/>
-      <c r="B136" s="23" t="n"/>
-      <c r="C136" s="8" t="n"/>
-      <c r="D136" s="8" t="n"/>
-      <c r="E136" s="8" t="n"/>
-      <c r="F136" s="8" t="n"/>
-      <c r="G136" s="8" t="n"/>
-      <c r="H136" s="8" t="n"/>
-      <c r="I136" s="8" t="n"/>
-      <c r="J136" s="24" t="n"/>
-      <c r="K136" s="8" t="n"/>
-      <c r="L136" s="8" t="n"/>
-      <c r="M136" s="8" t="n"/>
-      <c r="N136" s="8" t="n"/>
-      <c r="O136" s="25" t="n"/>
-      <c r="P136" s="25" t="n"/>
-      <c r="Q136" s="25" t="n"/>
-      <c r="R136" s="8" t="n"/>
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>C1-135</t>
+        </is>
+      </c>
+      <c r="B136" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G136" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J136" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K136" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L136" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M136" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N136" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O136" s="25" t="n">
+        <v>0.7644</v>
+      </c>
+      <c r="P136" s="25" t="n">
+        <v>0.6253</v>
+      </c>
+      <c r="Q136" s="25" t="n">
+        <v>0.6936</v>
+      </c>
+      <c r="R136" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="19">
-      <c r="A137" s="8" t="n"/>
-      <c r="B137" s="23" t="n"/>
-      <c r="C137" s="8" t="n"/>
-      <c r="D137" s="8" t="n"/>
-      <c r="E137" s="8" t="n"/>
-      <c r="F137" s="8" t="n"/>
-      <c r="G137" s="8" t="n"/>
-      <c r="H137" s="8" t="n"/>
-      <c r="I137" s="8" t="n"/>
-      <c r="J137" s="24" t="n"/>
-      <c r="K137" s="8" t="n"/>
-      <c r="L137" s="8" t="n"/>
-      <c r="M137" s="8" t="n"/>
-      <c r="N137" s="8" t="n"/>
-      <c r="O137" s="25" t="n"/>
-      <c r="P137" s="25" t="n"/>
-      <c r="Q137" s="25" t="n"/>
-      <c r="R137" s="8" t="n"/>
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>C1-136</t>
+        </is>
+      </c>
+      <c r="B137" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G137" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J137" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K137" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L137" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M137" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N137" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O137" s="25" t="n">
+        <v>0.7696</v>
+      </c>
+      <c r="P137" s="25" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="Q137" s="25" t="n">
+        <v>0.6798999999999999</v>
+      </c>
+      <c r="R137" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="19">
-      <c r="A138" s="8" t="n"/>
-      <c r="B138" s="23" t="n"/>
-      <c r="C138" s="8" t="n"/>
-      <c r="D138" s="8" t="n"/>
-      <c r="E138" s="8" t="n"/>
-      <c r="F138" s="8" t="n"/>
-      <c r="G138" s="8" t="n"/>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="8" t="n"/>
-      <c r="J138" s="24" t="n"/>
-      <c r="K138" s="8" t="n"/>
-      <c r="L138" s="8" t="n"/>
-      <c r="M138" s="8" t="n"/>
-      <c r="N138" s="8" t="n"/>
-      <c r="O138" s="25" t="n"/>
-      <c r="P138" s="25" t="n"/>
-      <c r="Q138" s="25" t="n"/>
-      <c r="R138" s="8" t="n"/>
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>C1-137</t>
+        </is>
+      </c>
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G138" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J138" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K138" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L138" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M138" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N138" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O138" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P138" s="25" t="n">
+        <v>0.6333</v>
+      </c>
+      <c r="Q138" s="25" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="R138" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="19">
-      <c r="A139" s="8" t="n"/>
-      <c r="B139" s="23" t="n"/>
-      <c r="C139" s="8" t="n"/>
-      <c r="D139" s="8" t="n"/>
-      <c r="E139" s="8" t="n"/>
-      <c r="F139" s="8" t="n"/>
-      <c r="G139" s="8" t="n"/>
-      <c r="H139" s="8" t="n"/>
-      <c r="I139" s="8" t="n"/>
-      <c r="J139" s="24" t="n"/>
-      <c r="K139" s="8" t="n"/>
-      <c r="L139" s="8" t="n"/>
-      <c r="M139" s="8" t="n"/>
-      <c r="N139" s="8" t="n"/>
-      <c r="O139" s="25" t="n"/>
-      <c r="P139" s="25" t="n"/>
-      <c r="Q139" s="25" t="n"/>
-      <c r="R139" s="8" t="n"/>
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>C1-138</t>
+        </is>
+      </c>
+      <c r="B139" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J139" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K139" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L139" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M139" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N139" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O139" s="25" t="n">
+        <v>0.7853</v>
+      </c>
+      <c r="P139" s="25" t="n">
+        <v>0.6276</v>
+      </c>
+      <c r="Q139" s="25" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="R139" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="19">
-      <c r="A140" s="8" t="n"/>
-      <c r="B140" s="23" t="n"/>
-      <c r="C140" s="8" t="n"/>
-      <c r="D140" s="8" t="n"/>
-      <c r="E140" s="8" t="n"/>
-      <c r="F140" s="8" t="n"/>
-      <c r="G140" s="8" t="n"/>
-      <c r="H140" s="8" t="n"/>
-      <c r="I140" s="8" t="n"/>
-      <c r="J140" s="24" t="n"/>
-      <c r="K140" s="8" t="n"/>
-      <c r="L140" s="8" t="n"/>
-      <c r="M140" s="8" t="n"/>
-      <c r="N140" s="8" t="n"/>
-      <c r="O140" s="25" t="n"/>
-      <c r="P140" s="25" t="n"/>
-      <c r="Q140" s="25" t="n"/>
-      <c r="R140" s="8" t="n"/>
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>C1-139</t>
+        </is>
+      </c>
+      <c r="B140" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G140" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H140" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J140" s="24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K140" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L140" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M140" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N140" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O140" s="25" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="P140" s="25" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+      <c r="Q140" s="25" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="R140" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 D, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="19">
-      <c r="A141" s="8" t="n"/>
-      <c r="B141" s="23" t="n"/>
-      <c r="C141" s="8" t="n"/>
-      <c r="D141" s="8" t="n"/>
-      <c r="E141" s="8" t="n"/>
-      <c r="F141" s="8" t="n"/>
-      <c r="G141" s="8" t="n"/>
-      <c r="H141" s="8" t="n"/>
-      <c r="I141" s="8" t="n"/>
-      <c r="J141" s="24" t="n"/>
-      <c r="K141" s="8" t="n"/>
-      <c r="L141" s="8" t="n"/>
-      <c r="M141" s="8" t="n"/>
-      <c r="N141" s="8" t="n"/>
-      <c r="O141" s="25" t="n"/>
-      <c r="P141" s="25" t="n"/>
-      <c r="Q141" s="25" t="n"/>
-      <c r="R141" s="8" t="n"/>
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>C1-140</t>
+        </is>
+      </c>
+      <c r="B141" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G141" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J141" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K141" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L141" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M141" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N141" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O141" s="25" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="P141" s="25" t="n">
+        <v>0.5896</v>
+      </c>
+      <c r="Q141" s="25" t="n">
+        <v>0.6674</v>
+      </c>
+      <c r="R141" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="19">
-      <c r="A142" s="8" t="n"/>
-      <c r="B142" s="23" t="n"/>
-      <c r="C142" s="8" t="n"/>
-      <c r="D142" s="8" t="n"/>
-      <c r="E142" s="8" t="n"/>
-      <c r="F142" s="8" t="n"/>
-      <c r="G142" s="8" t="n"/>
-      <c r="H142" s="8" t="n"/>
-      <c r="I142" s="8" t="n"/>
-      <c r="J142" s="24" t="n"/>
-      <c r="K142" s="8" t="n"/>
-      <c r="L142" s="8" t="n"/>
-      <c r="M142" s="8" t="n"/>
-      <c r="N142" s="8" t="n"/>
-      <c r="O142" s="25" t="n"/>
-      <c r="P142" s="25" t="n"/>
-      <c r="Q142" s="25" t="n"/>
-      <c r="R142" s="8" t="n"/>
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>C1-141</t>
+        </is>
+      </c>
+      <c r="B142" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G142" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J142" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K142" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L142" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M142" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N142" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O142" s="25" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="P142" s="25" t="n">
+        <v>0.5936</v>
+      </c>
+      <c r="Q142" s="25" t="n">
+        <v>0.6677999999999999</v>
+      </c>
+      <c r="R142" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="19">
-      <c r="A143" s="8" t="n"/>
-      <c r="B143" s="23" t="n"/>
-      <c r="C143" s="8" t="n"/>
-      <c r="D143" s="8" t="n"/>
-      <c r="E143" s="8" t="n"/>
-      <c r="F143" s="8" t="n"/>
-      <c r="G143" s="8" t="n"/>
-      <c r="H143" s="8" t="n"/>
-      <c r="I143" s="8" t="n"/>
-      <c r="J143" s="24" t="n"/>
-      <c r="K143" s="8" t="n"/>
-      <c r="L143" s="8" t="n"/>
-      <c r="M143" s="8" t="n"/>
-      <c r="N143" s="8" t="n"/>
-      <c r="O143" s="25" t="n"/>
-      <c r="P143" s="25" t="n"/>
-      <c r="Q143" s="25" t="n"/>
-      <c r="R143" s="8" t="n"/>
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>C1-142</t>
+        </is>
+      </c>
+      <c r="B143" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G143" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J143" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K143" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L143" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M143" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N143" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O143" s="25" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="P143" s="25" t="n">
+        <v>0.5779</v>
+      </c>
+      <c r="Q143" s="25" t="n">
+        <v>0.6694</v>
+      </c>
+      <c r="R143" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="19">
-      <c r="A144" s="8" t="n"/>
-      <c r="B144" s="23" t="n"/>
-      <c r="C144" s="8" t="n"/>
-      <c r="D144" s="8" t="n"/>
-      <c r="E144" s="8" t="n"/>
-      <c r="F144" s="8" t="n"/>
-      <c r="G144" s="8" t="n"/>
-      <c r="H144" s="8" t="n"/>
-      <c r="I144" s="8" t="n"/>
-      <c r="J144" s="24" t="n"/>
-      <c r="K144" s="8" t="n"/>
-      <c r="L144" s="8" t="n"/>
-      <c r="M144" s="8" t="n"/>
-      <c r="N144" s="8" t="n"/>
-      <c r="O144" s="25" t="n"/>
-      <c r="P144" s="25" t="n"/>
-      <c r="Q144" s="25" t="n"/>
-      <c r="R144" s="8" t="n"/>
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>C1-143</t>
+        </is>
+      </c>
+      <c r="B144" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G144" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J144" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K144" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L144" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M144" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N144" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O144" s="25" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="P144" s="25" t="n">
+        <v>0.5698</v>
+      </c>
+      <c r="Q144" s="25" t="n">
+        <v>0.6559</v>
+      </c>
+      <c r="R144" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="19">
-      <c r="A145" s="8" t="n"/>
-      <c r="B145" s="23" t="n"/>
-      <c r="C145" s="8" t="n"/>
-      <c r="D145" s="8" t="n"/>
-      <c r="E145" s="8" t="n"/>
-      <c r="F145" s="8" t="n"/>
-      <c r="G145" s="8" t="n"/>
-      <c r="H145" s="8" t="n"/>
-      <c r="I145" s="8" t="n"/>
-      <c r="J145" s="24" t="n"/>
-      <c r="K145" s="8" t="n"/>
-      <c r="L145" s="8" t="n"/>
-      <c r="M145" s="8" t="n"/>
-      <c r="N145" s="8" t="n"/>
-      <c r="O145" s="25" t="n"/>
-      <c r="P145" s="25" t="n"/>
-      <c r="Q145" s="25" t="n"/>
-      <c r="R145" s="8" t="n"/>
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>C1-144</t>
+        </is>
+      </c>
+      <c r="B145" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G145" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J145" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K145" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L145" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M145" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N145" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O145" s="25" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="P145" s="25" t="n">
+        <v>0.5836</v>
+      </c>
+      <c r="Q145" s="25" t="n">
+        <v>0.6595</v>
+      </c>
+      <c r="R145" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.0</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15" customHeight="1" s="19">
-      <c r="A146" s="8" t="n"/>
-      <c r="B146" s="23" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="8" t="n"/>
-      <c r="F146" s="8" t="n"/>
-      <c r="G146" s="8" t="n"/>
-      <c r="H146" s="8" t="n"/>
-      <c r="I146" s="8" t="n"/>
-      <c r="J146" s="24" t="n"/>
-      <c r="K146" s="8" t="n"/>
-      <c r="L146" s="8" t="n"/>
-      <c r="M146" s="8" t="n"/>
-      <c r="N146" s="8" t="n"/>
-      <c r="O146" s="25" t="n"/>
-      <c r="P146" s="25" t="n"/>
-      <c r="Q146" s="25" t="n"/>
-      <c r="R146" s="8" t="n"/>
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>C1-145</t>
+        </is>
+      </c>
+      <c r="B146" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G146" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J146" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K146" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L146" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M146" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N146" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O146" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P146" s="25" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="Q146" s="25" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="R146" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="19">
-      <c r="A147" s="8" t="n"/>
-      <c r="B147" s="23" t="n"/>
-      <c r="C147" s="8" t="n"/>
-      <c r="D147" s="8" t="n"/>
-      <c r="E147" s="8" t="n"/>
-      <c r="F147" s="8" t="n"/>
-      <c r="G147" s="8" t="n"/>
-      <c r="H147" s="8" t="n"/>
-      <c r="I147" s="8" t="n"/>
-      <c r="J147" s="24" t="n"/>
-      <c r="K147" s="8" t="n"/>
-      <c r="L147" s="8" t="n"/>
-      <c r="M147" s="8" t="n"/>
-      <c r="N147" s="8" t="n"/>
-      <c r="O147" s="25" t="n"/>
-      <c r="P147" s="25" t="n"/>
-      <c r="Q147" s="25" t="n"/>
-      <c r="R147" s="8" t="n"/>
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>C1-146</t>
+        </is>
+      </c>
+      <c r="B147" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G147" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I147" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J147" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K147" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L147" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M147" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N147" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O147" s="25" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="P147" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q147" s="25" t="n">
+        <v>0.6977</v>
+      </c>
+      <c r="R147" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="19">
-      <c r="A148" s="8" t="n"/>
-      <c r="B148" s="23" t="n"/>
-      <c r="C148" s="8" t="n"/>
-      <c r="D148" s="8" t="n"/>
-      <c r="E148" s="8" t="n"/>
-      <c r="F148" s="8" t="n"/>
-      <c r="G148" s="8" t="n"/>
-      <c r="H148" s="8" t="n"/>
-      <c r="I148" s="8" t="n"/>
-      <c r="J148" s="24" t="n"/>
-      <c r="K148" s="8" t="n"/>
-      <c r="L148" s="8" t="n"/>
-      <c r="M148" s="8" t="n"/>
-      <c r="N148" s="8" t="n"/>
-      <c r="O148" s="25" t="n"/>
-      <c r="P148" s="25" t="n"/>
-      <c r="Q148" s="25" t="n"/>
-      <c r="R148" s="8" t="n"/>
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>C1-147</t>
+        </is>
+      </c>
+      <c r="B148" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G148" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J148" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K148" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L148" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M148" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N148" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O148" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P148" s="25" t="n">
+        <v>0.5916</v>
+      </c>
+      <c r="Q148" s="25" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="R148" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="19">
-      <c r="A149" s="8" t="n"/>
-      <c r="B149" s="23" t="n"/>
-      <c r="C149" s="8" t="n"/>
-      <c r="D149" s="8" t="n"/>
-      <c r="E149" s="8" t="n"/>
-      <c r="F149" s="8" t="n"/>
-      <c r="G149" s="8" t="n"/>
-      <c r="H149" s="8" t="n"/>
-      <c r="I149" s="8" t="n"/>
-      <c r="J149" s="24" t="n"/>
-      <c r="K149" s="8" t="n"/>
-      <c r="L149" s="8" t="n"/>
-      <c r="M149" s="8" t="n"/>
-      <c r="N149" s="8" t="n"/>
-      <c r="O149" s="25" t="n"/>
-      <c r="P149" s="25" t="n"/>
-      <c r="Q149" s="25" t="n"/>
-      <c r="R149" s="8" t="n"/>
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>C1-148</t>
+        </is>
+      </c>
+      <c r="B149" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G149" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J149" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K149" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L149" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M149" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N149" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O149" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P149" s="25" t="n">
+        <v>0.5939</v>
+      </c>
+      <c r="Q149" s="25" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="R149" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="19">
-      <c r="A150" s="8" t="n"/>
-      <c r="B150" s="23" t="n"/>
-      <c r="C150" s="8" t="n"/>
-      <c r="D150" s="8" t="n"/>
-      <c r="E150" s="8" t="n"/>
-      <c r="F150" s="8" t="n"/>
-      <c r="G150" s="8" t="n"/>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="8" t="n"/>
-      <c r="J150" s="24" t="n"/>
-      <c r="K150" s="8" t="n"/>
-      <c r="L150" s="8" t="n"/>
-      <c r="M150" s="8" t="n"/>
-      <c r="N150" s="8" t="n"/>
-      <c r="O150" s="25" t="n"/>
-      <c r="P150" s="25" t="n"/>
-      <c r="Q150" s="25" t="n"/>
-      <c r="R150" s="8" t="n"/>
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>C1-149</t>
+        </is>
+      </c>
+      <c r="B150" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G150" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J150" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K150" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L150" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M150" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N150" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O150" s="25" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="P150" s="25" t="n">
+        <v>0.5988</v>
+      </c>
+      <c r="Q150" s="25" t="n">
+        <v>0.6926</v>
+      </c>
+      <c r="R150" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.2</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="19">
-      <c r="A151" s="8" t="n"/>
-      <c r="B151" s="23" t="n"/>
-      <c r="C151" s="8" t="n"/>
-      <c r="D151" s="8" t="n"/>
-      <c r="E151" s="8" t="n"/>
-      <c r="F151" s="8" t="n"/>
-      <c r="G151" s="8" t="n"/>
-      <c r="H151" s="8" t="n"/>
-      <c r="I151" s="8" t="n"/>
-      <c r="J151" s="24" t="n"/>
-      <c r="K151" s="8" t="n"/>
-      <c r="L151" s="8" t="n"/>
-      <c r="M151" s="8" t="n"/>
-      <c r="N151" s="8" t="n"/>
-      <c r="O151" s="25" t="n"/>
-      <c r="P151" s="25" t="n"/>
-      <c r="Q151" s="25" t="n"/>
-      <c r="R151" s="8" t="n"/>
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>C1-150</t>
+        </is>
+      </c>
+      <c r="B151" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G151" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H151" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I151" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J151" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K151" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L151" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M151" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N151" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O151" s="25" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="P151" s="25" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="Q151" s="25" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="R151" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="19">
-      <c r="A152" s="8" t="n"/>
-      <c r="B152" s="23" t="n"/>
-      <c r="C152" s="8" t="n"/>
-      <c r="D152" s="8" t="n"/>
-      <c r="E152" s="8" t="n"/>
-      <c r="F152" s="8" t="n"/>
-      <c r="G152" s="8" t="n"/>
-      <c r="H152" s="8" t="n"/>
-      <c r="I152" s="8" t="n"/>
-      <c r="J152" s="24" t="n"/>
-      <c r="K152" s="8" t="n"/>
-      <c r="L152" s="8" t="n"/>
-      <c r="M152" s="8" t="n"/>
-      <c r="N152" s="8" t="n"/>
-      <c r="O152" s="25" t="n"/>
-      <c r="P152" s="25" t="n"/>
-      <c r="Q152" s="25" t="n"/>
-      <c r="R152" s="8" t="n"/>
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t>C1-151</t>
+        </is>
+      </c>
+      <c r="B152" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G152" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J152" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K152" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L152" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M152" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N152" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O152" s="25" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="P152" s="25" t="n">
+        <v>0.5973000000000001</v>
+      </c>
+      <c r="Q152" s="25" t="n">
+        <v>0.6928</v>
+      </c>
+      <c r="R152" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="19">
-      <c r="A153" s="8" t="n"/>
-      <c r="B153" s="23" t="n"/>
-      <c r="C153" s="8" t="n"/>
-      <c r="D153" s="8" t="n"/>
-      <c r="E153" s="8" t="n"/>
-      <c r="F153" s="8" t="n"/>
-      <c r="G153" s="8" t="n"/>
-      <c r="H153" s="8" t="n"/>
-      <c r="I153" s="8" t="n"/>
-      <c r="J153" s="24" t="n"/>
-      <c r="K153" s="8" t="n"/>
-      <c r="L153" s="8" t="n"/>
-      <c r="M153" s="8" t="n"/>
-      <c r="N153" s="8" t="n"/>
-      <c r="O153" s="25" t="n"/>
-      <c r="P153" s="25" t="n"/>
-      <c r="Q153" s="25" t="n"/>
-      <c r="R153" s="8" t="n"/>
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>C1-152</t>
+        </is>
+      </c>
+      <c r="B153" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G153" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J153" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K153" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L153" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M153" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N153" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O153" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P153" s="25" t="n">
+        <v>0.6016</v>
+      </c>
+      <c r="Q153" s="25" t="n">
+        <v>0.7040999999999999</v>
+      </c>
+      <c r="R153" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="19">
-      <c r="A154" s="8" t="n"/>
-      <c r="B154" s="23" t="n"/>
-      <c r="C154" s="8" t="n"/>
-      <c r="D154" s="8" t="n"/>
-      <c r="E154" s="8" t="n"/>
-      <c r="F154" s="8" t="n"/>
-      <c r="G154" s="8" t="n"/>
-      <c r="H154" s="8" t="n"/>
-      <c r="I154" s="8" t="n"/>
-      <c r="J154" s="24" t="n"/>
-      <c r="K154" s="8" t="n"/>
-      <c r="L154" s="8" t="n"/>
-      <c r="M154" s="8" t="n"/>
-      <c r="N154" s="8" t="n"/>
-      <c r="O154" s="25" t="n"/>
-      <c r="P154" s="25" t="n"/>
-      <c r="Q154" s="25" t="n"/>
-      <c r="R154" s="8" t="n"/>
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>C1-153</t>
+        </is>
+      </c>
+      <c r="B154" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G154" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I154" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J154" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K154" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L154" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M154" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N154" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O154" s="25" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="P154" s="25" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="Q154" s="25" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="R154" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="19">
-      <c r="A155" s="8" t="n"/>
-      <c r="B155" s="23" t="n"/>
-      <c r="C155" s="8" t="n"/>
-      <c r="D155" s="8" t="n"/>
-      <c r="E155" s="8" t="n"/>
-      <c r="F155" s="8" t="n"/>
-      <c r="G155" s="8" t="n"/>
-      <c r="H155" s="8" t="n"/>
-      <c r="I155" s="8" t="n"/>
-      <c r="J155" s="24" t="n"/>
-      <c r="K155" s="8" t="n"/>
-      <c r="L155" s="8" t="n"/>
-      <c r="M155" s="8" t="n"/>
-      <c r="N155" s="8" t="n"/>
-      <c r="O155" s="25" t="n"/>
-      <c r="P155" s="25" t="n"/>
-      <c r="Q155" s="25" t="n"/>
-      <c r="R155" s="8" t="n"/>
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>C1-154</t>
+        </is>
+      </c>
+      <c r="B155" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>재검증</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>tensorflow(keras) 2.22.0-rc0</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>official_v1(data/final, Month·VisitorType 원핫, 26차원)</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G155" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J155" s="24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K155" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L155" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M155" s="8" t="inlineStr">
+        <is>
+          <t>val_pr_auc, patience=5, mode=max, restore_best=True</t>
+        </is>
+      </c>
+      <c r="N155" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="O155" s="25" t="n">
+        <v>0.8063</v>
+      </c>
+      <c r="P155" s="25" t="n">
+        <v>0.6123</v>
+      </c>
+      <c r="Q155" s="25" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="R155" s="8" t="inlineStr">
+        <is>
+          <t>공식 분할 기준, 재검증 E, dropout=0.3</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="19">
       <c r="A156" s="8" t="n"/>
@@ -22001,2966 +25901,154 @@
       <c r="Q852" s="25" t="n"/>
       <c r="R852" s="8" t="n"/>
     </row>
-    <row r="853" ht="15" customHeight="1" s="19">
-      <c r="A853" s="8" t="n"/>
-      <c r="B853" s="23" t="n"/>
-      <c r="C853" s="8" t="n"/>
-      <c r="D853" s="8" t="n"/>
-      <c r="E853" s="8" t="n"/>
-      <c r="F853" s="8" t="n"/>
-      <c r="G853" s="8" t="n"/>
-      <c r="H853" s="8" t="n"/>
-      <c r="I853" s="8" t="n"/>
-      <c r="J853" s="24" t="n"/>
-      <c r="K853" s="8" t="n"/>
-      <c r="L853" s="8" t="n"/>
-      <c r="M853" s="8" t="n"/>
-      <c r="N853" s="8" t="n"/>
-      <c r="O853" s="25" t="n"/>
-      <c r="P853" s="25" t="n"/>
-      <c r="Q853" s="25" t="n"/>
-      <c r="R853" s="8" t="n"/>
-    </row>
-    <row r="854" ht="15" customHeight="1" s="19">
-      <c r="A854" s="8" t="n"/>
-      <c r="B854" s="23" t="n"/>
-      <c r="C854" s="8" t="n"/>
-      <c r="D854" s="8" t="n"/>
-      <c r="E854" s="8" t="n"/>
-      <c r="F854" s="8" t="n"/>
-      <c r="G854" s="8" t="n"/>
-      <c r="H854" s="8" t="n"/>
-      <c r="I854" s="8" t="n"/>
-      <c r="J854" s="24" t="n"/>
-      <c r="K854" s="8" t="n"/>
-      <c r="L854" s="8" t="n"/>
-      <c r="M854" s="8" t="n"/>
-      <c r="N854" s="8" t="n"/>
-      <c r="O854" s="25" t="n"/>
-      <c r="P854" s="25" t="n"/>
-      <c r="Q854" s="25" t="n"/>
-      <c r="R854" s="8" t="n"/>
-    </row>
-    <row r="855" ht="15" customHeight="1" s="19">
-      <c r="A855" s="8" t="n"/>
-      <c r="B855" s="23" t="n"/>
-      <c r="C855" s="8" t="n"/>
-      <c r="D855" s="8" t="n"/>
-      <c r="E855" s="8" t="n"/>
-      <c r="F855" s="8" t="n"/>
-      <c r="G855" s="8" t="n"/>
-      <c r="H855" s="8" t="n"/>
-      <c r="I855" s="8" t="n"/>
-      <c r="J855" s="24" t="n"/>
-      <c r="K855" s="8" t="n"/>
-      <c r="L855" s="8" t="n"/>
-      <c r="M855" s="8" t="n"/>
-      <c r="N855" s="8" t="n"/>
-      <c r="O855" s="25" t="n"/>
-      <c r="P855" s="25" t="n"/>
-      <c r="Q855" s="25" t="n"/>
-      <c r="R855" s="8" t="n"/>
-    </row>
-    <row r="856" ht="15" customHeight="1" s="19">
-      <c r="A856" s="8" t="n"/>
-      <c r="B856" s="23" t="n"/>
-      <c r="C856" s="8" t="n"/>
-      <c r="D856" s="8" t="n"/>
-      <c r="E856" s="8" t="n"/>
-      <c r="F856" s="8" t="n"/>
-      <c r="G856" s="8" t="n"/>
-      <c r="H856" s="8" t="n"/>
-      <c r="I856" s="8" t="n"/>
-      <c r="J856" s="24" t="n"/>
-      <c r="K856" s="8" t="n"/>
-      <c r="L856" s="8" t="n"/>
-      <c r="M856" s="8" t="n"/>
-      <c r="N856" s="8" t="n"/>
-      <c r="O856" s="25" t="n"/>
-      <c r="P856" s="25" t="n"/>
-      <c r="Q856" s="25" t="n"/>
-      <c r="R856" s="8" t="n"/>
-    </row>
-    <row r="857" ht="15" customHeight="1" s="19">
-      <c r="A857" s="8" t="n"/>
-      <c r="B857" s="23" t="n"/>
-      <c r="C857" s="8" t="n"/>
-      <c r="D857" s="8" t="n"/>
-      <c r="E857" s="8" t="n"/>
-      <c r="F857" s="8" t="n"/>
-      <c r="G857" s="8" t="n"/>
-      <c r="H857" s="8" t="n"/>
-      <c r="I857" s="8" t="n"/>
-      <c r="J857" s="24" t="n"/>
-      <c r="K857" s="8" t="n"/>
-      <c r="L857" s="8" t="n"/>
-      <c r="M857" s="8" t="n"/>
-      <c r="N857" s="8" t="n"/>
-      <c r="O857" s="25" t="n"/>
-      <c r="P857" s="25" t="n"/>
-      <c r="Q857" s="25" t="n"/>
-      <c r="R857" s="8" t="n"/>
-    </row>
-    <row r="858" ht="15" customHeight="1" s="19">
-      <c r="A858" s="8" t="n"/>
-      <c r="B858" s="23" t="n"/>
-      <c r="C858" s="8" t="n"/>
-      <c r="D858" s="8" t="n"/>
-      <c r="E858" s="8" t="n"/>
-      <c r="F858" s="8" t="n"/>
-      <c r="G858" s="8" t="n"/>
-      <c r="H858" s="8" t="n"/>
-      <c r="I858" s="8" t="n"/>
-      <c r="J858" s="24" t="n"/>
-      <c r="K858" s="8" t="n"/>
-      <c r="L858" s="8" t="n"/>
-      <c r="M858" s="8" t="n"/>
-      <c r="N858" s="8" t="n"/>
-      <c r="O858" s="25" t="n"/>
-      <c r="P858" s="25" t="n"/>
-      <c r="Q858" s="25" t="n"/>
-      <c r="R858" s="8" t="n"/>
-    </row>
-    <row r="859" ht="15" customHeight="1" s="19">
-      <c r="A859" s="8" t="n"/>
-      <c r="B859" s="23" t="n"/>
-      <c r="C859" s="8" t="n"/>
-      <c r="D859" s="8" t="n"/>
-      <c r="E859" s="8" t="n"/>
-      <c r="F859" s="8" t="n"/>
-      <c r="G859" s="8" t="n"/>
-      <c r="H859" s="8" t="n"/>
-      <c r="I859" s="8" t="n"/>
-      <c r="J859" s="24" t="n"/>
-      <c r="K859" s="8" t="n"/>
-      <c r="L859" s="8" t="n"/>
-      <c r="M859" s="8" t="n"/>
-      <c r="N859" s="8" t="n"/>
-      <c r="O859" s="25" t="n"/>
-      <c r="P859" s="25" t="n"/>
-      <c r="Q859" s="25" t="n"/>
-      <c r="R859" s="8" t="n"/>
-    </row>
-    <row r="860" ht="15" customHeight="1" s="19">
-      <c r="A860" s="8" t="n"/>
-      <c r="B860" s="23" t="n"/>
-      <c r="C860" s="8" t="n"/>
-      <c r="D860" s="8" t="n"/>
-      <c r="E860" s="8" t="n"/>
-      <c r="F860" s="8" t="n"/>
-      <c r="G860" s="8" t="n"/>
-      <c r="H860" s="8" t="n"/>
-      <c r="I860" s="8" t="n"/>
-      <c r="J860" s="24" t="n"/>
-      <c r="K860" s="8" t="n"/>
-      <c r="L860" s="8" t="n"/>
-      <c r="M860" s="8" t="n"/>
-      <c r="N860" s="8" t="n"/>
-      <c r="O860" s="25" t="n"/>
-      <c r="P860" s="25" t="n"/>
-      <c r="Q860" s="25" t="n"/>
-      <c r="R860" s="8" t="n"/>
-    </row>
-    <row r="861" ht="15" customHeight="1" s="19">
-      <c r="A861" s="8" t="n"/>
-      <c r="B861" s="23" t="n"/>
-      <c r="C861" s="8" t="n"/>
-      <c r="D861" s="8" t="n"/>
-      <c r="E861" s="8" t="n"/>
-      <c r="F861" s="8" t="n"/>
-      <c r="G861" s="8" t="n"/>
-      <c r="H861" s="8" t="n"/>
-      <c r="I861" s="8" t="n"/>
-      <c r="J861" s="24" t="n"/>
-      <c r="K861" s="8" t="n"/>
-      <c r="L861" s="8" t="n"/>
-      <c r="M861" s="8" t="n"/>
-      <c r="N861" s="8" t="n"/>
-      <c r="O861" s="25" t="n"/>
-      <c r="P861" s="25" t="n"/>
-      <c r="Q861" s="25" t="n"/>
-      <c r="R861" s="8" t="n"/>
-    </row>
-    <row r="862" ht="15" customHeight="1" s="19">
-      <c r="A862" s="8" t="n"/>
-      <c r="B862" s="23" t="n"/>
-      <c r="C862" s="8" t="n"/>
-      <c r="D862" s="8" t="n"/>
-      <c r="E862" s="8" t="n"/>
-      <c r="F862" s="8" t="n"/>
-      <c r="G862" s="8" t="n"/>
-      <c r="H862" s="8" t="n"/>
-      <c r="I862" s="8" t="n"/>
-      <c r="J862" s="24" t="n"/>
-      <c r="K862" s="8" t="n"/>
-      <c r="L862" s="8" t="n"/>
-      <c r="M862" s="8" t="n"/>
-      <c r="N862" s="8" t="n"/>
-      <c r="O862" s="25" t="n"/>
-      <c r="P862" s="25" t="n"/>
-      <c r="Q862" s="25" t="n"/>
-      <c r="R862" s="8" t="n"/>
-    </row>
-    <row r="863" ht="15" customHeight="1" s="19">
-      <c r="A863" s="8" t="n"/>
-      <c r="B863" s="23" t="n"/>
-      <c r="C863" s="8" t="n"/>
-      <c r="D863" s="8" t="n"/>
-      <c r="E863" s="8" t="n"/>
-      <c r="F863" s="8" t="n"/>
-      <c r="G863" s="8" t="n"/>
-      <c r="H863" s="8" t="n"/>
-      <c r="I863" s="8" t="n"/>
-      <c r="J863" s="24" t="n"/>
-      <c r="K863" s="8" t="n"/>
-      <c r="L863" s="8" t="n"/>
-      <c r="M863" s="8" t="n"/>
-      <c r="N863" s="8" t="n"/>
-      <c r="O863" s="25" t="n"/>
-      <c r="P863" s="25" t="n"/>
-      <c r="Q863" s="25" t="n"/>
-      <c r="R863" s="8" t="n"/>
-    </row>
-    <row r="864" ht="15" customHeight="1" s="19">
-      <c r="A864" s="8" t="n"/>
-      <c r="B864" s="23" t="n"/>
-      <c r="C864" s="8" t="n"/>
-      <c r="D864" s="8" t="n"/>
-      <c r="E864" s="8" t="n"/>
-      <c r="F864" s="8" t="n"/>
-      <c r="G864" s="8" t="n"/>
-      <c r="H864" s="8" t="n"/>
-      <c r="I864" s="8" t="n"/>
-      <c r="J864" s="24" t="n"/>
-      <c r="K864" s="8" t="n"/>
-      <c r="L864" s="8" t="n"/>
-      <c r="M864" s="8" t="n"/>
-      <c r="N864" s="8" t="n"/>
-      <c r="O864" s="25" t="n"/>
-      <c r="P864" s="25" t="n"/>
-      <c r="Q864" s="25" t="n"/>
-      <c r="R864" s="8" t="n"/>
-    </row>
-    <row r="865" ht="15" customHeight="1" s="19">
-      <c r="A865" s="8" t="n"/>
-      <c r="B865" s="23" t="n"/>
-      <c r="C865" s="8" t="n"/>
-      <c r="D865" s="8" t="n"/>
-      <c r="E865" s="8" t="n"/>
-      <c r="F865" s="8" t="n"/>
-      <c r="G865" s="8" t="n"/>
-      <c r="H865" s="8" t="n"/>
-      <c r="I865" s="8" t="n"/>
-      <c r="J865" s="24" t="n"/>
-      <c r="K865" s="8" t="n"/>
-      <c r="L865" s="8" t="n"/>
-      <c r="M865" s="8" t="n"/>
-      <c r="N865" s="8" t="n"/>
-      <c r="O865" s="25" t="n"/>
-      <c r="P865" s="25" t="n"/>
-      <c r="Q865" s="25" t="n"/>
-      <c r="R865" s="8" t="n"/>
-    </row>
-    <row r="866" ht="15" customHeight="1" s="19">
-      <c r="A866" s="8" t="n"/>
-      <c r="B866" s="23" t="n"/>
-      <c r="C866" s="8" t="n"/>
-      <c r="D866" s="8" t="n"/>
-      <c r="E866" s="8" t="n"/>
-      <c r="F866" s="8" t="n"/>
-      <c r="G866" s="8" t="n"/>
-      <c r="H866" s="8" t="n"/>
-      <c r="I866" s="8" t="n"/>
-      <c r="J866" s="24" t="n"/>
-      <c r="K866" s="8" t="n"/>
-      <c r="L866" s="8" t="n"/>
-      <c r="M866" s="8" t="n"/>
-      <c r="N866" s="8" t="n"/>
-      <c r="O866" s="25" t="n"/>
-      <c r="P866" s="25" t="n"/>
-      <c r="Q866" s="25" t="n"/>
-      <c r="R866" s="8" t="n"/>
-    </row>
-    <row r="867" ht="15" customHeight="1" s="19">
-      <c r="A867" s="8" t="n"/>
-      <c r="B867" s="23" t="n"/>
-      <c r="C867" s="8" t="n"/>
-      <c r="D867" s="8" t="n"/>
-      <c r="E867" s="8" t="n"/>
-      <c r="F867" s="8" t="n"/>
-      <c r="G867" s="8" t="n"/>
-      <c r="H867" s="8" t="n"/>
-      <c r="I867" s="8" t="n"/>
-      <c r="J867" s="24" t="n"/>
-      <c r="K867" s="8" t="n"/>
-      <c r="L867" s="8" t="n"/>
-      <c r="M867" s="8" t="n"/>
-      <c r="N867" s="8" t="n"/>
-      <c r="O867" s="25" t="n"/>
-      <c r="P867" s="25" t="n"/>
-      <c r="Q867" s="25" t="n"/>
-      <c r="R867" s="8" t="n"/>
-    </row>
-    <row r="868" ht="15" customHeight="1" s="19">
-      <c r="A868" s="8" t="n"/>
-      <c r="B868" s="23" t="n"/>
-      <c r="C868" s="8" t="n"/>
-      <c r="D868" s="8" t="n"/>
-      <c r="E868" s="8" t="n"/>
-      <c r="F868" s="8" t="n"/>
-      <c r="G868" s="8" t="n"/>
-      <c r="H868" s="8" t="n"/>
-      <c r="I868" s="8" t="n"/>
-      <c r="J868" s="24" t="n"/>
-      <c r="K868" s="8" t="n"/>
-      <c r="L868" s="8" t="n"/>
-      <c r="M868" s="8" t="n"/>
-      <c r="N868" s="8" t="n"/>
-      <c r="O868" s="25" t="n"/>
-      <c r="P868" s="25" t="n"/>
-      <c r="Q868" s="25" t="n"/>
-      <c r="R868" s="8" t="n"/>
-    </row>
-    <row r="869" ht="15" customHeight="1" s="19">
-      <c r="A869" s="8" t="n"/>
-      <c r="B869" s="23" t="n"/>
-      <c r="C869" s="8" t="n"/>
-      <c r="D869" s="8" t="n"/>
-      <c r="E869" s="8" t="n"/>
-      <c r="F869" s="8" t="n"/>
-      <c r="G869" s="8" t="n"/>
-      <c r="H869" s="8" t="n"/>
-      <c r="I869" s="8" t="n"/>
-      <c r="J869" s="24" t="n"/>
-      <c r="K869" s="8" t="n"/>
-      <c r="L869" s="8" t="n"/>
-      <c r="M869" s="8" t="n"/>
-      <c r="N869" s="8" t="n"/>
-      <c r="O869" s="25" t="n"/>
-      <c r="P869" s="25" t="n"/>
-      <c r="Q869" s="25" t="n"/>
-      <c r="R869" s="8" t="n"/>
-    </row>
-    <row r="870" ht="15" customHeight="1" s="19">
-      <c r="A870" s="8" t="n"/>
-      <c r="B870" s="23" t="n"/>
-      <c r="C870" s="8" t="n"/>
-      <c r="D870" s="8" t="n"/>
-      <c r="E870" s="8" t="n"/>
-      <c r="F870" s="8" t="n"/>
-      <c r="G870" s="8" t="n"/>
-      <c r="H870" s="8" t="n"/>
-      <c r="I870" s="8" t="n"/>
-      <c r="J870" s="24" t="n"/>
-      <c r="K870" s="8" t="n"/>
-      <c r="L870" s="8" t="n"/>
-      <c r="M870" s="8" t="n"/>
-      <c r="N870" s="8" t="n"/>
-      <c r="O870" s="25" t="n"/>
-      <c r="P870" s="25" t="n"/>
-      <c r="Q870" s="25" t="n"/>
-      <c r="R870" s="8" t="n"/>
-    </row>
-    <row r="871" ht="15" customHeight="1" s="19">
-      <c r="A871" s="8" t="n"/>
-      <c r="B871" s="23" t="n"/>
-      <c r="C871" s="8" t="n"/>
-      <c r="D871" s="8" t="n"/>
-      <c r="E871" s="8" t="n"/>
-      <c r="F871" s="8" t="n"/>
-      <c r="G871" s="8" t="n"/>
-      <c r="H871" s="8" t="n"/>
-      <c r="I871" s="8" t="n"/>
-      <c r="J871" s="24" t="n"/>
-      <c r="K871" s="8" t="n"/>
-      <c r="L871" s="8" t="n"/>
-      <c r="M871" s="8" t="n"/>
-      <c r="N871" s="8" t="n"/>
-      <c r="O871" s="25" t="n"/>
-      <c r="P871" s="25" t="n"/>
-      <c r="Q871" s="25" t="n"/>
-      <c r="R871" s="8" t="n"/>
-    </row>
-    <row r="872" ht="15" customHeight="1" s="19">
-      <c r="A872" s="8" t="n"/>
-      <c r="B872" s="23" t="n"/>
-      <c r="C872" s="8" t="n"/>
-      <c r="D872" s="8" t="n"/>
-      <c r="E872" s="8" t="n"/>
-      <c r="F872" s="8" t="n"/>
-      <c r="G872" s="8" t="n"/>
-      <c r="H872" s="8" t="n"/>
-      <c r="I872" s="8" t="n"/>
-      <c r="J872" s="24" t="n"/>
-      <c r="K872" s="8" t="n"/>
-      <c r="L872" s="8" t="n"/>
-      <c r="M872" s="8" t="n"/>
-      <c r="N872" s="8" t="n"/>
-      <c r="O872" s="25" t="n"/>
-      <c r="P872" s="25" t="n"/>
-      <c r="Q872" s="25" t="n"/>
-      <c r="R872" s="8" t="n"/>
-    </row>
-    <row r="873" ht="15" customHeight="1" s="19">
-      <c r="A873" s="8" t="n"/>
-      <c r="B873" s="23" t="n"/>
-      <c r="C873" s="8" t="n"/>
-      <c r="D873" s="8" t="n"/>
-      <c r="E873" s="8" t="n"/>
-      <c r="F873" s="8" t="n"/>
-      <c r="G873" s="8" t="n"/>
-      <c r="H873" s="8" t="n"/>
-      <c r="I873" s="8" t="n"/>
-      <c r="J873" s="24" t="n"/>
-      <c r="K873" s="8" t="n"/>
-      <c r="L873" s="8" t="n"/>
-      <c r="M873" s="8" t="n"/>
-      <c r="N873" s="8" t="n"/>
-      <c r="O873" s="25" t="n"/>
-      <c r="P873" s="25" t="n"/>
-      <c r="Q873" s="25" t="n"/>
-      <c r="R873" s="8" t="n"/>
-    </row>
-    <row r="874" ht="15" customHeight="1" s="19">
-      <c r="A874" s="8" t="n"/>
-      <c r="B874" s="23" t="n"/>
-      <c r="C874" s="8" t="n"/>
-      <c r="D874" s="8" t="n"/>
-      <c r="E874" s="8" t="n"/>
-      <c r="F874" s="8" t="n"/>
-      <c r="G874" s="8" t="n"/>
-      <c r="H874" s="8" t="n"/>
-      <c r="I874" s="8" t="n"/>
-      <c r="J874" s="24" t="n"/>
-      <c r="K874" s="8" t="n"/>
-      <c r="L874" s="8" t="n"/>
-      <c r="M874" s="8" t="n"/>
-      <c r="N874" s="8" t="n"/>
-      <c r="O874" s="25" t="n"/>
-      <c r="P874" s="25" t="n"/>
-      <c r="Q874" s="25" t="n"/>
-      <c r="R874" s="8" t="n"/>
-    </row>
-    <row r="875" ht="15" customHeight="1" s="19">
-      <c r="A875" s="8" t="n"/>
-      <c r="B875" s="23" t="n"/>
-      <c r="C875" s="8" t="n"/>
-      <c r="D875" s="8" t="n"/>
-      <c r="E875" s="8" t="n"/>
-      <c r="F875" s="8" t="n"/>
-      <c r="G875" s="8" t="n"/>
-      <c r="H875" s="8" t="n"/>
-      <c r="I875" s="8" t="n"/>
-      <c r="J875" s="24" t="n"/>
-      <c r="K875" s="8" t="n"/>
-      <c r="L875" s="8" t="n"/>
-      <c r="M875" s="8" t="n"/>
-      <c r="N875" s="8" t="n"/>
-      <c r="O875" s="25" t="n"/>
-      <c r="P875" s="25" t="n"/>
-      <c r="Q875" s="25" t="n"/>
-      <c r="R875" s="8" t="n"/>
-    </row>
-    <row r="876" ht="15" customHeight="1" s="19">
-      <c r="A876" s="8" t="n"/>
-      <c r="B876" s="23" t="n"/>
-      <c r="C876" s="8" t="n"/>
-      <c r="D876" s="8" t="n"/>
-      <c r="E876" s="8" t="n"/>
-      <c r="F876" s="8" t="n"/>
-      <c r="G876" s="8" t="n"/>
-      <c r="H876" s="8" t="n"/>
-      <c r="I876" s="8" t="n"/>
-      <c r="J876" s="24" t="n"/>
-      <c r="K876" s="8" t="n"/>
-      <c r="L876" s="8" t="n"/>
-      <c r="M876" s="8" t="n"/>
-      <c r="N876" s="8" t="n"/>
-      <c r="O876" s="25" t="n"/>
-      <c r="P876" s="25" t="n"/>
-      <c r="Q876" s="25" t="n"/>
-      <c r="R876" s="8" t="n"/>
-    </row>
-    <row r="877" ht="15" customHeight="1" s="19">
-      <c r="A877" s="8" t="n"/>
-      <c r="B877" s="23" t="n"/>
-      <c r="C877" s="8" t="n"/>
-      <c r="D877" s="8" t="n"/>
-      <c r="E877" s="8" t="n"/>
-      <c r="F877" s="8" t="n"/>
-      <c r="G877" s="8" t="n"/>
-      <c r="H877" s="8" t="n"/>
-      <c r="I877" s="8" t="n"/>
-      <c r="J877" s="24" t="n"/>
-      <c r="K877" s="8" t="n"/>
-      <c r="L877" s="8" t="n"/>
-      <c r="M877" s="8" t="n"/>
-      <c r="N877" s="8" t="n"/>
-      <c r="O877" s="25" t="n"/>
-      <c r="P877" s="25" t="n"/>
-      <c r="Q877" s="25" t="n"/>
-      <c r="R877" s="8" t="n"/>
-    </row>
-    <row r="878" ht="15" customHeight="1" s="19">
-      <c r="A878" s="8" t="n"/>
-      <c r="B878" s="23" t="n"/>
-      <c r="C878" s="8" t="n"/>
-      <c r="D878" s="8" t="n"/>
-      <c r="E878" s="8" t="n"/>
-      <c r="F878" s="8" t="n"/>
-      <c r="G878" s="8" t="n"/>
-      <c r="H878" s="8" t="n"/>
-      <c r="I878" s="8" t="n"/>
-      <c r="J878" s="24" t="n"/>
-      <c r="K878" s="8" t="n"/>
-      <c r="L878" s="8" t="n"/>
-      <c r="M878" s="8" t="n"/>
-      <c r="N878" s="8" t="n"/>
-      <c r="O878" s="25" t="n"/>
-      <c r="P878" s="25" t="n"/>
-      <c r="Q878" s="25" t="n"/>
-      <c r="R878" s="8" t="n"/>
-    </row>
-    <row r="879" ht="15" customHeight="1" s="19">
-      <c r="A879" s="8" t="n"/>
-      <c r="B879" s="23" t="n"/>
-      <c r="C879" s="8" t="n"/>
-      <c r="D879" s="8" t="n"/>
-      <c r="E879" s="8" t="n"/>
-      <c r="F879" s="8" t="n"/>
-      <c r="G879" s="8" t="n"/>
-      <c r="H879" s="8" t="n"/>
-      <c r="I879" s="8" t="n"/>
-      <c r="J879" s="24" t="n"/>
-      <c r="K879" s="8" t="n"/>
-      <c r="L879" s="8" t="n"/>
-      <c r="M879" s="8" t="n"/>
-      <c r="N879" s="8" t="n"/>
-      <c r="O879" s="25" t="n"/>
-      <c r="P879" s="25" t="n"/>
-      <c r="Q879" s="25" t="n"/>
-      <c r="R879" s="8" t="n"/>
-    </row>
-    <row r="880" ht="15" customHeight="1" s="19">
-      <c r="A880" s="8" t="n"/>
-      <c r="B880" s="23" t="n"/>
-      <c r="C880" s="8" t="n"/>
-      <c r="D880" s="8" t="n"/>
-      <c r="E880" s="8" t="n"/>
-      <c r="F880" s="8" t="n"/>
-      <c r="G880" s="8" t="n"/>
-      <c r="H880" s="8" t="n"/>
-      <c r="I880" s="8" t="n"/>
-      <c r="J880" s="24" t="n"/>
-      <c r="K880" s="8" t="n"/>
-      <c r="L880" s="8" t="n"/>
-      <c r="M880" s="8" t="n"/>
-      <c r="N880" s="8" t="n"/>
-      <c r="O880" s="25" t="n"/>
-      <c r="P880" s="25" t="n"/>
-      <c r="Q880" s="25" t="n"/>
-      <c r="R880" s="8" t="n"/>
-    </row>
-    <row r="881" ht="15" customHeight="1" s="19">
-      <c r="A881" s="8" t="n"/>
-      <c r="B881" s="23" t="n"/>
-      <c r="C881" s="8" t="n"/>
-      <c r="D881" s="8" t="n"/>
-      <c r="E881" s="8" t="n"/>
-      <c r="F881" s="8" t="n"/>
-      <c r="G881" s="8" t="n"/>
-      <c r="H881" s="8" t="n"/>
-      <c r="I881" s="8" t="n"/>
-      <c r="J881" s="24" t="n"/>
-      <c r="K881" s="8" t="n"/>
-      <c r="L881" s="8" t="n"/>
-      <c r="M881" s="8" t="n"/>
-      <c r="N881" s="8" t="n"/>
-      <c r="O881" s="25" t="n"/>
-      <c r="P881" s="25" t="n"/>
-      <c r="Q881" s="25" t="n"/>
-      <c r="R881" s="8" t="n"/>
-    </row>
-    <row r="882" ht="15" customHeight="1" s="19">
-      <c r="A882" s="8" t="n"/>
-      <c r="B882" s="23" t="n"/>
-      <c r="C882" s="8" t="n"/>
-      <c r="D882" s="8" t="n"/>
-      <c r="E882" s="8" t="n"/>
-      <c r="F882" s="8" t="n"/>
-      <c r="G882" s="8" t="n"/>
-      <c r="H882" s="8" t="n"/>
-      <c r="I882" s="8" t="n"/>
-      <c r="J882" s="24" t="n"/>
-      <c r="K882" s="8" t="n"/>
-      <c r="L882" s="8" t="n"/>
-      <c r="M882" s="8" t="n"/>
-      <c r="N882" s="8" t="n"/>
-      <c r="O882" s="25" t="n"/>
-      <c r="P882" s="25" t="n"/>
-      <c r="Q882" s="25" t="n"/>
-      <c r="R882" s="8" t="n"/>
-    </row>
-    <row r="883" ht="15" customHeight="1" s="19">
-      <c r="A883" s="8" t="n"/>
-      <c r="B883" s="23" t="n"/>
-      <c r="C883" s="8" t="n"/>
-      <c r="D883" s="8" t="n"/>
-      <c r="E883" s="8" t="n"/>
-      <c r="F883" s="8" t="n"/>
-      <c r="G883" s="8" t="n"/>
-      <c r="H883" s="8" t="n"/>
-      <c r="I883" s="8" t="n"/>
-      <c r="J883" s="24" t="n"/>
-      <c r="K883" s="8" t="n"/>
-      <c r="L883" s="8" t="n"/>
-      <c r="M883" s="8" t="n"/>
-      <c r="N883" s="8" t="n"/>
-      <c r="O883" s="25" t="n"/>
-      <c r="P883" s="25" t="n"/>
-      <c r="Q883" s="25" t="n"/>
-      <c r="R883" s="8" t="n"/>
-    </row>
-    <row r="884" ht="15" customHeight="1" s="19">
-      <c r="A884" s="8" t="n"/>
-      <c r="B884" s="23" t="n"/>
-      <c r="C884" s="8" t="n"/>
-      <c r="D884" s="8" t="n"/>
-      <c r="E884" s="8" t="n"/>
-      <c r="F884" s="8" t="n"/>
-      <c r="G884" s="8" t="n"/>
-      <c r="H884" s="8" t="n"/>
-      <c r="I884" s="8" t="n"/>
-      <c r="J884" s="24" t="n"/>
-      <c r="K884" s="8" t="n"/>
-      <c r="L884" s="8" t="n"/>
-      <c r="M884" s="8" t="n"/>
-      <c r="N884" s="8" t="n"/>
-      <c r="O884" s="25" t="n"/>
-      <c r="P884" s="25" t="n"/>
-      <c r="Q884" s="25" t="n"/>
-      <c r="R884" s="8" t="n"/>
-    </row>
-    <row r="885" ht="15" customHeight="1" s="19">
-      <c r="A885" s="8" t="n"/>
-      <c r="B885" s="23" t="n"/>
-      <c r="C885" s="8" t="n"/>
-      <c r="D885" s="8" t="n"/>
-      <c r="E885" s="8" t="n"/>
-      <c r="F885" s="8" t="n"/>
-      <c r="G885" s="8" t="n"/>
-      <c r="H885" s="8" t="n"/>
-      <c r="I885" s="8" t="n"/>
-      <c r="J885" s="24" t="n"/>
-      <c r="K885" s="8" t="n"/>
-      <c r="L885" s="8" t="n"/>
-      <c r="M885" s="8" t="n"/>
-      <c r="N885" s="8" t="n"/>
-      <c r="O885" s="25" t="n"/>
-      <c r="P885" s="25" t="n"/>
-      <c r="Q885" s="25" t="n"/>
-      <c r="R885" s="8" t="n"/>
-    </row>
-    <row r="886" ht="15" customHeight="1" s="19">
-      <c r="A886" s="8" t="n"/>
-      <c r="B886" s="23" t="n"/>
-      <c r="C886" s="8" t="n"/>
-      <c r="D886" s="8" t="n"/>
-      <c r="E886" s="8" t="n"/>
-      <c r="F886" s="8" t="n"/>
-      <c r="G886" s="8" t="n"/>
-      <c r="H886" s="8" t="n"/>
-      <c r="I886" s="8" t="n"/>
-      <c r="J886" s="24" t="n"/>
-      <c r="K886" s="8" t="n"/>
-      <c r="L886" s="8" t="n"/>
-      <c r="M886" s="8" t="n"/>
-      <c r="N886" s="8" t="n"/>
-      <c r="O886" s="25" t="n"/>
-      <c r="P886" s="25" t="n"/>
-      <c r="Q886" s="25" t="n"/>
-      <c r="R886" s="8" t="n"/>
-    </row>
-    <row r="887" ht="15" customHeight="1" s="19">
-      <c r="A887" s="8" t="n"/>
-      <c r="B887" s="23" t="n"/>
-      <c r="C887" s="8" t="n"/>
-      <c r="D887" s="8" t="n"/>
-      <c r="E887" s="8" t="n"/>
-      <c r="F887" s="8" t="n"/>
-      <c r="G887" s="8" t="n"/>
-      <c r="H887" s="8" t="n"/>
-      <c r="I887" s="8" t="n"/>
-      <c r="J887" s="24" t="n"/>
-      <c r="K887" s="8" t="n"/>
-      <c r="L887" s="8" t="n"/>
-      <c r="M887" s="8" t="n"/>
-      <c r="N887" s="8" t="n"/>
-      <c r="O887" s="25" t="n"/>
-      <c r="P887" s="25" t="n"/>
-      <c r="Q887" s="25" t="n"/>
-      <c r="R887" s="8" t="n"/>
-    </row>
-    <row r="888" ht="15" customHeight="1" s="19">
-      <c r="A888" s="8" t="n"/>
-      <c r="B888" s="23" t="n"/>
-      <c r="C888" s="8" t="n"/>
-      <c r="D888" s="8" t="n"/>
-      <c r="E888" s="8" t="n"/>
-      <c r="F888" s="8" t="n"/>
-      <c r="G888" s="8" t="n"/>
-      <c r="H888" s="8" t="n"/>
-      <c r="I888" s="8" t="n"/>
-      <c r="J888" s="24" t="n"/>
-      <c r="K888" s="8" t="n"/>
-      <c r="L888" s="8" t="n"/>
-      <c r="M888" s="8" t="n"/>
-      <c r="N888" s="8" t="n"/>
-      <c r="O888" s="25" t="n"/>
-      <c r="P888" s="25" t="n"/>
-      <c r="Q888" s="25" t="n"/>
-      <c r="R888" s="8" t="n"/>
-    </row>
-    <row r="889" ht="15" customHeight="1" s="19">
-      <c r="A889" s="8" t="n"/>
-      <c r="B889" s="23" t="n"/>
-      <c r="C889" s="8" t="n"/>
-      <c r="D889" s="8" t="n"/>
-      <c r="E889" s="8" t="n"/>
-      <c r="F889" s="8" t="n"/>
-      <c r="G889" s="8" t="n"/>
-      <c r="H889" s="8" t="n"/>
-      <c r="I889" s="8" t="n"/>
-      <c r="J889" s="24" t="n"/>
-      <c r="K889" s="8" t="n"/>
-      <c r="L889" s="8" t="n"/>
-      <c r="M889" s="8" t="n"/>
-      <c r="N889" s="8" t="n"/>
-      <c r="O889" s="25" t="n"/>
-      <c r="P889" s="25" t="n"/>
-      <c r="Q889" s="25" t="n"/>
-      <c r="R889" s="8" t="n"/>
-    </row>
-    <row r="890" ht="15" customHeight="1" s="19">
-      <c r="A890" s="8" t="n"/>
-      <c r="B890" s="23" t="n"/>
-      <c r="C890" s="8" t="n"/>
-      <c r="D890" s="8" t="n"/>
-      <c r="E890" s="8" t="n"/>
-      <c r="F890" s="8" t="n"/>
-      <c r="G890" s="8" t="n"/>
-      <c r="H890" s="8" t="n"/>
-      <c r="I890" s="8" t="n"/>
-      <c r="J890" s="24" t="n"/>
-      <c r="K890" s="8" t="n"/>
-      <c r="L890" s="8" t="n"/>
-      <c r="M890" s="8" t="n"/>
-      <c r="N890" s="8" t="n"/>
-      <c r="O890" s="25" t="n"/>
-      <c r="P890" s="25" t="n"/>
-      <c r="Q890" s="25" t="n"/>
-      <c r="R890" s="8" t="n"/>
-    </row>
-    <row r="891" ht="15" customHeight="1" s="19">
-      <c r="A891" s="8" t="n"/>
-      <c r="B891" s="23" t="n"/>
-      <c r="C891" s="8" t="n"/>
-      <c r="D891" s="8" t="n"/>
-      <c r="E891" s="8" t="n"/>
-      <c r="F891" s="8" t="n"/>
-      <c r="G891" s="8" t="n"/>
-      <c r="H891" s="8" t="n"/>
-      <c r="I891" s="8" t="n"/>
-      <c r="J891" s="24" t="n"/>
-      <c r="K891" s="8" t="n"/>
-      <c r="L891" s="8" t="n"/>
-      <c r="M891" s="8" t="n"/>
-      <c r="N891" s="8" t="n"/>
-      <c r="O891" s="25" t="n"/>
-      <c r="P891" s="25" t="n"/>
-      <c r="Q891" s="25" t="n"/>
-      <c r="R891" s="8" t="n"/>
-    </row>
-    <row r="892" ht="15" customHeight="1" s="19">
-      <c r="A892" s="8" t="n"/>
-      <c r="B892" s="23" t="n"/>
-      <c r="C892" s="8" t="n"/>
-      <c r="D892" s="8" t="n"/>
-      <c r="E892" s="8" t="n"/>
-      <c r="F892" s="8" t="n"/>
-      <c r="G892" s="8" t="n"/>
-      <c r="H892" s="8" t="n"/>
-      <c r="I892" s="8" t="n"/>
-      <c r="J892" s="24" t="n"/>
-      <c r="K892" s="8" t="n"/>
-      <c r="L892" s="8" t="n"/>
-      <c r="M892" s="8" t="n"/>
-      <c r="N892" s="8" t="n"/>
-      <c r="O892" s="25" t="n"/>
-      <c r="P892" s="25" t="n"/>
-      <c r="Q892" s="25" t="n"/>
-      <c r="R892" s="8" t="n"/>
-    </row>
-    <row r="893" ht="15" customHeight="1" s="19">
-      <c r="A893" s="8" t="n"/>
-      <c r="B893" s="23" t="n"/>
-      <c r="C893" s="8" t="n"/>
-      <c r="D893" s="8" t="n"/>
-      <c r="E893" s="8" t="n"/>
-      <c r="F893" s="8" t="n"/>
-      <c r="G893" s="8" t="n"/>
-      <c r="H893" s="8" t="n"/>
-      <c r="I893" s="8" t="n"/>
-      <c r="J893" s="24" t="n"/>
-      <c r="K893" s="8" t="n"/>
-      <c r="L893" s="8" t="n"/>
-      <c r="M893" s="8" t="n"/>
-      <c r="N893" s="8" t="n"/>
-      <c r="O893" s="25" t="n"/>
-      <c r="P893" s="25" t="n"/>
-      <c r="Q893" s="25" t="n"/>
-      <c r="R893" s="8" t="n"/>
-    </row>
-    <row r="894" ht="15" customHeight="1" s="19">
-      <c r="A894" s="8" t="n"/>
-      <c r="B894" s="23" t="n"/>
-      <c r="C894" s="8" t="n"/>
-      <c r="D894" s="8" t="n"/>
-      <c r="E894" s="8" t="n"/>
-      <c r="F894" s="8" t="n"/>
-      <c r="G894" s="8" t="n"/>
-      <c r="H894" s="8" t="n"/>
-      <c r="I894" s="8" t="n"/>
-      <c r="J894" s="24" t="n"/>
-      <c r="K894" s="8" t="n"/>
-      <c r="L894" s="8" t="n"/>
-      <c r="M894" s="8" t="n"/>
-      <c r="N894" s="8" t="n"/>
-      <c r="O894" s="25" t="n"/>
-      <c r="P894" s="25" t="n"/>
-      <c r="Q894" s="25" t="n"/>
-      <c r="R894" s="8" t="n"/>
-    </row>
-    <row r="895" ht="15" customHeight="1" s="19">
-      <c r="A895" s="8" t="n"/>
-      <c r="B895" s="23" t="n"/>
-      <c r="C895" s="8" t="n"/>
-      <c r="D895" s="8" t="n"/>
-      <c r="E895" s="8" t="n"/>
-      <c r="F895" s="8" t="n"/>
-      <c r="G895" s="8" t="n"/>
-      <c r="H895" s="8" t="n"/>
-      <c r="I895" s="8" t="n"/>
-      <c r="J895" s="24" t="n"/>
-      <c r="K895" s="8" t="n"/>
-      <c r="L895" s="8" t="n"/>
-      <c r="M895" s="8" t="n"/>
-      <c r="N895" s="8" t="n"/>
-      <c r="O895" s="25" t="n"/>
-      <c r="P895" s="25" t="n"/>
-      <c r="Q895" s="25" t="n"/>
-      <c r="R895" s="8" t="n"/>
-    </row>
-    <row r="896" ht="15" customHeight="1" s="19">
-      <c r="A896" s="8" t="n"/>
-      <c r="B896" s="23" t="n"/>
-      <c r="C896" s="8" t="n"/>
-      <c r="D896" s="8" t="n"/>
-      <c r="E896" s="8" t="n"/>
-      <c r="F896" s="8" t="n"/>
-      <c r="G896" s="8" t="n"/>
-      <c r="H896" s="8" t="n"/>
-      <c r="I896" s="8" t="n"/>
-      <c r="J896" s="24" t="n"/>
-      <c r="K896" s="8" t="n"/>
-      <c r="L896" s="8" t="n"/>
-      <c r="M896" s="8" t="n"/>
-      <c r="N896" s="8" t="n"/>
-      <c r="O896" s="25" t="n"/>
-      <c r="P896" s="25" t="n"/>
-      <c r="Q896" s="25" t="n"/>
-      <c r="R896" s="8" t="n"/>
-    </row>
-    <row r="897" ht="15" customHeight="1" s="19">
-      <c r="A897" s="8" t="n"/>
-      <c r="B897" s="23" t="n"/>
-      <c r="C897" s="8" t="n"/>
-      <c r="D897" s="8" t="n"/>
-      <c r="E897" s="8" t="n"/>
-      <c r="F897" s="8" t="n"/>
-      <c r="G897" s="8" t="n"/>
-      <c r="H897" s="8" t="n"/>
-      <c r="I897" s="8" t="n"/>
-      <c r="J897" s="24" t="n"/>
-      <c r="K897" s="8" t="n"/>
-      <c r="L897" s="8" t="n"/>
-      <c r="M897" s="8" t="n"/>
-      <c r="N897" s="8" t="n"/>
-      <c r="O897" s="25" t="n"/>
-      <c r="P897" s="25" t="n"/>
-      <c r="Q897" s="25" t="n"/>
-      <c r="R897" s="8" t="n"/>
-    </row>
-    <row r="898" ht="15" customHeight="1" s="19">
-      <c r="A898" s="8" t="n"/>
-      <c r="B898" s="23" t="n"/>
-      <c r="C898" s="8" t="n"/>
-      <c r="D898" s="8" t="n"/>
-      <c r="E898" s="8" t="n"/>
-      <c r="F898" s="8" t="n"/>
-      <c r="G898" s="8" t="n"/>
-      <c r="H898" s="8" t="n"/>
-      <c r="I898" s="8" t="n"/>
-      <c r="J898" s="24" t="n"/>
-      <c r="K898" s="8" t="n"/>
-      <c r="L898" s="8" t="n"/>
-      <c r="M898" s="8" t="n"/>
-      <c r="N898" s="8" t="n"/>
-      <c r="O898" s="25" t="n"/>
-      <c r="P898" s="25" t="n"/>
-      <c r="Q898" s="25" t="n"/>
-      <c r="R898" s="8" t="n"/>
-    </row>
-    <row r="899" ht="15" customHeight="1" s="19">
-      <c r="A899" s="8" t="n"/>
-      <c r="B899" s="23" t="n"/>
-      <c r="C899" s="8" t="n"/>
-      <c r="D899" s="8" t="n"/>
-      <c r="E899" s="8" t="n"/>
-      <c r="F899" s="8" t="n"/>
-      <c r="G899" s="8" t="n"/>
-      <c r="H899" s="8" t="n"/>
-      <c r="I899" s="8" t="n"/>
-      <c r="J899" s="24" t="n"/>
-      <c r="K899" s="8" t="n"/>
-      <c r="L899" s="8" t="n"/>
-      <c r="M899" s="8" t="n"/>
-      <c r="N899" s="8" t="n"/>
-      <c r="O899" s="25" t="n"/>
-      <c r="P899" s="25" t="n"/>
-      <c r="Q899" s="25" t="n"/>
-      <c r="R899" s="8" t="n"/>
-    </row>
-    <row r="900" ht="15" customHeight="1" s="19">
-      <c r="A900" s="8" t="n"/>
-      <c r="B900" s="23" t="n"/>
-      <c r="C900" s="8" t="n"/>
-      <c r="D900" s="8" t="n"/>
-      <c r="E900" s="8" t="n"/>
-      <c r="F900" s="8" t="n"/>
-      <c r="G900" s="8" t="n"/>
-      <c r="H900" s="8" t="n"/>
-      <c r="I900" s="8" t="n"/>
-      <c r="J900" s="24" t="n"/>
-      <c r="K900" s="8" t="n"/>
-      <c r="L900" s="8" t="n"/>
-      <c r="M900" s="8" t="n"/>
-      <c r="N900" s="8" t="n"/>
-      <c r="O900" s="25" t="n"/>
-      <c r="P900" s="25" t="n"/>
-      <c r="Q900" s="25" t="n"/>
-      <c r="R900" s="8" t="n"/>
-    </row>
-    <row r="901" ht="15" customHeight="1" s="19">
-      <c r="A901" s="8" t="n"/>
-      <c r="B901" s="23" t="n"/>
-      <c r="C901" s="8" t="n"/>
-      <c r="D901" s="8" t="n"/>
-      <c r="E901" s="8" t="n"/>
-      <c r="F901" s="8" t="n"/>
-      <c r="G901" s="8" t="n"/>
-      <c r="H901" s="8" t="n"/>
-      <c r="I901" s="8" t="n"/>
-      <c r="J901" s="24" t="n"/>
-      <c r="K901" s="8" t="n"/>
-      <c r="L901" s="8" t="n"/>
-      <c r="M901" s="8" t="n"/>
-      <c r="N901" s="8" t="n"/>
-      <c r="O901" s="25" t="n"/>
-      <c r="P901" s="25" t="n"/>
-      <c r="Q901" s="25" t="n"/>
-      <c r="R901" s="8" t="n"/>
-    </row>
-    <row r="902" ht="15" customHeight="1" s="19">
-      <c r="A902" s="8" t="n"/>
-      <c r="B902" s="23" t="n"/>
-      <c r="C902" s="8" t="n"/>
-      <c r="D902" s="8" t="n"/>
-      <c r="E902" s="8" t="n"/>
-      <c r="F902" s="8" t="n"/>
-      <c r="G902" s="8" t="n"/>
-      <c r="H902" s="8" t="n"/>
-      <c r="I902" s="8" t="n"/>
-      <c r="J902" s="24" t="n"/>
-      <c r="K902" s="8" t="n"/>
-      <c r="L902" s="8" t="n"/>
-      <c r="M902" s="8" t="n"/>
-      <c r="N902" s="8" t="n"/>
-      <c r="O902" s="25" t="n"/>
-      <c r="P902" s="25" t="n"/>
-      <c r="Q902" s="25" t="n"/>
-      <c r="R902" s="8" t="n"/>
-    </row>
-    <row r="903" ht="15" customHeight="1" s="19">
-      <c r="A903" s="8" t="n"/>
-      <c r="B903" s="23" t="n"/>
-      <c r="C903" s="8" t="n"/>
-      <c r="D903" s="8" t="n"/>
-      <c r="E903" s="8" t="n"/>
-      <c r="F903" s="8" t="n"/>
-      <c r="G903" s="8" t="n"/>
-      <c r="H903" s="8" t="n"/>
-      <c r="I903" s="8" t="n"/>
-      <c r="J903" s="24" t="n"/>
-      <c r="K903" s="8" t="n"/>
-      <c r="L903" s="8" t="n"/>
-      <c r="M903" s="8" t="n"/>
-      <c r="N903" s="8" t="n"/>
-      <c r="O903" s="25" t="n"/>
-      <c r="P903" s="25" t="n"/>
-      <c r="Q903" s="25" t="n"/>
-      <c r="R903" s="8" t="n"/>
-    </row>
-    <row r="904" ht="15" customHeight="1" s="19">
-      <c r="A904" s="8" t="n"/>
-      <c r="B904" s="23" t="n"/>
-      <c r="C904" s="8" t="n"/>
-      <c r="D904" s="8" t="n"/>
-      <c r="E904" s="8" t="n"/>
-      <c r="F904" s="8" t="n"/>
-      <c r="G904" s="8" t="n"/>
-      <c r="H904" s="8" t="n"/>
-      <c r="I904" s="8" t="n"/>
-      <c r="J904" s="24" t="n"/>
-      <c r="K904" s="8" t="n"/>
-      <c r="L904" s="8" t="n"/>
-      <c r="M904" s="8" t="n"/>
-      <c r="N904" s="8" t="n"/>
-      <c r="O904" s="25" t="n"/>
-      <c r="P904" s="25" t="n"/>
-      <c r="Q904" s="25" t="n"/>
-      <c r="R904" s="8" t="n"/>
-    </row>
-    <row r="905" ht="15" customHeight="1" s="19">
-      <c r="A905" s="8" t="n"/>
-      <c r="B905" s="23" t="n"/>
-      <c r="C905" s="8" t="n"/>
-      <c r="D905" s="8" t="n"/>
-      <c r="E905" s="8" t="n"/>
-      <c r="F905" s="8" t="n"/>
-      <c r="G905" s="8" t="n"/>
-      <c r="H905" s="8" t="n"/>
-      <c r="I905" s="8" t="n"/>
-      <c r="J905" s="24" t="n"/>
-      <c r="K905" s="8" t="n"/>
-      <c r="L905" s="8" t="n"/>
-      <c r="M905" s="8" t="n"/>
-      <c r="N905" s="8" t="n"/>
-      <c r="O905" s="25" t="n"/>
-      <c r="P905" s="25" t="n"/>
-      <c r="Q905" s="25" t="n"/>
-      <c r="R905" s="8" t="n"/>
-    </row>
-    <row r="906" ht="15" customHeight="1" s="19">
-      <c r="A906" s="8" t="n"/>
-      <c r="B906" s="23" t="n"/>
-      <c r="C906" s="8" t="n"/>
-      <c r="D906" s="8" t="n"/>
-      <c r="E906" s="8" t="n"/>
-      <c r="F906" s="8" t="n"/>
-      <c r="G906" s="8" t="n"/>
-      <c r="H906" s="8" t="n"/>
-      <c r="I906" s="8" t="n"/>
-      <c r="J906" s="24" t="n"/>
-      <c r="K906" s="8" t="n"/>
-      <c r="L906" s="8" t="n"/>
-      <c r="M906" s="8" t="n"/>
-      <c r="N906" s="8" t="n"/>
-      <c r="O906" s="25" t="n"/>
-      <c r="P906" s="25" t="n"/>
-      <c r="Q906" s="25" t="n"/>
-      <c r="R906" s="8" t="n"/>
-    </row>
-    <row r="907" ht="15" customHeight="1" s="19">
-      <c r="A907" s="8" t="n"/>
-      <c r="B907" s="23" t="n"/>
-      <c r="C907" s="8" t="n"/>
-      <c r="D907" s="8" t="n"/>
-      <c r="E907" s="8" t="n"/>
-      <c r="F907" s="8" t="n"/>
-      <c r="G907" s="8" t="n"/>
-      <c r="H907" s="8" t="n"/>
-      <c r="I907" s="8" t="n"/>
-      <c r="J907" s="24" t="n"/>
-      <c r="K907" s="8" t="n"/>
-      <c r="L907" s="8" t="n"/>
-      <c r="M907" s="8" t="n"/>
-      <c r="N907" s="8" t="n"/>
-      <c r="O907" s="25" t="n"/>
-      <c r="P907" s="25" t="n"/>
-      <c r="Q907" s="25" t="n"/>
-      <c r="R907" s="8" t="n"/>
-    </row>
-    <row r="908" ht="15" customHeight="1" s="19">
-      <c r="A908" s="8" t="n"/>
-      <c r="B908" s="23" t="n"/>
-      <c r="C908" s="8" t="n"/>
-      <c r="D908" s="8" t="n"/>
-      <c r="E908" s="8" t="n"/>
-      <c r="F908" s="8" t="n"/>
-      <c r="G908" s="8" t="n"/>
-      <c r="H908" s="8" t="n"/>
-      <c r="I908" s="8" t="n"/>
-      <c r="J908" s="24" t="n"/>
-      <c r="K908" s="8" t="n"/>
-      <c r="L908" s="8" t="n"/>
-      <c r="M908" s="8" t="n"/>
-      <c r="N908" s="8" t="n"/>
-      <c r="O908" s="25" t="n"/>
-      <c r="P908" s="25" t="n"/>
-      <c r="Q908" s="25" t="n"/>
-      <c r="R908" s="8" t="n"/>
-    </row>
-    <row r="909" ht="15" customHeight="1" s="19">
-      <c r="A909" s="8" t="n"/>
-      <c r="B909" s="23" t="n"/>
-      <c r="C909" s="8" t="n"/>
-      <c r="D909" s="8" t="n"/>
-      <c r="E909" s="8" t="n"/>
-      <c r="F909" s="8" t="n"/>
-      <c r="G909" s="8" t="n"/>
-      <c r="H909" s="8" t="n"/>
-      <c r="I909" s="8" t="n"/>
-      <c r="J909" s="24" t="n"/>
-      <c r="K909" s="8" t="n"/>
-      <c r="L909" s="8" t="n"/>
-      <c r="M909" s="8" t="n"/>
-      <c r="N909" s="8" t="n"/>
-      <c r="O909" s="25" t="n"/>
-      <c r="P909" s="25" t="n"/>
-      <c r="Q909" s="25" t="n"/>
-      <c r="R909" s="8" t="n"/>
-    </row>
-    <row r="910" ht="15" customHeight="1" s="19">
-      <c r="A910" s="8" t="n"/>
-      <c r="B910" s="23" t="n"/>
-      <c r="C910" s="8" t="n"/>
-      <c r="D910" s="8" t="n"/>
-      <c r="E910" s="8" t="n"/>
-      <c r="F910" s="8" t="n"/>
-      <c r="G910" s="8" t="n"/>
-      <c r="H910" s="8" t="n"/>
-      <c r="I910" s="8" t="n"/>
-      <c r="J910" s="24" t="n"/>
-      <c r="K910" s="8" t="n"/>
-      <c r="L910" s="8" t="n"/>
-      <c r="M910" s="8" t="n"/>
-      <c r="N910" s="8" t="n"/>
-      <c r="O910" s="25" t="n"/>
-      <c r="P910" s="25" t="n"/>
-      <c r="Q910" s="25" t="n"/>
-      <c r="R910" s="8" t="n"/>
-    </row>
-    <row r="911" ht="15" customHeight="1" s="19">
-      <c r="A911" s="8" t="n"/>
-      <c r="B911" s="23" t="n"/>
-      <c r="C911" s="8" t="n"/>
-      <c r="D911" s="8" t="n"/>
-      <c r="E911" s="8" t="n"/>
-      <c r="F911" s="8" t="n"/>
-      <c r="G911" s="8" t="n"/>
-      <c r="H911" s="8" t="n"/>
-      <c r="I911" s="8" t="n"/>
-      <c r="J911" s="24" t="n"/>
-      <c r="K911" s="8" t="n"/>
-      <c r="L911" s="8" t="n"/>
-      <c r="M911" s="8" t="n"/>
-      <c r="N911" s="8" t="n"/>
-      <c r="O911" s="25" t="n"/>
-      <c r="P911" s="25" t="n"/>
-      <c r="Q911" s="25" t="n"/>
-      <c r="R911" s="8" t="n"/>
-    </row>
-    <row r="912" ht="15" customHeight="1" s="19">
-      <c r="A912" s="8" t="n"/>
-      <c r="B912" s="23" t="n"/>
-      <c r="C912" s="8" t="n"/>
-      <c r="D912" s="8" t="n"/>
-      <c r="E912" s="8" t="n"/>
-      <c r="F912" s="8" t="n"/>
-      <c r="G912" s="8" t="n"/>
-      <c r="H912" s="8" t="n"/>
-      <c r="I912" s="8" t="n"/>
-      <c r="J912" s="24" t="n"/>
-      <c r="K912" s="8" t="n"/>
-      <c r="L912" s="8" t="n"/>
-      <c r="M912" s="8" t="n"/>
-      <c r="N912" s="8" t="n"/>
-      <c r="O912" s="25" t="n"/>
-      <c r="P912" s="25" t="n"/>
-      <c r="Q912" s="25" t="n"/>
-      <c r="R912" s="8" t="n"/>
-    </row>
-    <row r="913" ht="15" customHeight="1" s="19">
-      <c r="A913" s="8" t="n"/>
-      <c r="B913" s="23" t="n"/>
-      <c r="C913" s="8" t="n"/>
-      <c r="D913" s="8" t="n"/>
-      <c r="E913" s="8" t="n"/>
-      <c r="F913" s="8" t="n"/>
-      <c r="G913" s="8" t="n"/>
-      <c r="H913" s="8" t="n"/>
-      <c r="I913" s="8" t="n"/>
-      <c r="J913" s="24" t="n"/>
-      <c r="K913" s="8" t="n"/>
-      <c r="L913" s="8" t="n"/>
-      <c r="M913" s="8" t="n"/>
-      <c r="N913" s="8" t="n"/>
-      <c r="O913" s="25" t="n"/>
-      <c r="P913" s="25" t="n"/>
-      <c r="Q913" s="25" t="n"/>
-      <c r="R913" s="8" t="n"/>
-    </row>
-    <row r="914" ht="15" customHeight="1" s="19">
-      <c r="A914" s="8" t="n"/>
-      <c r="B914" s="23" t="n"/>
-      <c r="C914" s="8" t="n"/>
-      <c r="D914" s="8" t="n"/>
-      <c r="E914" s="8" t="n"/>
-      <c r="F914" s="8" t="n"/>
-      <c r="G914" s="8" t="n"/>
-      <c r="H914" s="8" t="n"/>
-      <c r="I914" s="8" t="n"/>
-      <c r="J914" s="24" t="n"/>
-      <c r="K914" s="8" t="n"/>
-      <c r="L914" s="8" t="n"/>
-      <c r="M914" s="8" t="n"/>
-      <c r="N914" s="8" t="n"/>
-      <c r="O914" s="25" t="n"/>
-      <c r="P914" s="25" t="n"/>
-      <c r="Q914" s="25" t="n"/>
-      <c r="R914" s="8" t="n"/>
-    </row>
-    <row r="915" ht="15" customHeight="1" s="19">
-      <c r="A915" s="8" t="n"/>
-      <c r="B915" s="23" t="n"/>
-      <c r="C915" s="8" t="n"/>
-      <c r="D915" s="8" t="n"/>
-      <c r="E915" s="8" t="n"/>
-      <c r="F915" s="8" t="n"/>
-      <c r="G915" s="8" t="n"/>
-      <c r="H915" s="8" t="n"/>
-      <c r="I915" s="8" t="n"/>
-      <c r="J915" s="24" t="n"/>
-      <c r="K915" s="8" t="n"/>
-      <c r="L915" s="8" t="n"/>
-      <c r="M915" s="8" t="n"/>
-      <c r="N915" s="8" t="n"/>
-      <c r="O915" s="25" t="n"/>
-      <c r="P915" s="25" t="n"/>
-      <c r="Q915" s="25" t="n"/>
-      <c r="R915" s="8" t="n"/>
-    </row>
-    <row r="916" ht="15" customHeight="1" s="19">
-      <c r="A916" s="8" t="n"/>
-      <c r="B916" s="23" t="n"/>
-      <c r="C916" s="8" t="n"/>
-      <c r="D916" s="8" t="n"/>
-      <c r="E916" s="8" t="n"/>
-      <c r="F916" s="8" t="n"/>
-      <c r="G916" s="8" t="n"/>
-      <c r="H916" s="8" t="n"/>
-      <c r="I916" s="8" t="n"/>
-      <c r="J916" s="24" t="n"/>
-      <c r="K916" s="8" t="n"/>
-      <c r="L916" s="8" t="n"/>
-      <c r="M916" s="8" t="n"/>
-      <c r="N916" s="8" t="n"/>
-      <c r="O916" s="25" t="n"/>
-      <c r="P916" s="25" t="n"/>
-      <c r="Q916" s="25" t="n"/>
-      <c r="R916" s="8" t="n"/>
-    </row>
-    <row r="917" ht="15" customHeight="1" s="19">
-      <c r="A917" s="8" t="n"/>
-      <c r="B917" s="23" t="n"/>
-      <c r="C917" s="8" t="n"/>
-      <c r="D917" s="8" t="n"/>
-      <c r="E917" s="8" t="n"/>
-      <c r="F917" s="8" t="n"/>
-      <c r="G917" s="8" t="n"/>
-      <c r="H917" s="8" t="n"/>
-      <c r="I917" s="8" t="n"/>
-      <c r="J917" s="24" t="n"/>
-      <c r="K917" s="8" t="n"/>
-      <c r="L917" s="8" t="n"/>
-      <c r="M917" s="8" t="n"/>
-      <c r="N917" s="8" t="n"/>
-      <c r="O917" s="25" t="n"/>
-      <c r="P917" s="25" t="n"/>
-      <c r="Q917" s="25" t="n"/>
-      <c r="R917" s="8" t="n"/>
-    </row>
-    <row r="918" ht="15" customHeight="1" s="19">
-      <c r="A918" s="8" t="n"/>
-      <c r="B918" s="23" t="n"/>
-      <c r="C918" s="8" t="n"/>
-      <c r="D918" s="8" t="n"/>
-      <c r="E918" s="8" t="n"/>
-      <c r="F918" s="8" t="n"/>
-      <c r="G918" s="8" t="n"/>
-      <c r="H918" s="8" t="n"/>
-      <c r="I918" s="8" t="n"/>
-      <c r="J918" s="24" t="n"/>
-      <c r="K918" s="8" t="n"/>
-      <c r="L918" s="8" t="n"/>
-      <c r="M918" s="8" t="n"/>
-      <c r="N918" s="8" t="n"/>
-      <c r="O918" s="25" t="n"/>
-      <c r="P918" s="25" t="n"/>
-      <c r="Q918" s="25" t="n"/>
-      <c r="R918" s="8" t="n"/>
-    </row>
-    <row r="919" ht="15" customHeight="1" s="19">
-      <c r="A919" s="8" t="n"/>
-      <c r="B919" s="23" t="n"/>
-      <c r="C919" s="8" t="n"/>
-      <c r="D919" s="8" t="n"/>
-      <c r="E919" s="8" t="n"/>
-      <c r="F919" s="8" t="n"/>
-      <c r="G919" s="8" t="n"/>
-      <c r="H919" s="8" t="n"/>
-      <c r="I919" s="8" t="n"/>
-      <c r="J919" s="24" t="n"/>
-      <c r="K919" s="8" t="n"/>
-      <c r="L919" s="8" t="n"/>
-      <c r="M919" s="8" t="n"/>
-      <c r="N919" s="8" t="n"/>
-      <c r="O919" s="25" t="n"/>
-      <c r="P919" s="25" t="n"/>
-      <c r="Q919" s="25" t="n"/>
-      <c r="R919" s="8" t="n"/>
-    </row>
-    <row r="920" ht="15" customHeight="1" s="19">
-      <c r="A920" s="8" t="n"/>
-      <c r="B920" s="23" t="n"/>
-      <c r="C920" s="8" t="n"/>
-      <c r="D920" s="8" t="n"/>
-      <c r="E920" s="8" t="n"/>
-      <c r="F920" s="8" t="n"/>
-      <c r="G920" s="8" t="n"/>
-      <c r="H920" s="8" t="n"/>
-      <c r="I920" s="8" t="n"/>
-      <c r="J920" s="24" t="n"/>
-      <c r="K920" s="8" t="n"/>
-      <c r="L920" s="8" t="n"/>
-      <c r="M920" s="8" t="n"/>
-      <c r="N920" s="8" t="n"/>
-      <c r="O920" s="25" t="n"/>
-      <c r="P920" s="25" t="n"/>
-      <c r="Q920" s="25" t="n"/>
-      <c r="R920" s="8" t="n"/>
-    </row>
-    <row r="921" ht="15" customHeight="1" s="19">
-      <c r="A921" s="8" t="n"/>
-      <c r="B921" s="23" t="n"/>
-      <c r="C921" s="8" t="n"/>
-      <c r="D921" s="8" t="n"/>
-      <c r="E921" s="8" t="n"/>
-      <c r="F921" s="8" t="n"/>
-      <c r="G921" s="8" t="n"/>
-      <c r="H921" s="8" t="n"/>
-      <c r="I921" s="8" t="n"/>
-      <c r="J921" s="24" t="n"/>
-      <c r="K921" s="8" t="n"/>
-      <c r="L921" s="8" t="n"/>
-      <c r="M921" s="8" t="n"/>
-      <c r="N921" s="8" t="n"/>
-      <c r="O921" s="25" t="n"/>
-      <c r="P921" s="25" t="n"/>
-      <c r="Q921" s="25" t="n"/>
-      <c r="R921" s="8" t="n"/>
-    </row>
-    <row r="922" ht="15" customHeight="1" s="19">
-      <c r="A922" s="8" t="n"/>
-      <c r="B922" s="23" t="n"/>
-      <c r="C922" s="8" t="n"/>
-      <c r="D922" s="8" t="n"/>
-      <c r="E922" s="8" t="n"/>
-      <c r="F922" s="8" t="n"/>
-      <c r="G922" s="8" t="n"/>
-      <c r="H922" s="8" t="n"/>
-      <c r="I922" s="8" t="n"/>
-      <c r="J922" s="24" t="n"/>
-      <c r="K922" s="8" t="n"/>
-      <c r="L922" s="8" t="n"/>
-      <c r="M922" s="8" t="n"/>
-      <c r="N922" s="8" t="n"/>
-      <c r="O922" s="25" t="n"/>
-      <c r="P922" s="25" t="n"/>
-      <c r="Q922" s="25" t="n"/>
-      <c r="R922" s="8" t="n"/>
-    </row>
-    <row r="923" ht="15" customHeight="1" s="19">
-      <c r="A923" s="8" t="n"/>
-      <c r="B923" s="23" t="n"/>
-      <c r="C923" s="8" t="n"/>
-      <c r="D923" s="8" t="n"/>
-      <c r="E923" s="8" t="n"/>
-      <c r="F923" s="8" t="n"/>
-      <c r="G923" s="8" t="n"/>
-      <c r="H923" s="8" t="n"/>
-      <c r="I923" s="8" t="n"/>
-      <c r="J923" s="24" t="n"/>
-      <c r="K923" s="8" t="n"/>
-      <c r="L923" s="8" t="n"/>
-      <c r="M923" s="8" t="n"/>
-      <c r="N923" s="8" t="n"/>
-      <c r="O923" s="25" t="n"/>
-      <c r="P923" s="25" t="n"/>
-      <c r="Q923" s="25" t="n"/>
-      <c r="R923" s="8" t="n"/>
-    </row>
-    <row r="924" ht="15" customHeight="1" s="19">
-      <c r="A924" s="8" t="n"/>
-      <c r="B924" s="23" t="n"/>
-      <c r="C924" s="8" t="n"/>
-      <c r="D924" s="8" t="n"/>
-      <c r="E924" s="8" t="n"/>
-      <c r="F924" s="8" t="n"/>
-      <c r="G924" s="8" t="n"/>
-      <c r="H924" s="8" t="n"/>
-      <c r="I924" s="8" t="n"/>
-      <c r="J924" s="24" t="n"/>
-      <c r="K924" s="8" t="n"/>
-      <c r="L924" s="8" t="n"/>
-      <c r="M924" s="8" t="n"/>
-      <c r="N924" s="8" t="n"/>
-      <c r="O924" s="25" t="n"/>
-      <c r="P924" s="25" t="n"/>
-      <c r="Q924" s="25" t="n"/>
-      <c r="R924" s="8" t="n"/>
-    </row>
-    <row r="925" ht="15" customHeight="1" s="19">
-      <c r="A925" s="8" t="n"/>
-      <c r="B925" s="23" t="n"/>
-      <c r="C925" s="8" t="n"/>
-      <c r="D925" s="8" t="n"/>
-      <c r="E925" s="8" t="n"/>
-      <c r="F925" s="8" t="n"/>
-      <c r="G925" s="8" t="n"/>
-      <c r="H925" s="8" t="n"/>
-      <c r="I925" s="8" t="n"/>
-      <c r="J925" s="24" t="n"/>
-      <c r="K925" s="8" t="n"/>
-      <c r="L925" s="8" t="n"/>
-      <c r="M925" s="8" t="n"/>
-      <c r="N925" s="8" t="n"/>
-      <c r="O925" s="25" t="n"/>
-      <c r="P925" s="25" t="n"/>
-      <c r="Q925" s="25" t="n"/>
-      <c r="R925" s="8" t="n"/>
-    </row>
-    <row r="926" ht="15" customHeight="1" s="19">
-      <c r="A926" s="8" t="n"/>
-      <c r="B926" s="23" t="n"/>
-      <c r="C926" s="8" t="n"/>
-      <c r="D926" s="8" t="n"/>
-      <c r="E926" s="8" t="n"/>
-      <c r="F926" s="8" t="n"/>
-      <c r="G926" s="8" t="n"/>
-      <c r="H926" s="8" t="n"/>
-      <c r="I926" s="8" t="n"/>
-      <c r="J926" s="24" t="n"/>
-      <c r="K926" s="8" t="n"/>
-      <c r="L926" s="8" t="n"/>
-      <c r="M926" s="8" t="n"/>
-      <c r="N926" s="8" t="n"/>
-      <c r="O926" s="25" t="n"/>
-      <c r="P926" s="25" t="n"/>
-      <c r="Q926" s="25" t="n"/>
-      <c r="R926" s="8" t="n"/>
-    </row>
-    <row r="927" ht="15" customHeight="1" s="19">
-      <c r="A927" s="8" t="n"/>
-      <c r="B927" s="23" t="n"/>
-      <c r="C927" s="8" t="n"/>
-      <c r="D927" s="8" t="n"/>
-      <c r="E927" s="8" t="n"/>
-      <c r="F927" s="8" t="n"/>
-      <c r="G927" s="8" t="n"/>
-      <c r="H927" s="8" t="n"/>
-      <c r="I927" s="8" t="n"/>
-      <c r="J927" s="24" t="n"/>
-      <c r="K927" s="8" t="n"/>
-      <c r="L927" s="8" t="n"/>
-      <c r="M927" s="8" t="n"/>
-      <c r="N927" s="8" t="n"/>
-      <c r="O927" s="25" t="n"/>
-      <c r="P927" s="25" t="n"/>
-      <c r="Q927" s="25" t="n"/>
-      <c r="R927" s="8" t="n"/>
-    </row>
-    <row r="928" ht="15" customHeight="1" s="19">
-      <c r="A928" s="8" t="n"/>
-      <c r="B928" s="23" t="n"/>
-      <c r="C928" s="8" t="n"/>
-      <c r="D928" s="8" t="n"/>
-      <c r="E928" s="8" t="n"/>
-      <c r="F928" s="8" t="n"/>
-      <c r="G928" s="8" t="n"/>
-      <c r="H928" s="8" t="n"/>
-      <c r="I928" s="8" t="n"/>
-      <c r="J928" s="24" t="n"/>
-      <c r="K928" s="8" t="n"/>
-      <c r="L928" s="8" t="n"/>
-      <c r="M928" s="8" t="n"/>
-      <c r="N928" s="8" t="n"/>
-      <c r="O928" s="25" t="n"/>
-      <c r="P928" s="25" t="n"/>
-      <c r="Q928" s="25" t="n"/>
-      <c r="R928" s="8" t="n"/>
-    </row>
-    <row r="929" ht="15" customHeight="1" s="19">
-      <c r="A929" s="8" t="n"/>
-      <c r="B929" s="23" t="n"/>
-      <c r="C929" s="8" t="n"/>
-      <c r="D929" s="8" t="n"/>
-      <c r="E929" s="8" t="n"/>
-      <c r="F929" s="8" t="n"/>
-      <c r="G929" s="8" t="n"/>
-      <c r="H929" s="8" t="n"/>
-      <c r="I929" s="8" t="n"/>
-      <c r="J929" s="24" t="n"/>
-      <c r="K929" s="8" t="n"/>
-      <c r="L929" s="8" t="n"/>
-      <c r="M929" s="8" t="n"/>
-      <c r="N929" s="8" t="n"/>
-      <c r="O929" s="25" t="n"/>
-      <c r="P929" s="25" t="n"/>
-      <c r="Q929" s="25" t="n"/>
-      <c r="R929" s="8" t="n"/>
-    </row>
-    <row r="930" ht="15" customHeight="1" s="19">
-      <c r="A930" s="8" t="n"/>
-      <c r="B930" s="23" t="n"/>
-      <c r="C930" s="8" t="n"/>
-      <c r="D930" s="8" t="n"/>
-      <c r="E930" s="8" t="n"/>
-      <c r="F930" s="8" t="n"/>
-      <c r="G930" s="8" t="n"/>
-      <c r="H930" s="8" t="n"/>
-      <c r="I930" s="8" t="n"/>
-      <c r="J930" s="24" t="n"/>
-      <c r="K930" s="8" t="n"/>
-      <c r="L930" s="8" t="n"/>
-      <c r="M930" s="8" t="n"/>
-      <c r="N930" s="8" t="n"/>
-      <c r="O930" s="25" t="n"/>
-      <c r="P930" s="25" t="n"/>
-      <c r="Q930" s="25" t="n"/>
-      <c r="R930" s="8" t="n"/>
-    </row>
-    <row r="931" ht="15" customHeight="1" s="19">
-      <c r="A931" s="8" t="n"/>
-      <c r="B931" s="23" t="n"/>
-      <c r="C931" s="8" t="n"/>
-      <c r="D931" s="8" t="n"/>
-      <c r="E931" s="8" t="n"/>
-      <c r="F931" s="8" t="n"/>
-      <c r="G931" s="8" t="n"/>
-      <c r="H931" s="8" t="n"/>
-      <c r="I931" s="8" t="n"/>
-      <c r="J931" s="24" t="n"/>
-      <c r="K931" s="8" t="n"/>
-      <c r="L931" s="8" t="n"/>
-      <c r="M931" s="8" t="n"/>
-      <c r="N931" s="8" t="n"/>
-      <c r="O931" s="25" t="n"/>
-      <c r="P931" s="25" t="n"/>
-      <c r="Q931" s="25" t="n"/>
-      <c r="R931" s="8" t="n"/>
-    </row>
-    <row r="932" ht="15" customHeight="1" s="19">
-      <c r="A932" s="8" t="n"/>
-      <c r="B932" s="23" t="n"/>
-      <c r="C932" s="8" t="n"/>
-      <c r="D932" s="8" t="n"/>
-      <c r="E932" s="8" t="n"/>
-      <c r="F932" s="8" t="n"/>
-      <c r="G932" s="8" t="n"/>
-      <c r="H932" s="8" t="n"/>
-      <c r="I932" s="8" t="n"/>
-      <c r="J932" s="24" t="n"/>
-      <c r="K932" s="8" t="n"/>
-      <c r="L932" s="8" t="n"/>
-      <c r="M932" s="8" t="n"/>
-      <c r="N932" s="8" t="n"/>
-      <c r="O932" s="25" t="n"/>
-      <c r="P932" s="25" t="n"/>
-      <c r="Q932" s="25" t="n"/>
-      <c r="R932" s="8" t="n"/>
-    </row>
-    <row r="933" ht="15" customHeight="1" s="19">
-      <c r="A933" s="8" t="n"/>
-      <c r="B933" s="23" t="n"/>
-      <c r="C933" s="8" t="n"/>
-      <c r="D933" s="8" t="n"/>
-      <c r="E933" s="8" t="n"/>
-      <c r="F933" s="8" t="n"/>
-      <c r="G933" s="8" t="n"/>
-      <c r="H933" s="8" t="n"/>
-      <c r="I933" s="8" t="n"/>
-      <c r="J933" s="24" t="n"/>
-      <c r="K933" s="8" t="n"/>
-      <c r="L933" s="8" t="n"/>
-      <c r="M933" s="8" t="n"/>
-      <c r="N933" s="8" t="n"/>
-      <c r="O933" s="25" t="n"/>
-      <c r="P933" s="25" t="n"/>
-      <c r="Q933" s="25" t="n"/>
-      <c r="R933" s="8" t="n"/>
-    </row>
-    <row r="934" ht="15" customHeight="1" s="19">
-      <c r="A934" s="8" t="n"/>
-      <c r="B934" s="23" t="n"/>
-      <c r="C934" s="8" t="n"/>
-      <c r="D934" s="8" t="n"/>
-      <c r="E934" s="8" t="n"/>
-      <c r="F934" s="8" t="n"/>
-      <c r="G934" s="8" t="n"/>
-      <c r="H934" s="8" t="n"/>
-      <c r="I934" s="8" t="n"/>
-      <c r="J934" s="24" t="n"/>
-      <c r="K934" s="8" t="n"/>
-      <c r="L934" s="8" t="n"/>
-      <c r="M934" s="8" t="n"/>
-      <c r="N934" s="8" t="n"/>
-      <c r="O934" s="25" t="n"/>
-      <c r="P934" s="25" t="n"/>
-      <c r="Q934" s="25" t="n"/>
-      <c r="R934" s="8" t="n"/>
-    </row>
-    <row r="935" ht="15" customHeight="1" s="19">
-      <c r="A935" s="8" t="n"/>
-      <c r="B935" s="23" t="n"/>
-      <c r="C935" s="8" t="n"/>
-      <c r="D935" s="8" t="n"/>
-      <c r="E935" s="8" t="n"/>
-      <c r="F935" s="8" t="n"/>
-      <c r="G935" s="8" t="n"/>
-      <c r="H935" s="8" t="n"/>
-      <c r="I935" s="8" t="n"/>
-      <c r="J935" s="24" t="n"/>
-      <c r="K935" s="8" t="n"/>
-      <c r="L935" s="8" t="n"/>
-      <c r="M935" s="8" t="n"/>
-      <c r="N935" s="8" t="n"/>
-      <c r="O935" s="25" t="n"/>
-      <c r="P935" s="25" t="n"/>
-      <c r="Q935" s="25" t="n"/>
-      <c r="R935" s="8" t="n"/>
-    </row>
-    <row r="936" ht="15" customHeight="1" s="19">
-      <c r="A936" s="8" t="n"/>
-      <c r="B936" s="23" t="n"/>
-      <c r="C936" s="8" t="n"/>
-      <c r="D936" s="8" t="n"/>
-      <c r="E936" s="8" t="n"/>
-      <c r="F936" s="8" t="n"/>
-      <c r="G936" s="8" t="n"/>
-      <c r="H936" s="8" t="n"/>
-      <c r="I936" s="8" t="n"/>
-      <c r="J936" s="24" t="n"/>
-      <c r="K936" s="8" t="n"/>
-      <c r="L936" s="8" t="n"/>
-      <c r="M936" s="8" t="n"/>
-      <c r="N936" s="8" t="n"/>
-      <c r="O936" s="25" t="n"/>
-      <c r="P936" s="25" t="n"/>
-      <c r="Q936" s="25" t="n"/>
-      <c r="R936" s="8" t="n"/>
-    </row>
-    <row r="937" ht="15" customHeight="1" s="19">
-      <c r="A937" s="8" t="n"/>
-      <c r="B937" s="23" t="n"/>
-      <c r="C937" s="8" t="n"/>
-      <c r="D937" s="8" t="n"/>
-      <c r="E937" s="8" t="n"/>
-      <c r="F937" s="8" t="n"/>
-      <c r="G937" s="8" t="n"/>
-      <c r="H937" s="8" t="n"/>
-      <c r="I937" s="8" t="n"/>
-      <c r="J937" s="24" t="n"/>
-      <c r="K937" s="8" t="n"/>
-      <c r="L937" s="8" t="n"/>
-      <c r="M937" s="8" t="n"/>
-      <c r="N937" s="8" t="n"/>
-      <c r="O937" s="25" t="n"/>
-      <c r="P937" s="25" t="n"/>
-      <c r="Q937" s="25" t="n"/>
-      <c r="R937" s="8" t="n"/>
-    </row>
-    <row r="938" ht="15" customHeight="1" s="19">
-      <c r="A938" s="8" t="n"/>
-      <c r="B938" s="23" t="n"/>
-      <c r="C938" s="8" t="n"/>
-      <c r="D938" s="8" t="n"/>
-      <c r="E938" s="8" t="n"/>
-      <c r="F938" s="8" t="n"/>
-      <c r="G938" s="8" t="n"/>
-      <c r="H938" s="8" t="n"/>
-      <c r="I938" s="8" t="n"/>
-      <c r="J938" s="24" t="n"/>
-      <c r="K938" s="8" t="n"/>
-      <c r="L938" s="8" t="n"/>
-      <c r="M938" s="8" t="n"/>
-      <c r="N938" s="8" t="n"/>
-      <c r="O938" s="25" t="n"/>
-      <c r="P938" s="25" t="n"/>
-      <c r="Q938" s="25" t="n"/>
-      <c r="R938" s="8" t="n"/>
-    </row>
-    <row r="939" ht="15" customHeight="1" s="19">
-      <c r="A939" s="8" t="n"/>
-      <c r="B939" s="23" t="n"/>
-      <c r="C939" s="8" t="n"/>
-      <c r="D939" s="8" t="n"/>
-      <c r="E939" s="8" t="n"/>
-      <c r="F939" s="8" t="n"/>
-      <c r="G939" s="8" t="n"/>
-      <c r="H939" s="8" t="n"/>
-      <c r="I939" s="8" t="n"/>
-      <c r="J939" s="24" t="n"/>
-      <c r="K939" s="8" t="n"/>
-      <c r="L939" s="8" t="n"/>
-      <c r="M939" s="8" t="n"/>
-      <c r="N939" s="8" t="n"/>
-      <c r="O939" s="25" t="n"/>
-      <c r="P939" s="25" t="n"/>
-      <c r="Q939" s="25" t="n"/>
-      <c r="R939" s="8" t="n"/>
-    </row>
-    <row r="940" ht="15" customHeight="1" s="19">
-      <c r="A940" s="8" t="n"/>
-      <c r="B940" s="23" t="n"/>
-      <c r="C940" s="8" t="n"/>
-      <c r="D940" s="8" t="n"/>
-      <c r="E940" s="8" t="n"/>
-      <c r="F940" s="8" t="n"/>
-      <c r="G940" s="8" t="n"/>
-      <c r="H940" s="8" t="n"/>
-      <c r="I940" s="8" t="n"/>
-      <c r="J940" s="24" t="n"/>
-      <c r="K940" s="8" t="n"/>
-      <c r="L940" s="8" t="n"/>
-      <c r="M940" s="8" t="n"/>
-      <c r="N940" s="8" t="n"/>
-      <c r="O940" s="25" t="n"/>
-      <c r="P940" s="25" t="n"/>
-      <c r="Q940" s="25" t="n"/>
-      <c r="R940" s="8" t="n"/>
-    </row>
-    <row r="941" ht="15" customHeight="1" s="19">
-      <c r="A941" s="8" t="n"/>
-      <c r="B941" s="23" t="n"/>
-      <c r="C941" s="8" t="n"/>
-      <c r="D941" s="8" t="n"/>
-      <c r="E941" s="8" t="n"/>
-      <c r="F941" s="8" t="n"/>
-      <c r="G941" s="8" t="n"/>
-      <c r="H941" s="8" t="n"/>
-      <c r="I941" s="8" t="n"/>
-      <c r="J941" s="24" t="n"/>
-      <c r="K941" s="8" t="n"/>
-      <c r="L941" s="8" t="n"/>
-      <c r="M941" s="8" t="n"/>
-      <c r="N941" s="8" t="n"/>
-      <c r="O941" s="25" t="n"/>
-      <c r="P941" s="25" t="n"/>
-      <c r="Q941" s="25" t="n"/>
-      <c r="R941" s="8" t="n"/>
-    </row>
-    <row r="942" ht="15" customHeight="1" s="19">
-      <c r="A942" s="8" t="n"/>
-      <c r="B942" s="23" t="n"/>
-      <c r="C942" s="8" t="n"/>
-      <c r="D942" s="8" t="n"/>
-      <c r="E942" s="8" t="n"/>
-      <c r="F942" s="8" t="n"/>
-      <c r="G942" s="8" t="n"/>
-      <c r="H942" s="8" t="n"/>
-      <c r="I942" s="8" t="n"/>
-      <c r="J942" s="24" t="n"/>
-      <c r="K942" s="8" t="n"/>
-      <c r="L942" s="8" t="n"/>
-      <c r="M942" s="8" t="n"/>
-      <c r="N942" s="8" t="n"/>
-      <c r="O942" s="25" t="n"/>
-      <c r="P942" s="25" t="n"/>
-      <c r="Q942" s="25" t="n"/>
-      <c r="R942" s="8" t="n"/>
-    </row>
-    <row r="943" ht="15" customHeight="1" s="19">
-      <c r="A943" s="8" t="n"/>
-      <c r="B943" s="23" t="n"/>
-      <c r="C943" s="8" t="n"/>
-      <c r="D943" s="8" t="n"/>
-      <c r="E943" s="8" t="n"/>
-      <c r="F943" s="8" t="n"/>
-      <c r="G943" s="8" t="n"/>
-      <c r="H943" s="8" t="n"/>
-      <c r="I943" s="8" t="n"/>
-      <c r="J943" s="24" t="n"/>
-      <c r="K943" s="8" t="n"/>
-      <c r="L943" s="8" t="n"/>
-      <c r="M943" s="8" t="n"/>
-      <c r="N943" s="8" t="n"/>
-      <c r="O943" s="25" t="n"/>
-      <c r="P943" s="25" t="n"/>
-      <c r="Q943" s="25" t="n"/>
-      <c r="R943" s="8" t="n"/>
-    </row>
-    <row r="944" ht="15" customHeight="1" s="19">
-      <c r="A944" s="8" t="n"/>
-      <c r="B944" s="23" t="n"/>
-      <c r="C944" s="8" t="n"/>
-      <c r="D944" s="8" t="n"/>
-      <c r="E944" s="8" t="n"/>
-      <c r="F944" s="8" t="n"/>
-      <c r="G944" s="8" t="n"/>
-      <c r="H944" s="8" t="n"/>
-      <c r="I944" s="8" t="n"/>
-      <c r="J944" s="24" t="n"/>
-      <c r="K944" s="8" t="n"/>
-      <c r="L944" s="8" t="n"/>
-      <c r="M944" s="8" t="n"/>
-      <c r="N944" s="8" t="n"/>
-      <c r="O944" s="25" t="n"/>
-      <c r="P944" s="25" t="n"/>
-      <c r="Q944" s="25" t="n"/>
-      <c r="R944" s="8" t="n"/>
-    </row>
-    <row r="945" ht="15" customHeight="1" s="19">
-      <c r="A945" s="8" t="n"/>
-      <c r="B945" s="23" t="n"/>
-      <c r="C945" s="8" t="n"/>
-      <c r="D945" s="8" t="n"/>
-      <c r="E945" s="8" t="n"/>
-      <c r="F945" s="8" t="n"/>
-      <c r="G945" s="8" t="n"/>
-      <c r="H945" s="8" t="n"/>
-      <c r="I945" s="8" t="n"/>
-      <c r="J945" s="24" t="n"/>
-      <c r="K945" s="8" t="n"/>
-      <c r="L945" s="8" t="n"/>
-      <c r="M945" s="8" t="n"/>
-      <c r="N945" s="8" t="n"/>
-      <c r="O945" s="25" t="n"/>
-      <c r="P945" s="25" t="n"/>
-      <c r="Q945" s="25" t="n"/>
-      <c r="R945" s="8" t="n"/>
-    </row>
-    <row r="946" ht="15" customHeight="1" s="19">
-      <c r="A946" s="8" t="n"/>
-      <c r="B946" s="23" t="n"/>
-      <c r="C946" s="8" t="n"/>
-      <c r="D946" s="8" t="n"/>
-      <c r="E946" s="8" t="n"/>
-      <c r="F946" s="8" t="n"/>
-      <c r="G946" s="8" t="n"/>
-      <c r="H946" s="8" t="n"/>
-      <c r="I946" s="8" t="n"/>
-      <c r="J946" s="24" t="n"/>
-      <c r="K946" s="8" t="n"/>
-      <c r="L946" s="8" t="n"/>
-      <c r="M946" s="8" t="n"/>
-      <c r="N946" s="8" t="n"/>
-      <c r="O946" s="25" t="n"/>
-      <c r="P946" s="25" t="n"/>
-      <c r="Q946" s="25" t="n"/>
-      <c r="R946" s="8" t="n"/>
-    </row>
-    <row r="947" ht="15" customHeight="1" s="19">
-      <c r="A947" s="8" t="n"/>
-      <c r="B947" s="23" t="n"/>
-      <c r="C947" s="8" t="n"/>
-      <c r="D947" s="8" t="n"/>
-      <c r="E947" s="8" t="n"/>
-      <c r="F947" s="8" t="n"/>
-      <c r="G947" s="8" t="n"/>
-      <c r="H947" s="8" t="n"/>
-      <c r="I947" s="8" t="n"/>
-      <c r="J947" s="24" t="n"/>
-      <c r="K947" s="8" t="n"/>
-      <c r="L947" s="8" t="n"/>
-      <c r="M947" s="8" t="n"/>
-      <c r="N947" s="8" t="n"/>
-      <c r="O947" s="25" t="n"/>
-      <c r="P947" s="25" t="n"/>
-      <c r="Q947" s="25" t="n"/>
-      <c r="R947" s="8" t="n"/>
-    </row>
-    <row r="948" ht="15" customHeight="1" s="19">
-      <c r="A948" s="8" t="n"/>
-      <c r="B948" s="23" t="n"/>
-      <c r="C948" s="8" t="n"/>
-      <c r="D948" s="8" t="n"/>
-      <c r="E948" s="8" t="n"/>
-      <c r="F948" s="8" t="n"/>
-      <c r="G948" s="8" t="n"/>
-      <c r="H948" s="8" t="n"/>
-      <c r="I948" s="8" t="n"/>
-      <c r="J948" s="24" t="n"/>
-      <c r="K948" s="8" t="n"/>
-      <c r="L948" s="8" t="n"/>
-      <c r="M948" s="8" t="n"/>
-      <c r="N948" s="8" t="n"/>
-      <c r="O948" s="25" t="n"/>
-      <c r="P948" s="25" t="n"/>
-      <c r="Q948" s="25" t="n"/>
-      <c r="R948" s="8" t="n"/>
-    </row>
-    <row r="949" ht="15" customHeight="1" s="19">
-      <c r="A949" s="8" t="n"/>
-      <c r="B949" s="23" t="n"/>
-      <c r="C949" s="8" t="n"/>
-      <c r="D949" s="8" t="n"/>
-      <c r="E949" s="8" t="n"/>
-      <c r="F949" s="8" t="n"/>
-      <c r="G949" s="8" t="n"/>
-      <c r="H949" s="8" t="n"/>
-      <c r="I949" s="8" t="n"/>
-      <c r="J949" s="24" t="n"/>
-      <c r="K949" s="8" t="n"/>
-      <c r="L949" s="8" t="n"/>
-      <c r="M949" s="8" t="n"/>
-      <c r="N949" s="8" t="n"/>
-      <c r="O949" s="25" t="n"/>
-      <c r="P949" s="25" t="n"/>
-      <c r="Q949" s="25" t="n"/>
-      <c r="R949" s="8" t="n"/>
-    </row>
-    <row r="950" ht="15" customHeight="1" s="19">
-      <c r="A950" s="8" t="n"/>
-      <c r="B950" s="23" t="n"/>
-      <c r="C950" s="8" t="n"/>
-      <c r="D950" s="8" t="n"/>
-      <c r="E950" s="8" t="n"/>
-      <c r="F950" s="8" t="n"/>
-      <c r="G950" s="8" t="n"/>
-      <c r="H950" s="8" t="n"/>
-      <c r="I950" s="8" t="n"/>
-      <c r="J950" s="24" t="n"/>
-      <c r="K950" s="8" t="n"/>
-      <c r="L950" s="8" t="n"/>
-      <c r="M950" s="8" t="n"/>
-      <c r="N950" s="8" t="n"/>
-      <c r="O950" s="25" t="n"/>
-      <c r="P950" s="25" t="n"/>
-      <c r="Q950" s="25" t="n"/>
-      <c r="R950" s="8" t="n"/>
-    </row>
-    <row r="951" ht="15" customHeight="1" s="19">
-      <c r="A951" s="8" t="n"/>
-      <c r="B951" s="23" t="n"/>
-      <c r="C951" s="8" t="n"/>
-      <c r="D951" s="8" t="n"/>
-      <c r="E951" s="8" t="n"/>
-      <c r="F951" s="8" t="n"/>
-      <c r="G951" s="8" t="n"/>
-      <c r="H951" s="8" t="n"/>
-      <c r="I951" s="8" t="n"/>
-      <c r="J951" s="24" t="n"/>
-      <c r="K951" s="8" t="n"/>
-      <c r="L951" s="8" t="n"/>
-      <c r="M951" s="8" t="n"/>
-      <c r="N951" s="8" t="n"/>
-      <c r="O951" s="25" t="n"/>
-      <c r="P951" s="25" t="n"/>
-      <c r="Q951" s="25" t="n"/>
-      <c r="R951" s="8" t="n"/>
-    </row>
-    <row r="952" ht="15" customHeight="1" s="19">
-      <c r="A952" s="8" t="n"/>
-      <c r="B952" s="23" t="n"/>
-      <c r="C952" s="8" t="n"/>
-      <c r="D952" s="8" t="n"/>
-      <c r="E952" s="8" t="n"/>
-      <c r="F952" s="8" t="n"/>
-      <c r="G952" s="8" t="n"/>
-      <c r="H952" s="8" t="n"/>
-      <c r="I952" s="8" t="n"/>
-      <c r="J952" s="24" t="n"/>
-      <c r="K952" s="8" t="n"/>
-      <c r="L952" s="8" t="n"/>
-      <c r="M952" s="8" t="n"/>
-      <c r="N952" s="8" t="n"/>
-      <c r="O952" s="25" t="n"/>
-      <c r="P952" s="25" t="n"/>
-      <c r="Q952" s="25" t="n"/>
-      <c r="R952" s="8" t="n"/>
-    </row>
-    <row r="953" ht="15" customHeight="1" s="19">
-      <c r="A953" s="8" t="n"/>
-      <c r="B953" s="23" t="n"/>
-      <c r="C953" s="8" t="n"/>
-      <c r="D953" s="8" t="n"/>
-      <c r="E953" s="8" t="n"/>
-      <c r="F953" s="8" t="n"/>
-      <c r="G953" s="8" t="n"/>
-      <c r="H953" s="8" t="n"/>
-      <c r="I953" s="8" t="n"/>
-      <c r="J953" s="24" t="n"/>
-      <c r="K953" s="8" t="n"/>
-      <c r="L953" s="8" t="n"/>
-      <c r="M953" s="8" t="n"/>
-      <c r="N953" s="8" t="n"/>
-      <c r="O953" s="25" t="n"/>
-      <c r="P953" s="25" t="n"/>
-      <c r="Q953" s="25" t="n"/>
-      <c r="R953" s="8" t="n"/>
-    </row>
-    <row r="954" ht="15" customHeight="1" s="19">
-      <c r="A954" s="8" t="n"/>
-      <c r="B954" s="23" t="n"/>
-      <c r="C954" s="8" t="n"/>
-      <c r="D954" s="8" t="n"/>
-      <c r="E954" s="8" t="n"/>
-      <c r="F954" s="8" t="n"/>
-      <c r="G954" s="8" t="n"/>
-      <c r="H954" s="8" t="n"/>
-      <c r="I954" s="8" t="n"/>
-      <c r="J954" s="24" t="n"/>
-      <c r="K954" s="8" t="n"/>
-      <c r="L954" s="8" t="n"/>
-      <c r="M954" s="8" t="n"/>
-      <c r="N954" s="8" t="n"/>
-      <c r="O954" s="25" t="n"/>
-      <c r="P954" s="25" t="n"/>
-      <c r="Q954" s="25" t="n"/>
-      <c r="R954" s="8" t="n"/>
-    </row>
-    <row r="955" ht="15" customHeight="1" s="19">
-      <c r="A955" s="8" t="n"/>
-      <c r="B955" s="23" t="n"/>
-      <c r="C955" s="8" t="n"/>
-      <c r="D955" s="8" t="n"/>
-      <c r="E955" s="8" t="n"/>
-      <c r="F955" s="8" t="n"/>
-      <c r="G955" s="8" t="n"/>
-      <c r="H955" s="8" t="n"/>
-      <c r="I955" s="8" t="n"/>
-      <c r="J955" s="24" t="n"/>
-      <c r="K955" s="8" t="n"/>
-      <c r="L955" s="8" t="n"/>
-      <c r="M955" s="8" t="n"/>
-      <c r="N955" s="8" t="n"/>
-      <c r="O955" s="25" t="n"/>
-      <c r="P955" s="25" t="n"/>
-      <c r="Q955" s="25" t="n"/>
-      <c r="R955" s="8" t="n"/>
-    </row>
-    <row r="956" ht="15" customHeight="1" s="19">
-      <c r="A956" s="8" t="n"/>
-      <c r="B956" s="23" t="n"/>
-      <c r="C956" s="8" t="n"/>
-      <c r="D956" s="8" t="n"/>
-      <c r="E956" s="8" t="n"/>
-      <c r="F956" s="8" t="n"/>
-      <c r="G956" s="8" t="n"/>
-      <c r="H956" s="8" t="n"/>
-      <c r="I956" s="8" t="n"/>
-      <c r="J956" s="24" t="n"/>
-      <c r="K956" s="8" t="n"/>
-      <c r="L956" s="8" t="n"/>
-      <c r="M956" s="8" t="n"/>
-      <c r="N956" s="8" t="n"/>
-      <c r="O956" s="25" t="n"/>
-      <c r="P956" s="25" t="n"/>
-      <c r="Q956" s="25" t="n"/>
-      <c r="R956" s="8" t="n"/>
-    </row>
-    <row r="957" ht="15" customHeight="1" s="19">
-      <c r="A957" s="8" t="n"/>
-      <c r="B957" s="23" t="n"/>
-      <c r="C957" s="8" t="n"/>
-      <c r="D957" s="8" t="n"/>
-      <c r="E957" s="8" t="n"/>
-      <c r="F957" s="8" t="n"/>
-      <c r="G957" s="8" t="n"/>
-      <c r="H957" s="8" t="n"/>
-      <c r="I957" s="8" t="n"/>
-      <c r="J957" s="24" t="n"/>
-      <c r="K957" s="8" t="n"/>
-      <c r="L957" s="8" t="n"/>
-      <c r="M957" s="8" t="n"/>
-      <c r="N957" s="8" t="n"/>
-      <c r="O957" s="25" t="n"/>
-      <c r="P957" s="25" t="n"/>
-      <c r="Q957" s="25" t="n"/>
-      <c r="R957" s="8" t="n"/>
-    </row>
-    <row r="958" ht="15" customHeight="1" s="19">
-      <c r="A958" s="8" t="n"/>
-      <c r="B958" s="23" t="n"/>
-      <c r="C958" s="8" t="n"/>
-      <c r="D958" s="8" t="n"/>
-      <c r="E958" s="8" t="n"/>
-      <c r="F958" s="8" t="n"/>
-      <c r="G958" s="8" t="n"/>
-      <c r="H958" s="8" t="n"/>
-      <c r="I958" s="8" t="n"/>
-      <c r="J958" s="24" t="n"/>
-      <c r="K958" s="8" t="n"/>
-      <c r="L958" s="8" t="n"/>
-      <c r="M958" s="8" t="n"/>
-      <c r="N958" s="8" t="n"/>
-      <c r="O958" s="25" t="n"/>
-      <c r="P958" s="25" t="n"/>
-      <c r="Q958" s="25" t="n"/>
-      <c r="R958" s="8" t="n"/>
-    </row>
-    <row r="959" ht="15" customHeight="1" s="19">
-      <c r="A959" s="8" t="n"/>
-      <c r="B959" s="23" t="n"/>
-      <c r="C959" s="8" t="n"/>
-      <c r="D959" s="8" t="n"/>
-      <c r="E959" s="8" t="n"/>
-      <c r="F959" s="8" t="n"/>
-      <c r="G959" s="8" t="n"/>
-      <c r="H959" s="8" t="n"/>
-      <c r="I959" s="8" t="n"/>
-      <c r="J959" s="24" t="n"/>
-      <c r="K959" s="8" t="n"/>
-      <c r="L959" s="8" t="n"/>
-      <c r="M959" s="8" t="n"/>
-      <c r="N959" s="8" t="n"/>
-      <c r="O959" s="25" t="n"/>
-      <c r="P959" s="25" t="n"/>
-      <c r="Q959" s="25" t="n"/>
-      <c r="R959" s="8" t="n"/>
-    </row>
-    <row r="960" ht="15" customHeight="1" s="19">
-      <c r="A960" s="8" t="n"/>
-      <c r="B960" s="23" t="n"/>
-      <c r="C960" s="8" t="n"/>
-      <c r="D960" s="8" t="n"/>
-      <c r="E960" s="8" t="n"/>
-      <c r="F960" s="8" t="n"/>
-      <c r="G960" s="8" t="n"/>
-      <c r="H960" s="8" t="n"/>
-      <c r="I960" s="8" t="n"/>
-      <c r="J960" s="24" t="n"/>
-      <c r="K960" s="8" t="n"/>
-      <c r="L960" s="8" t="n"/>
-      <c r="M960" s="8" t="n"/>
-      <c r="N960" s="8" t="n"/>
-      <c r="O960" s="25" t="n"/>
-      <c r="P960" s="25" t="n"/>
-      <c r="Q960" s="25" t="n"/>
-      <c r="R960" s="8" t="n"/>
-    </row>
-    <row r="961" ht="15" customHeight="1" s="19">
-      <c r="A961" s="8" t="n"/>
-      <c r="B961" s="23" t="n"/>
-      <c r="C961" s="8" t="n"/>
-      <c r="D961" s="8" t="n"/>
-      <c r="E961" s="8" t="n"/>
-      <c r="F961" s="8" t="n"/>
-      <c r="G961" s="8" t="n"/>
-      <c r="H961" s="8" t="n"/>
-      <c r="I961" s="8" t="n"/>
-      <c r="J961" s="24" t="n"/>
-      <c r="K961" s="8" t="n"/>
-      <c r="L961" s="8" t="n"/>
-      <c r="M961" s="8" t="n"/>
-      <c r="N961" s="8" t="n"/>
-      <c r="O961" s="25" t="n"/>
-      <c r="P961" s="25" t="n"/>
-      <c r="Q961" s="25" t="n"/>
-      <c r="R961" s="8" t="n"/>
-    </row>
-    <row r="962" ht="15" customHeight="1" s="19">
-      <c r="A962" s="8" t="n"/>
-      <c r="B962" s="23" t="n"/>
-      <c r="C962" s="8" t="n"/>
-      <c r="D962" s="8" t="n"/>
-      <c r="E962" s="8" t="n"/>
-      <c r="F962" s="8" t="n"/>
-      <c r="G962" s="8" t="n"/>
-      <c r="H962" s="8" t="n"/>
-      <c r="I962" s="8" t="n"/>
-      <c r="J962" s="24" t="n"/>
-      <c r="K962" s="8" t="n"/>
-      <c r="L962" s="8" t="n"/>
-      <c r="M962" s="8" t="n"/>
-      <c r="N962" s="8" t="n"/>
-      <c r="O962" s="25" t="n"/>
-      <c r="P962" s="25" t="n"/>
-      <c r="Q962" s="25" t="n"/>
-      <c r="R962" s="8" t="n"/>
-    </row>
-    <row r="963" ht="15" customHeight="1" s="19">
-      <c r="A963" s="8" t="n"/>
-      <c r="B963" s="23" t="n"/>
-      <c r="C963" s="8" t="n"/>
-      <c r="D963" s="8" t="n"/>
-      <c r="E963" s="8" t="n"/>
-      <c r="F963" s="8" t="n"/>
-      <c r="G963" s="8" t="n"/>
-      <c r="H963" s="8" t="n"/>
-      <c r="I963" s="8" t="n"/>
-      <c r="J963" s="24" t="n"/>
-      <c r="K963" s="8" t="n"/>
-      <c r="L963" s="8" t="n"/>
-      <c r="M963" s="8" t="n"/>
-      <c r="N963" s="8" t="n"/>
-      <c r="O963" s="25" t="n"/>
-      <c r="P963" s="25" t="n"/>
-      <c r="Q963" s="25" t="n"/>
-      <c r="R963" s="8" t="n"/>
-    </row>
-    <row r="964" ht="15" customHeight="1" s="19">
-      <c r="A964" s="8" t="n"/>
-      <c r="B964" s="23" t="n"/>
-      <c r="C964" s="8" t="n"/>
-      <c r="D964" s="8" t="n"/>
-      <c r="E964" s="8" t="n"/>
-      <c r="F964" s="8" t="n"/>
-      <c r="G964" s="8" t="n"/>
-      <c r="H964" s="8" t="n"/>
-      <c r="I964" s="8" t="n"/>
-      <c r="J964" s="24" t="n"/>
-      <c r="K964" s="8" t="n"/>
-      <c r="L964" s="8" t="n"/>
-      <c r="M964" s="8" t="n"/>
-      <c r="N964" s="8" t="n"/>
-      <c r="O964" s="25" t="n"/>
-      <c r="P964" s="25" t="n"/>
-      <c r="Q964" s="25" t="n"/>
-      <c r="R964" s="8" t="n"/>
-    </row>
-    <row r="965" ht="15" customHeight="1" s="19">
-      <c r="A965" s="8" t="n"/>
-      <c r="B965" s="23" t="n"/>
-      <c r="C965" s="8" t="n"/>
-      <c r="D965" s="8" t="n"/>
-      <c r="E965" s="8" t="n"/>
-      <c r="F965" s="8" t="n"/>
-      <c r="G965" s="8" t="n"/>
-      <c r="H965" s="8" t="n"/>
-      <c r="I965" s="8" t="n"/>
-      <c r="J965" s="24" t="n"/>
-      <c r="K965" s="8" t="n"/>
-      <c r="L965" s="8" t="n"/>
-      <c r="M965" s="8" t="n"/>
-      <c r="N965" s="8" t="n"/>
-      <c r="O965" s="25" t="n"/>
-      <c r="P965" s="25" t="n"/>
-      <c r="Q965" s="25" t="n"/>
-      <c r="R965" s="8" t="n"/>
-    </row>
-    <row r="966" ht="15" customHeight="1" s="19">
-      <c r="A966" s="8" t="n"/>
-      <c r="B966" s="23" t="n"/>
-      <c r="C966" s="8" t="n"/>
-      <c r="D966" s="8" t="n"/>
-      <c r="E966" s="8" t="n"/>
-      <c r="F966" s="8" t="n"/>
-      <c r="G966" s="8" t="n"/>
-      <c r="H966" s="8" t="n"/>
-      <c r="I966" s="8" t="n"/>
-      <c r="J966" s="24" t="n"/>
-      <c r="K966" s="8" t="n"/>
-      <c r="L966" s="8" t="n"/>
-      <c r="M966" s="8" t="n"/>
-      <c r="N966" s="8" t="n"/>
-      <c r="O966" s="25" t="n"/>
-      <c r="P966" s="25" t="n"/>
-      <c r="Q966" s="25" t="n"/>
-      <c r="R966" s="8" t="n"/>
-    </row>
-    <row r="967" ht="15" customHeight="1" s="19">
-      <c r="A967" s="8" t="n"/>
-      <c r="B967" s="23" t="n"/>
-      <c r="C967" s="8" t="n"/>
-      <c r="D967" s="8" t="n"/>
-      <c r="E967" s="8" t="n"/>
-      <c r="F967" s="8" t="n"/>
-      <c r="G967" s="8" t="n"/>
-      <c r="H967" s="8" t="n"/>
-      <c r="I967" s="8" t="n"/>
-      <c r="J967" s="24" t="n"/>
-      <c r="K967" s="8" t="n"/>
-      <c r="L967" s="8" t="n"/>
-      <c r="M967" s="8" t="n"/>
-      <c r="N967" s="8" t="n"/>
-      <c r="O967" s="25" t="n"/>
-      <c r="P967" s="25" t="n"/>
-      <c r="Q967" s="25" t="n"/>
-      <c r="R967" s="8" t="n"/>
-    </row>
-    <row r="968" ht="15" customHeight="1" s="19">
-      <c r="A968" s="8" t="n"/>
-      <c r="B968" s="23" t="n"/>
-      <c r="C968" s="8" t="n"/>
-      <c r="D968" s="8" t="n"/>
-      <c r="E968" s="8" t="n"/>
-      <c r="F968" s="8" t="n"/>
-      <c r="G968" s="8" t="n"/>
-      <c r="H968" s="8" t="n"/>
-      <c r="I968" s="8" t="n"/>
-      <c r="J968" s="24" t="n"/>
-      <c r="K968" s="8" t="n"/>
-      <c r="L968" s="8" t="n"/>
-      <c r="M968" s="8" t="n"/>
-      <c r="N968" s="8" t="n"/>
-      <c r="O968" s="25" t="n"/>
-      <c r="P968" s="25" t="n"/>
-      <c r="Q968" s="25" t="n"/>
-      <c r="R968" s="8" t="n"/>
-    </row>
-    <row r="969" ht="15" customHeight="1" s="19">
-      <c r="A969" s="8" t="n"/>
-      <c r="B969" s="23" t="n"/>
-      <c r="C969" s="8" t="n"/>
-      <c r="D969" s="8" t="n"/>
-      <c r="E969" s="8" t="n"/>
-      <c r="F969" s="8" t="n"/>
-      <c r="G969" s="8" t="n"/>
-      <c r="H969" s="8" t="n"/>
-      <c r="I969" s="8" t="n"/>
-      <c r="J969" s="24" t="n"/>
-      <c r="K969" s="8" t="n"/>
-      <c r="L969" s="8" t="n"/>
-      <c r="M969" s="8" t="n"/>
-      <c r="N969" s="8" t="n"/>
-      <c r="O969" s="25" t="n"/>
-      <c r="P969" s="25" t="n"/>
-      <c r="Q969" s="25" t="n"/>
-      <c r="R969" s="8" t="n"/>
-    </row>
-    <row r="970" ht="15" customHeight="1" s="19">
-      <c r="A970" s="8" t="n"/>
-      <c r="B970" s="23" t="n"/>
-      <c r="C970" s="8" t="n"/>
-      <c r="D970" s="8" t="n"/>
-      <c r="E970" s="8" t="n"/>
-      <c r="F970" s="8" t="n"/>
-      <c r="G970" s="8" t="n"/>
-      <c r="H970" s="8" t="n"/>
-      <c r="I970" s="8" t="n"/>
-      <c r="J970" s="24" t="n"/>
-      <c r="K970" s="8" t="n"/>
-      <c r="L970" s="8" t="n"/>
-      <c r="M970" s="8" t="n"/>
-      <c r="N970" s="8" t="n"/>
-      <c r="O970" s="25" t="n"/>
-      <c r="P970" s="25" t="n"/>
-      <c r="Q970" s="25" t="n"/>
-      <c r="R970" s="8" t="n"/>
-    </row>
-    <row r="971" ht="15" customHeight="1" s="19">
-      <c r="A971" s="8" t="n"/>
-      <c r="B971" s="23" t="n"/>
-      <c r="C971" s="8" t="n"/>
-      <c r="D971" s="8" t="n"/>
-      <c r="E971" s="8" t="n"/>
-      <c r="F971" s="8" t="n"/>
-      <c r="G971" s="8" t="n"/>
-      <c r="H971" s="8" t="n"/>
-      <c r="I971" s="8" t="n"/>
-      <c r="J971" s="24" t="n"/>
-      <c r="K971" s="8" t="n"/>
-      <c r="L971" s="8" t="n"/>
-      <c r="M971" s="8" t="n"/>
-      <c r="N971" s="8" t="n"/>
-      <c r="O971" s="25" t="n"/>
-      <c r="P971" s="25" t="n"/>
-      <c r="Q971" s="25" t="n"/>
-      <c r="R971" s="8" t="n"/>
-    </row>
-    <row r="972" ht="15" customHeight="1" s="19">
-      <c r="A972" s="8" t="n"/>
-      <c r="B972" s="23" t="n"/>
-      <c r="C972" s="8" t="n"/>
-      <c r="D972" s="8" t="n"/>
-      <c r="E972" s="8" t="n"/>
-      <c r="F972" s="8" t="n"/>
-      <c r="G972" s="8" t="n"/>
-      <c r="H972" s="8" t="n"/>
-      <c r="I972" s="8" t="n"/>
-      <c r="J972" s="24" t="n"/>
-      <c r="K972" s="8" t="n"/>
-      <c r="L972" s="8" t="n"/>
-      <c r="M972" s="8" t="n"/>
-      <c r="N972" s="8" t="n"/>
-      <c r="O972" s="25" t="n"/>
-      <c r="P972" s="25" t="n"/>
-      <c r="Q972" s="25" t="n"/>
-      <c r="R972" s="8" t="n"/>
-    </row>
-    <row r="973" ht="15" customHeight="1" s="19">
-      <c r="A973" s="8" t="n"/>
-      <c r="B973" s="23" t="n"/>
-      <c r="C973" s="8" t="n"/>
-      <c r="D973" s="8" t="n"/>
-      <c r="E973" s="8" t="n"/>
-      <c r="F973" s="8" t="n"/>
-      <c r="G973" s="8" t="n"/>
-      <c r="H973" s="8" t="n"/>
-      <c r="I973" s="8" t="n"/>
-      <c r="J973" s="24" t="n"/>
-      <c r="K973" s="8" t="n"/>
-      <c r="L973" s="8" t="n"/>
-      <c r="M973" s="8" t="n"/>
-      <c r="N973" s="8" t="n"/>
-      <c r="O973" s="25" t="n"/>
-      <c r="P973" s="25" t="n"/>
-      <c r="Q973" s="25" t="n"/>
-      <c r="R973" s="8" t="n"/>
-    </row>
-    <row r="974" ht="15" customHeight="1" s="19">
-      <c r="A974" s="8" t="n"/>
-      <c r="B974" s="23" t="n"/>
-      <c r="C974" s="8" t="n"/>
-      <c r="D974" s="8" t="n"/>
-      <c r="E974" s="8" t="n"/>
-      <c r="F974" s="8" t="n"/>
-      <c r="G974" s="8" t="n"/>
-      <c r="H974" s="8" t="n"/>
-      <c r="I974" s="8" t="n"/>
-      <c r="J974" s="24" t="n"/>
-      <c r="K974" s="8" t="n"/>
-      <c r="L974" s="8" t="n"/>
-      <c r="M974" s="8" t="n"/>
-      <c r="N974" s="8" t="n"/>
-      <c r="O974" s="25" t="n"/>
-      <c r="P974" s="25" t="n"/>
-      <c r="Q974" s="25" t="n"/>
-      <c r="R974" s="8" t="n"/>
-    </row>
-    <row r="975" ht="15" customHeight="1" s="19">
-      <c r="A975" s="8" t="n"/>
-      <c r="B975" s="23" t="n"/>
-      <c r="C975" s="8" t="n"/>
-      <c r="D975" s="8" t="n"/>
-      <c r="E975" s="8" t="n"/>
-      <c r="F975" s="8" t="n"/>
-      <c r="G975" s="8" t="n"/>
-      <c r="H975" s="8" t="n"/>
-      <c r="I975" s="8" t="n"/>
-      <c r="J975" s="24" t="n"/>
-      <c r="K975" s="8" t="n"/>
-      <c r="L975" s="8" t="n"/>
-      <c r="M975" s="8" t="n"/>
-      <c r="N975" s="8" t="n"/>
-      <c r="O975" s="25" t="n"/>
-      <c r="P975" s="25" t="n"/>
-      <c r="Q975" s="25" t="n"/>
-      <c r="R975" s="8" t="n"/>
-    </row>
-    <row r="976" ht="15" customHeight="1" s="19">
-      <c r="A976" s="8" t="n"/>
-      <c r="B976" s="23" t="n"/>
-      <c r="C976" s="8" t="n"/>
-      <c r="D976" s="8" t="n"/>
-      <c r="E976" s="8" t="n"/>
-      <c r="F976" s="8" t="n"/>
-      <c r="G976" s="8" t="n"/>
-      <c r="H976" s="8" t="n"/>
-      <c r="I976" s="8" t="n"/>
-      <c r="J976" s="24" t="n"/>
-      <c r="K976" s="8" t="n"/>
-      <c r="L976" s="8" t="n"/>
-      <c r="M976" s="8" t="n"/>
-      <c r="N976" s="8" t="n"/>
-      <c r="O976" s="25" t="n"/>
-      <c r="P976" s="25" t="n"/>
-      <c r="Q976" s="25" t="n"/>
-      <c r="R976" s="8" t="n"/>
-    </row>
-    <row r="977" ht="15" customHeight="1" s="19">
-      <c r="A977" s="8" t="n"/>
-      <c r="B977" s="23" t="n"/>
-      <c r="C977" s="8" t="n"/>
-      <c r="D977" s="8" t="n"/>
-      <c r="E977" s="8" t="n"/>
-      <c r="F977" s="8" t="n"/>
-      <c r="G977" s="8" t="n"/>
-      <c r="H977" s="8" t="n"/>
-      <c r="I977" s="8" t="n"/>
-      <c r="J977" s="24" t="n"/>
-      <c r="K977" s="8" t="n"/>
-      <c r="L977" s="8" t="n"/>
-      <c r="M977" s="8" t="n"/>
-      <c r="N977" s="8" t="n"/>
-      <c r="O977" s="25" t="n"/>
-      <c r="P977" s="25" t="n"/>
-      <c r="Q977" s="25" t="n"/>
-      <c r="R977" s="8" t="n"/>
-    </row>
-    <row r="978" ht="15" customHeight="1" s="19">
-      <c r="A978" s="8" t="n"/>
-      <c r="B978" s="23" t="n"/>
-      <c r="C978" s="8" t="n"/>
-      <c r="D978" s="8" t="n"/>
-      <c r="E978" s="8" t="n"/>
-      <c r="F978" s="8" t="n"/>
-      <c r="G978" s="8" t="n"/>
-      <c r="H978" s="8" t="n"/>
-      <c r="I978" s="8" t="n"/>
-      <c r="J978" s="24" t="n"/>
-      <c r="K978" s="8" t="n"/>
-      <c r="L978" s="8" t="n"/>
-      <c r="M978" s="8" t="n"/>
-      <c r="N978" s="8" t="n"/>
-      <c r="O978" s="25" t="n"/>
-      <c r="P978" s="25" t="n"/>
-      <c r="Q978" s="25" t="n"/>
-      <c r="R978" s="8" t="n"/>
-    </row>
-    <row r="979" ht="15" customHeight="1" s="19">
-      <c r="A979" s="8" t="n"/>
-      <c r="B979" s="23" t="n"/>
-      <c r="C979" s="8" t="n"/>
-      <c r="D979" s="8" t="n"/>
-      <c r="E979" s="8" t="n"/>
-      <c r="F979" s="8" t="n"/>
-      <c r="G979" s="8" t="n"/>
-      <c r="H979" s="8" t="n"/>
-      <c r="I979" s="8" t="n"/>
-      <c r="J979" s="24" t="n"/>
-      <c r="K979" s="8" t="n"/>
-      <c r="L979" s="8" t="n"/>
-      <c r="M979" s="8" t="n"/>
-      <c r="N979" s="8" t="n"/>
-      <c r="O979" s="25" t="n"/>
-      <c r="P979" s="25" t="n"/>
-      <c r="Q979" s="25" t="n"/>
-      <c r="R979" s="8" t="n"/>
-    </row>
-    <row r="980" ht="15" customHeight="1" s="19">
-      <c r="A980" s="8" t="n"/>
-      <c r="B980" s="23" t="n"/>
-      <c r="C980" s="8" t="n"/>
-      <c r="D980" s="8" t="n"/>
-      <c r="E980" s="8" t="n"/>
-      <c r="F980" s="8" t="n"/>
-      <c r="G980" s="8" t="n"/>
-      <c r="H980" s="8" t="n"/>
-      <c r="I980" s="8" t="n"/>
-      <c r="J980" s="24" t="n"/>
-      <c r="K980" s="8" t="n"/>
-      <c r="L980" s="8" t="n"/>
-      <c r="M980" s="8" t="n"/>
-      <c r="N980" s="8" t="n"/>
-      <c r="O980" s="25" t="n"/>
-      <c r="P980" s="25" t="n"/>
-      <c r="Q980" s="25" t="n"/>
-      <c r="R980" s="8" t="n"/>
-    </row>
-    <row r="981" ht="15" customHeight="1" s="19">
-      <c r="A981" s="8" t="n"/>
-      <c r="B981" s="23" t="n"/>
-      <c r="C981" s="8" t="n"/>
-      <c r="D981" s="8" t="n"/>
-      <c r="E981" s="8" t="n"/>
-      <c r="F981" s="8" t="n"/>
-      <c r="G981" s="8" t="n"/>
-      <c r="H981" s="8" t="n"/>
-      <c r="I981" s="8" t="n"/>
-      <c r="J981" s="24" t="n"/>
-      <c r="K981" s="8" t="n"/>
-      <c r="L981" s="8" t="n"/>
-      <c r="M981" s="8" t="n"/>
-      <c r="N981" s="8" t="n"/>
-      <c r="O981" s="25" t="n"/>
-      <c r="P981" s="25" t="n"/>
-      <c r="Q981" s="25" t="n"/>
-      <c r="R981" s="8" t="n"/>
-    </row>
-    <row r="982" ht="15" customHeight="1" s="19">
-      <c r="A982" s="8" t="n"/>
-      <c r="B982" s="23" t="n"/>
-      <c r="C982" s="8" t="n"/>
-      <c r="D982" s="8" t="n"/>
-      <c r="E982" s="8" t="n"/>
-      <c r="F982" s="8" t="n"/>
-      <c r="G982" s="8" t="n"/>
-      <c r="H982" s="8" t="n"/>
-      <c r="I982" s="8" t="n"/>
-      <c r="J982" s="24" t="n"/>
-      <c r="K982" s="8" t="n"/>
-      <c r="L982" s="8" t="n"/>
-      <c r="M982" s="8" t="n"/>
-      <c r="N982" s="8" t="n"/>
-      <c r="O982" s="25" t="n"/>
-      <c r="P982" s="25" t="n"/>
-      <c r="Q982" s="25" t="n"/>
-      <c r="R982" s="8" t="n"/>
-    </row>
-    <row r="983" ht="15" customHeight="1" s="19">
-      <c r="A983" s="8" t="n"/>
-      <c r="B983" s="23" t="n"/>
-      <c r="C983" s="8" t="n"/>
-      <c r="D983" s="8" t="n"/>
-      <c r="E983" s="8" t="n"/>
-      <c r="F983" s="8" t="n"/>
-      <c r="G983" s="8" t="n"/>
-      <c r="H983" s="8" t="n"/>
-      <c r="I983" s="8" t="n"/>
-      <c r="J983" s="24" t="n"/>
-      <c r="K983" s="8" t="n"/>
-      <c r="L983" s="8" t="n"/>
-      <c r="M983" s="8" t="n"/>
-      <c r="N983" s="8" t="n"/>
-      <c r="O983" s="25" t="n"/>
-      <c r="P983" s="25" t="n"/>
-      <c r="Q983" s="25" t="n"/>
-      <c r="R983" s="8" t="n"/>
-    </row>
-    <row r="984" ht="15" customHeight="1" s="19">
-      <c r="A984" s="8" t="n"/>
-      <c r="B984" s="23" t="n"/>
-      <c r="C984" s="8" t="n"/>
-      <c r="D984" s="8" t="n"/>
-      <c r="E984" s="8" t="n"/>
-      <c r="F984" s="8" t="n"/>
-      <c r="G984" s="8" t="n"/>
-      <c r="H984" s="8" t="n"/>
-      <c r="I984" s="8" t="n"/>
-      <c r="J984" s="24" t="n"/>
-      <c r="K984" s="8" t="n"/>
-      <c r="L984" s="8" t="n"/>
-      <c r="M984" s="8" t="n"/>
-      <c r="N984" s="8" t="n"/>
-      <c r="O984" s="25" t="n"/>
-      <c r="P984" s="25" t="n"/>
-      <c r="Q984" s="25" t="n"/>
-      <c r="R984" s="8" t="n"/>
-    </row>
-    <row r="985" ht="15" customHeight="1" s="19">
-      <c r="A985" s="8" t="n"/>
-      <c r="B985" s="23" t="n"/>
-      <c r="C985" s="8" t="n"/>
-      <c r="D985" s="8" t="n"/>
-      <c r="E985" s="8" t="n"/>
-      <c r="F985" s="8" t="n"/>
-      <c r="G985" s="8" t="n"/>
-      <c r="H985" s="8" t="n"/>
-      <c r="I985" s="8" t="n"/>
-      <c r="J985" s="24" t="n"/>
-      <c r="K985" s="8" t="n"/>
-      <c r="L985" s="8" t="n"/>
-      <c r="M985" s="8" t="n"/>
-      <c r="N985" s="8" t="n"/>
-      <c r="O985" s="25" t="n"/>
-      <c r="P985" s="25" t="n"/>
-      <c r="Q985" s="25" t="n"/>
-      <c r="R985" s="8" t="n"/>
-    </row>
-    <row r="986" ht="15" customHeight="1" s="19">
-      <c r="A986" s="8" t="n"/>
-      <c r="B986" s="23" t="n"/>
-      <c r="C986" s="8" t="n"/>
-      <c r="D986" s="8" t="n"/>
-      <c r="E986" s="8" t="n"/>
-      <c r="F986" s="8" t="n"/>
-      <c r="G986" s="8" t="n"/>
-      <c r="H986" s="8" t="n"/>
-      <c r="I986" s="8" t="n"/>
-      <c r="J986" s="24" t="n"/>
-      <c r="K986" s="8" t="n"/>
-      <c r="L986" s="8" t="n"/>
-      <c r="M986" s="8" t="n"/>
-      <c r="N986" s="8" t="n"/>
-      <c r="O986" s="25" t="n"/>
-      <c r="P986" s="25" t="n"/>
-      <c r="Q986" s="25" t="n"/>
-      <c r="R986" s="8" t="n"/>
-    </row>
-    <row r="987" ht="15" customHeight="1" s="19">
-      <c r="A987" s="8" t="n"/>
-      <c r="B987" s="23" t="n"/>
-      <c r="C987" s="8" t="n"/>
-      <c r="D987" s="8" t="n"/>
-      <c r="E987" s="8" t="n"/>
-      <c r="F987" s="8" t="n"/>
-      <c r="G987" s="8" t="n"/>
-      <c r="H987" s="8" t="n"/>
-      <c r="I987" s="8" t="n"/>
-      <c r="J987" s="24" t="n"/>
-      <c r="K987" s="8" t="n"/>
-      <c r="L987" s="8" t="n"/>
-      <c r="M987" s="8" t="n"/>
-      <c r="N987" s="8" t="n"/>
-      <c r="O987" s="25" t="n"/>
-      <c r="P987" s="25" t="n"/>
-      <c r="Q987" s="25" t="n"/>
-      <c r="R987" s="8" t="n"/>
-    </row>
-    <row r="988" ht="15" customHeight="1" s="19">
-      <c r="A988" s="8" t="n"/>
-      <c r="B988" s="23" t="n"/>
-      <c r="C988" s="8" t="n"/>
-      <c r="D988" s="8" t="n"/>
-      <c r="E988" s="8" t="n"/>
-      <c r="F988" s="8" t="n"/>
-      <c r="G988" s="8" t="n"/>
-      <c r="H988" s="8" t="n"/>
-      <c r="I988" s="8" t="n"/>
-      <c r="J988" s="24" t="n"/>
-      <c r="K988" s="8" t="n"/>
-      <c r="L988" s="8" t="n"/>
-      <c r="M988" s="8" t="n"/>
-      <c r="N988" s="8" t="n"/>
-      <c r="O988" s="25" t="n"/>
-      <c r="P988" s="25" t="n"/>
-      <c r="Q988" s="25" t="n"/>
-      <c r="R988" s="8" t="n"/>
-    </row>
-    <row r="989" ht="15" customHeight="1" s="19">
-      <c r="A989" s="8" t="n"/>
-      <c r="B989" s="23" t="n"/>
-      <c r="C989" s="8" t="n"/>
-      <c r="D989" s="8" t="n"/>
-      <c r="E989" s="8" t="n"/>
-      <c r="F989" s="8" t="n"/>
-      <c r="G989" s="8" t="n"/>
-      <c r="H989" s="8" t="n"/>
-      <c r="I989" s="8" t="n"/>
-      <c r="J989" s="24" t="n"/>
-      <c r="K989" s="8" t="n"/>
-      <c r="L989" s="8" t="n"/>
-      <c r="M989" s="8" t="n"/>
-      <c r="N989" s="8" t="n"/>
-      <c r="O989" s="25" t="n"/>
-      <c r="P989" s="25" t="n"/>
-      <c r="Q989" s="25" t="n"/>
-      <c r="R989" s="8" t="n"/>
-    </row>
-    <row r="990" ht="15" customHeight="1" s="19">
-      <c r="A990" s="8" t="n"/>
-      <c r="B990" s="23" t="n"/>
-      <c r="C990" s="8" t="n"/>
-      <c r="D990" s="8" t="n"/>
-      <c r="E990" s="8" t="n"/>
-      <c r="F990" s="8" t="n"/>
-      <c r="G990" s="8" t="n"/>
-      <c r="H990" s="8" t="n"/>
-      <c r="I990" s="8" t="n"/>
-      <c r="J990" s="24" t="n"/>
-      <c r="K990" s="8" t="n"/>
-      <c r="L990" s="8" t="n"/>
-      <c r="M990" s="8" t="n"/>
-      <c r="N990" s="8" t="n"/>
-      <c r="O990" s="25" t="n"/>
-      <c r="P990" s="25" t="n"/>
-      <c r="Q990" s="25" t="n"/>
-      <c r="R990" s="8" t="n"/>
-    </row>
-    <row r="991" ht="15" customHeight="1" s="19">
-      <c r="A991" s="8" t="n"/>
-      <c r="B991" s="23" t="n"/>
-      <c r="C991" s="8" t="n"/>
-      <c r="D991" s="8" t="n"/>
-      <c r="E991" s="8" t="n"/>
-      <c r="F991" s="8" t="n"/>
-      <c r="G991" s="8" t="n"/>
-      <c r="H991" s="8" t="n"/>
-      <c r="I991" s="8" t="n"/>
-      <c r="J991" s="24" t="n"/>
-      <c r="K991" s="8" t="n"/>
-      <c r="L991" s="8" t="n"/>
-      <c r="M991" s="8" t="n"/>
-      <c r="N991" s="8" t="n"/>
-      <c r="O991" s="25" t="n"/>
-      <c r="P991" s="25" t="n"/>
-      <c r="Q991" s="25" t="n"/>
-      <c r="R991" s="8" t="n"/>
-    </row>
-    <row r="992" ht="15" customHeight="1" s="19">
-      <c r="A992" s="8" t="n"/>
-      <c r="B992" s="23" t="n"/>
-      <c r="C992" s="8" t="n"/>
-      <c r="D992" s="8" t="n"/>
-      <c r="E992" s="8" t="n"/>
-      <c r="F992" s="8" t="n"/>
-      <c r="G992" s="8" t="n"/>
-      <c r="H992" s="8" t="n"/>
-      <c r="I992" s="8" t="n"/>
-      <c r="J992" s="24" t="n"/>
-      <c r="K992" s="8" t="n"/>
-      <c r="L992" s="8" t="n"/>
-      <c r="M992" s="8" t="n"/>
-      <c r="N992" s="8" t="n"/>
-      <c r="O992" s="25" t="n"/>
-      <c r="P992" s="25" t="n"/>
-      <c r="Q992" s="25" t="n"/>
-      <c r="R992" s="8" t="n"/>
-    </row>
-    <row r="993" ht="15" customHeight="1" s="19">
-      <c r="A993" s="8" t="n"/>
-      <c r="B993" s="23" t="n"/>
-      <c r="C993" s="8" t="n"/>
-      <c r="D993" s="8" t="n"/>
-      <c r="E993" s="8" t="n"/>
-      <c r="F993" s="8" t="n"/>
-      <c r="G993" s="8" t="n"/>
-      <c r="H993" s="8" t="n"/>
-      <c r="I993" s="8" t="n"/>
-      <c r="J993" s="24" t="n"/>
-      <c r="K993" s="8" t="n"/>
-      <c r="L993" s="8" t="n"/>
-      <c r="M993" s="8" t="n"/>
-      <c r="N993" s="8" t="n"/>
-      <c r="O993" s="25" t="n"/>
-      <c r="P993" s="25" t="n"/>
-      <c r="Q993" s="25" t="n"/>
-      <c r="R993" s="8" t="n"/>
-    </row>
-    <row r="994" ht="15" customHeight="1" s="19">
-      <c r="A994" s="8" t="n"/>
-      <c r="B994" s="23" t="n"/>
-      <c r="C994" s="8" t="n"/>
-      <c r="D994" s="8" t="n"/>
-      <c r="E994" s="8" t="n"/>
-      <c r="F994" s="8" t="n"/>
-      <c r="G994" s="8" t="n"/>
-      <c r="H994" s="8" t="n"/>
-      <c r="I994" s="8" t="n"/>
-      <c r="J994" s="24" t="n"/>
-      <c r="K994" s="8" t="n"/>
-      <c r="L994" s="8" t="n"/>
-      <c r="M994" s="8" t="n"/>
-      <c r="N994" s="8" t="n"/>
-      <c r="O994" s="25" t="n"/>
-      <c r="P994" s="25" t="n"/>
-      <c r="Q994" s="25" t="n"/>
-      <c r="R994" s="8" t="n"/>
-    </row>
-    <row r="995" ht="15" customHeight="1" s="19">
-      <c r="A995" s="8" t="n"/>
-      <c r="B995" s="23" t="n"/>
-      <c r="C995" s="8" t="n"/>
-      <c r="D995" s="8" t="n"/>
-      <c r="E995" s="8" t="n"/>
-      <c r="F995" s="8" t="n"/>
-      <c r="G995" s="8" t="n"/>
-      <c r="H995" s="8" t="n"/>
-      <c r="I995" s="8" t="n"/>
-      <c r="J995" s="24" t="n"/>
-      <c r="K995" s="8" t="n"/>
-      <c r="L995" s="8" t="n"/>
-      <c r="M995" s="8" t="n"/>
-      <c r="N995" s="8" t="n"/>
-      <c r="O995" s="25" t="n"/>
-      <c r="P995" s="25" t="n"/>
-      <c r="Q995" s="25" t="n"/>
-      <c r="R995" s="8" t="n"/>
-    </row>
-    <row r="996" ht="15" customHeight="1" s="19">
-      <c r="A996" s="8" t="n"/>
-      <c r="B996" s="23" t="n"/>
-      <c r="C996" s="8" t="n"/>
-      <c r="D996" s="8" t="n"/>
-      <c r="E996" s="8" t="n"/>
-      <c r="F996" s="8" t="n"/>
-      <c r="G996" s="8" t="n"/>
-      <c r="H996" s="8" t="n"/>
-      <c r="I996" s="8" t="n"/>
-      <c r="J996" s="24" t="n"/>
-      <c r="K996" s="8" t="n"/>
-      <c r="L996" s="8" t="n"/>
-      <c r="M996" s="8" t="n"/>
-      <c r="N996" s="8" t="n"/>
-      <c r="O996" s="25" t="n"/>
-      <c r="P996" s="25" t="n"/>
-      <c r="Q996" s="25" t="n"/>
-      <c r="R996" s="8" t="n"/>
-    </row>
-    <row r="997" ht="15" customHeight="1" s="19">
-      <c r="A997" s="8" t="n"/>
-      <c r="B997" s="23" t="n"/>
-      <c r="C997" s="8" t="n"/>
-      <c r="D997" s="8" t="n"/>
-      <c r="E997" s="8" t="n"/>
-      <c r="F997" s="8" t="n"/>
-      <c r="G997" s="8" t="n"/>
-      <c r="H997" s="8" t="n"/>
-      <c r="I997" s="8" t="n"/>
-      <c r="J997" s="24" t="n"/>
-      <c r="K997" s="8" t="n"/>
-      <c r="L997" s="8" t="n"/>
-      <c r="M997" s="8" t="n"/>
-      <c r="N997" s="8" t="n"/>
-      <c r="O997" s="25" t="n"/>
-      <c r="P997" s="25" t="n"/>
-      <c r="Q997" s="25" t="n"/>
-      <c r="R997" s="8" t="n"/>
-    </row>
-    <row r="998" ht="15" customHeight="1" s="19">
-      <c r="A998" s="8" t="n"/>
-      <c r="B998" s="23" t="n"/>
-      <c r="C998" s="8" t="n"/>
-      <c r="D998" s="8" t="n"/>
-      <c r="E998" s="8" t="n"/>
-      <c r="F998" s="8" t="n"/>
-      <c r="G998" s="8" t="n"/>
-      <c r="H998" s="8" t="n"/>
-      <c r="I998" s="8" t="n"/>
-      <c r="J998" s="24" t="n"/>
-      <c r="K998" s="8" t="n"/>
-      <c r="L998" s="8" t="n"/>
-      <c r="M998" s="8" t="n"/>
-      <c r="N998" s="8" t="n"/>
-      <c r="O998" s="25" t="n"/>
-      <c r="P998" s="25" t="n"/>
-      <c r="Q998" s="25" t="n"/>
-      <c r="R998" s="8" t="n"/>
-    </row>
-    <row r="999" ht="15" customHeight="1" s="19">
-      <c r="A999" s="8" t="n"/>
-      <c r="B999" s="23" t="n"/>
-      <c r="C999" s="8" t="n"/>
-      <c r="D999" s="8" t="n"/>
-      <c r="E999" s="8" t="n"/>
-      <c r="F999" s="8" t="n"/>
-      <c r="G999" s="8" t="n"/>
-      <c r="H999" s="8" t="n"/>
-      <c r="I999" s="8" t="n"/>
-      <c r="J999" s="24" t="n"/>
-      <c r="K999" s="8" t="n"/>
-      <c r="L999" s="8" t="n"/>
-      <c r="M999" s="8" t="n"/>
-      <c r="N999" s="8" t="n"/>
-      <c r="O999" s="25" t="n"/>
-      <c r="P999" s="25" t="n"/>
-      <c r="Q999" s="25" t="n"/>
-      <c r="R999" s="8" t="n"/>
-    </row>
-    <row r="1000" ht="15" customHeight="1" s="19">
-      <c r="A1000" s="8" t="n"/>
-      <c r="B1000" s="23" t="n"/>
-      <c r="C1000" s="8" t="n"/>
-      <c r="D1000" s="8" t="n"/>
-      <c r="E1000" s="8" t="n"/>
-      <c r="F1000" s="8" t="n"/>
-      <c r="G1000" s="8" t="n"/>
-      <c r="H1000" s="8" t="n"/>
-      <c r="I1000" s="8" t="n"/>
-      <c r="J1000" s="24" t="n"/>
-      <c r="K1000" s="8" t="n"/>
-      <c r="L1000" s="8" t="n"/>
-      <c r="M1000" s="8" t="n"/>
-      <c r="N1000" s="8" t="n"/>
-      <c r="O1000" s="25" t="n"/>
-      <c r="P1000" s="25" t="n"/>
-      <c r="Q1000" s="25" t="n"/>
-      <c r="R1000" s="8" t="n"/>
-    </row>
+    <row r="853" ht="15" customHeight="1" s="19"/>
+    <row r="854" ht="15" customHeight="1" s="19"/>
+    <row r="855" ht="15" customHeight="1" s="19"/>
+    <row r="856" ht="15" customHeight="1" s="19"/>
+    <row r="857" ht="15" customHeight="1" s="19"/>
+    <row r="858" ht="15" customHeight="1" s="19"/>
+    <row r="859" ht="15" customHeight="1" s="19"/>
+    <row r="860" ht="15" customHeight="1" s="19"/>
+    <row r="861" ht="15" customHeight="1" s="19"/>
+    <row r="862" ht="15" customHeight="1" s="19"/>
+    <row r="863" ht="15" customHeight="1" s="19"/>
+    <row r="864" ht="15" customHeight="1" s="19"/>
+    <row r="865" ht="15" customHeight="1" s="19"/>
+    <row r="866" ht="15" customHeight="1" s="19"/>
+    <row r="867" ht="15" customHeight="1" s="19"/>
+    <row r="868" ht="15" customHeight="1" s="19"/>
+    <row r="869" ht="15" customHeight="1" s="19"/>
+    <row r="870" ht="15" customHeight="1" s="19"/>
+    <row r="871" ht="15" customHeight="1" s="19"/>
+    <row r="872" ht="15" customHeight="1" s="19"/>
+    <row r="873" ht="15" customHeight="1" s="19"/>
+    <row r="874" ht="15" customHeight="1" s="19"/>
+    <row r="875" ht="15" customHeight="1" s="19"/>
+    <row r="876" ht="15" customHeight="1" s="19"/>
+    <row r="877" ht="15" customHeight="1" s="19"/>
+    <row r="878" ht="15" customHeight="1" s="19"/>
+    <row r="879" ht="15" customHeight="1" s="19"/>
+    <row r="880" ht="15" customHeight="1" s="19"/>
+    <row r="881" ht="15" customHeight="1" s="19"/>
+    <row r="882" ht="15" customHeight="1" s="19"/>
+    <row r="883" ht="15" customHeight="1" s="19"/>
+    <row r="884" ht="15" customHeight="1" s="19"/>
+    <row r="885" ht="15" customHeight="1" s="19"/>
+    <row r="886" ht="15" customHeight="1" s="19"/>
+    <row r="887" ht="15" customHeight="1" s="19"/>
+    <row r="888" ht="15" customHeight="1" s="19"/>
+    <row r="889" ht="15" customHeight="1" s="19"/>
+    <row r="890" ht="15" customHeight="1" s="19"/>
+    <row r="891" ht="15" customHeight="1" s="19"/>
+    <row r="892" ht="15" customHeight="1" s="19"/>
+    <row r="893" ht="15" customHeight="1" s="19"/>
+    <row r="894" ht="15" customHeight="1" s="19"/>
+    <row r="895" ht="15" customHeight="1" s="19"/>
+    <row r="896" ht="15" customHeight="1" s="19"/>
+    <row r="897" ht="15" customHeight="1" s="19"/>
+    <row r="898" ht="15" customHeight="1" s="19"/>
+    <row r="899" ht="15" customHeight="1" s="19"/>
+    <row r="900" ht="15" customHeight="1" s="19"/>
+    <row r="901" ht="15" customHeight="1" s="19"/>
+    <row r="902" ht="15" customHeight="1" s="19"/>
+    <row r="903" ht="15" customHeight="1" s="19"/>
+    <row r="904" ht="15" customHeight="1" s="19"/>
+    <row r="905" ht="15" customHeight="1" s="19"/>
+    <row r="906" ht="15" customHeight="1" s="19"/>
+    <row r="907" ht="15" customHeight="1" s="19"/>
+    <row r="908" ht="15" customHeight="1" s="19"/>
+    <row r="909" ht="15" customHeight="1" s="19"/>
+    <row r="910" ht="15" customHeight="1" s="19"/>
+    <row r="911" ht="15" customHeight="1" s="19"/>
+    <row r="912" ht="15" customHeight="1" s="19"/>
+    <row r="913" ht="15" customHeight="1" s="19"/>
+    <row r="914" ht="15" customHeight="1" s="19"/>
+    <row r="915" ht="15" customHeight="1" s="19"/>
+    <row r="916" ht="15" customHeight="1" s="19"/>
+    <row r="917" ht="15" customHeight="1" s="19"/>
+    <row r="918" ht="15" customHeight="1" s="19"/>
+    <row r="919" ht="15" customHeight="1" s="19"/>
+    <row r="920" ht="15" customHeight="1" s="19"/>
+    <row r="921" ht="15" customHeight="1" s="19"/>
+    <row r="922" ht="15" customHeight="1" s="19"/>
+    <row r="923" ht="15" customHeight="1" s="19"/>
+    <row r="924" ht="15" customHeight="1" s="19"/>
+    <row r="925" ht="15" customHeight="1" s="19"/>
+    <row r="926" ht="15" customHeight="1" s="19"/>
+    <row r="927" ht="15" customHeight="1" s="19"/>
+    <row r="928" ht="15" customHeight="1" s="19"/>
+    <row r="929" ht="15" customHeight="1" s="19"/>
+    <row r="930" ht="15" customHeight="1" s="19"/>
+    <row r="931" ht="15" customHeight="1" s="19"/>
+    <row r="932" ht="15" customHeight="1" s="19"/>
+    <row r="933" ht="15" customHeight="1" s="19"/>
+    <row r="934" ht="15" customHeight="1" s="19"/>
+    <row r="935" ht="15" customHeight="1" s="19"/>
+    <row r="936" ht="15" customHeight="1" s="19"/>
+    <row r="937" ht="15" customHeight="1" s="19"/>
+    <row r="938" ht="15" customHeight="1" s="19"/>
+    <row r="939" ht="15" customHeight="1" s="19"/>
+    <row r="940" ht="15" customHeight="1" s="19"/>
+    <row r="941" ht="15" customHeight="1" s="19"/>
+    <row r="942" ht="15" customHeight="1" s="19"/>
+    <row r="943" ht="15" customHeight="1" s="19"/>
+    <row r="944" ht="15" customHeight="1" s="19"/>
+    <row r="945" ht="15" customHeight="1" s="19"/>
+    <row r="946" ht="15" customHeight="1" s="19"/>
+    <row r="947" ht="15" customHeight="1" s="19"/>
+    <row r="948" ht="15" customHeight="1" s="19"/>
+    <row r="949" ht="15" customHeight="1" s="19"/>
+    <row r="950" ht="15" customHeight="1" s="19"/>
+    <row r="951" ht="15" customHeight="1" s="19"/>
+    <row r="952" ht="15" customHeight="1" s="19"/>
+    <row r="953" ht="15" customHeight="1" s="19"/>
+    <row r="954" ht="15" customHeight="1" s="19"/>
+    <row r="955" ht="15" customHeight="1" s="19"/>
+    <row r="956" ht="15" customHeight="1" s="19"/>
+    <row r="957" ht="15" customHeight="1" s="19"/>
+    <row r="958" ht="15" customHeight="1" s="19"/>
+    <row r="959" ht="15" customHeight="1" s="19"/>
+    <row r="960" ht="15" customHeight="1" s="19"/>
+    <row r="961" ht="15" customHeight="1" s="19"/>
+    <row r="962" ht="15" customHeight="1" s="19"/>
+    <row r="963" ht="15" customHeight="1" s="19"/>
+    <row r="964" ht="15" customHeight="1" s="19"/>
+    <row r="965" ht="15" customHeight="1" s="19"/>
+    <row r="966" ht="15" customHeight="1" s="19"/>
+    <row r="967" ht="15" customHeight="1" s="19"/>
+    <row r="968" ht="15" customHeight="1" s="19"/>
+    <row r="969" ht="15" customHeight="1" s="19"/>
+    <row r="970" ht="15" customHeight="1" s="19"/>
+    <row r="971" ht="15" customHeight="1" s="19"/>
+    <row r="972" ht="15" customHeight="1" s="19"/>
+    <row r="973" ht="15" customHeight="1" s="19"/>
+    <row r="974" ht="15" customHeight="1" s="19"/>
+    <row r="975" ht="15" customHeight="1" s="19"/>
+    <row r="976" ht="15" customHeight="1" s="19"/>
+    <row r="977" ht="15" customHeight="1" s="19"/>
+    <row r="978" ht="15" customHeight="1" s="19"/>
+    <row r="979" ht="15" customHeight="1" s="19"/>
+    <row r="980" ht="15" customHeight="1" s="19"/>
+    <row r="981" ht="15" customHeight="1" s="19"/>
+    <row r="982" ht="15" customHeight="1" s="19"/>
+    <row r="983" ht="15" customHeight="1" s="19"/>
+    <row r="984" ht="15" customHeight="1" s="19"/>
+    <row r="985" ht="15" customHeight="1" s="19"/>
+    <row r="986" ht="15" customHeight="1" s="19"/>
+    <row r="987" ht="15" customHeight="1" s="19"/>
+    <row r="988" ht="15" customHeight="1" s="19"/>
+    <row r="989" ht="15" customHeight="1" s="19"/>
+    <row r="990" ht="15" customHeight="1" s="19"/>
+    <row r="991" ht="15" customHeight="1" s="19"/>
+    <row r="992" ht="15" customHeight="1" s="19"/>
+    <row r="993" ht="15" customHeight="1" s="19"/>
+    <row r="994" ht="15" customHeight="1" s="19"/>
+    <row r="995" ht="15" customHeight="1" s="19"/>
+    <row r="996" ht="15" customHeight="1" s="19"/>
+    <row r="997" ht="15" customHeight="1" s="19"/>
+    <row r="998" ht="15" customHeight="1" s="19"/>
+    <row r="999" ht="15" customHeight="1" s="19"/>
+    <row r="1000" ht="15" customHeight="1" s="19"/>
   </sheetData>
   <autoFilter ref="A1:R1000"/>
   <dataValidations count="7">
